--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="172">
   <si>
     <t>太空战舰是一个科幻飞行器不断攻击敌方飞行器的小游戏，横版，即时，有相关画面。玩家不需操作</t>
   </si>
@@ -265,6 +265,33 @@
     <t>支持可扩展，会以para_1,para_2等方式不断扩张</t>
   </si>
   <si>
+    <t>hightech</t>
+  </si>
+  <si>
+    <t>这个高科技的名字</t>
+  </si>
+  <si>
+    <t>高科技的效果</t>
+  </si>
+  <si>
+    <t>timeCostBase</t>
+  </si>
+  <si>
+    <t>升级高科技需要的基础时间</t>
+  </si>
+  <si>
+    <t>timeCostMutiple</t>
+  </si>
+  <si>
+    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为1.2，则2级12秒，3级14秒...四舍五入取整</t>
+  </si>
+  <si>
+    <t>通过第几关后解锁</t>
+  </si>
+  <si>
+    <t>可变参数，可能有多个，具体效果参看高科技的效果des</t>
+  </si>
+  <si>
     <t>如上</t>
   </si>
   <si>
@@ -488,6 +515,39 @@
   </si>
   <si>
     <t>死亡时后退距离</t>
+  </si>
+  <si>
+    <t>hightechLimit</t>
+  </si>
+  <si>
+    <t>同时研发的高科技数量</t>
+  </si>
+  <si>
+    <t>这个神器的名字</t>
+  </si>
+  <si>
+    <t>神器的效果</t>
+  </si>
+  <si>
+    <t>升级神器需要的基础时间</t>
+  </si>
+  <si>
+    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为0.2，则2级12秒，3级14秒...四舍五入取整</t>
+  </si>
+  <si>
+    <t>可变参数，具体效果参看神器的效果des</t>
+  </si>
+  <si>
+    <t>反物质炼铁炉</t>
+  </si>
+  <si>
+    <t>每para1秒在屏幕中生成一个铁块，总共含有根据过去一分钟的铁生成量*para2*等级的铁，点击获取，10秒后消失</t>
+  </si>
+  <si>
+    <t>正电子聚焦装置</t>
+  </si>
+  <si>
+    <t>提高所有能量武器的伤害，效果为原伤害*（1+para1*等级）.</t>
   </si>
 </sst>
 </file>
@@ -1103,8 +1163,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1438,7 +1501,7 @@
       <c r="B1" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1455,13 +1518,13 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1469,10 +1532,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1480,10 +1543,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1491,10 +1554,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1502,10 +1565,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1513,10 +1576,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1524,10 +1587,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1535,10 +1598,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1546,10 +1609,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
@@ -1531,88 +1531,180 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" t="s">
-        <v>134</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">激光飞船</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,null,1,1,1,null,null,null,null}</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" t="s">
-        <v>135</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火炮飞船</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,null,2,2,2,null,null,null,null}</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" t="s">
-        <v>137</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基础飞船组</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,null,3,1,2,4,null,null,null}</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C7" t="s">
-        <v>139</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">激光飞船-弱*6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,3,3,3,3,3,3,null,null}</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" t="s">
-        <v>141</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火炮飞船-弱*6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,4,4,4,4,4,4,null,null}</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" t="s">
-        <v>143</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOSS飞船-抵抗物理</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,null,null,5,null,null,null,null,null}</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" t="s">
-        <v>145</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOSS飞船-抵抗能量</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,null,null,6,null,null,null,null,null}</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" t="s">
-        <v>147</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOSS飞船-双BOSS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">｛null，null，null，5，null，null，6，null，null，null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOSS飞船-双抵抗物理</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,null,5,null,5,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOSS飞船-双抵抗能量</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,null,6,null,6,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">激光飞船-弱*4+强2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,3,3,1,1,3,3,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火炮飞船-弱*4+强2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,4,4,2,2,4,4,null,null}</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSS飞船-抵抗物理</t>
+          <t xml:space="preserve">中型飞船-抵抗物理</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSS飞船-抵抗能量</t>
+          <t xml:space="preserve">中型飞船-抵抗能量</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSS飞船-双BOSS</t>
+          <t xml:space="preserve">中型飞船-混合</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">｛null，null，null，5，null，null，6，null，null，null}</t>
+          <t xml:space="preserve">{null,null,null,5,null,null,6,null,null,null}</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSS飞船-双抵抗物理</t>
+          <t xml:space="preserve">中型飞船-双抵抗物理</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSS飞船-双抵抗能量</t>
+          <t xml:space="preserve">中型飞船-双抵抗能量</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1704,6 +1704,51 @@
       <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">{null,null,4,4,2,2,4,4,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大型飞船-抵抗物理</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,null,null,8,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大型飞船-抵抗能量</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,null,null,7,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大型飞船-混合</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{null,null,null,null,7,8,null,null,null,null}</t>
         </is>
       </c>
     </row>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -5,14 +5,14 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="0" firstSheet="0"/>
+    <workbookView windowWidth="17700" windowHeight="13908"/>
   </bookViews>
   <sheets>
-    <sheet name="monGroup" sheetId="5" r:id="rId5" state="visible"/>
+    <sheet name="monGroup" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,203 +32,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="172">
-  <si>
-    <t>太空战舰是一个科幻飞行器不断攻击敌方飞行器的小游戏，横版，即时，有相关画面。玩家不需操作</t>
-  </si>
-  <si>
-    <t>战舰会自动使用武器，攻击敌方飞行器，武器有各种参数，在武器表里定义</t>
-  </si>
-  <si>
-    <t>在每个关卡，敌方飞行器每隔一段距离就会出现。全部击落后才能前进，战斗时无法移动。关卡最后出现一个敌方BOSS飞行器，击毁后通关</t>
-  </si>
-  <si>
-    <t>敌方飞行器有各种参数，在怪物表里配置。怪物群负责整理一整群怪物，而关卡表将配置怪物群，用来辨别哪些敌方飞行器将出现在关卡里及出现在关卡的什么位置</t>
-  </si>
-  <si>
-    <t>敌方飞行器被击毁后会掉落资源，鼠标划过可以拾取。如果一段时间没有拾取，则自动拾取，但会有损耗，损耗比例在config里配置</t>
-  </si>
-  <si>
-    <t>飞行器初始武器为激光，激光会发射一道光束，攻击一个目标。</t>
-  </si>
-  <si>
-    <t>第二个武器为导弹，导弹在通关第一关后获得，导弹会同时发射3枚导弹，锁定3个敌人（若不足则只发射对应数量的导弹）</t>
-  </si>
-  <si>
-    <t>玩家可以选择任何一个已经通关过的关卡重新通关，或者无限循环该关卡。如果选择循环，则击败BOSS后就从这关开始重新前进</t>
-  </si>
-  <si>
-    <t>具体配置如下，表格均从第四行开始是实际配置</t>
-  </si>
-  <si>
-    <t>表格名</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>列名</t>
-  </si>
-  <si>
-    <t>用途</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="562">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>关卡的id</t>
-  </si>
-  <si>
-    <t>length</t>
-  </si>
-  <si>
-    <t>关卡长度</t>
-  </si>
-  <si>
-    <t>monGroup</t>
-  </si>
-  <si>
-    <t>怪物群id</t>
-  </si>
-  <si>
-    <t>格式为{id|比例，id|比例....}，id为monGroup表的id，比例表示在关卡长度的%多少处出现</t>
-  </si>
-  <si>
-    <t>atkRatio</t>
-  </si>
-  <si>
-    <t>攻击倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器的器伤害*这个值（向上取整，没有小数）</t>
-  </si>
-  <si>
-    <t>所有倍率，在关卡中由上一关的倍率线性成长到本关倍率。如第一关倍率是1，第二关倍率是10，则10%的长度时是2..以此类推</t>
-  </si>
-  <si>
-    <t>lifeRatio</t>
-  </si>
-  <si>
-    <t>生命倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器的生命*这个值（向上取整，没有小数）</t>
-  </si>
-  <si>
-    <t>resRatio</t>
-  </si>
-  <si>
-    <t>资源倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器摧毁时获得的资源乘该值</t>
-  </si>
-  <si>
-    <t>equipment</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>武器名</t>
-  </si>
-  <si>
     <t>des</t>
   </si>
   <si>
-    <t>武器说明</t>
-  </si>
-  <si>
-    <t>武器等级</t>
-  </si>
-  <si>
-    <t>dmg</t>
-  </si>
-  <si>
-    <t>武器命中时的伤害</t>
-  </si>
-  <si>
-    <t>cd</t>
-  </si>
-  <si>
-    <t>武器发射需要的时间</t>
-  </si>
-  <si>
-    <t>unlock</t>
-  </si>
-  <si>
-    <t>对应level表id，通关对应id的关卡后解锁该武器</t>
-  </si>
-  <si>
-    <t>res_1</t>
-  </si>
-  <si>
-    <t>升级该武器需要的资源</t>
-  </si>
-  <si>
-    <t>支持不做修改就能扩展，格式均为res_x。如res_2，res_3就表示第二种，第三种资源。资源为res表的id</t>
-  </si>
-  <si>
-    <t>cost_1</t>
-  </si>
-  <si>
-    <t>升到该等级需要的资源数量</t>
-  </si>
-  <si>
-    <t>支持不做修改就能扩展，格式均为cost_x。如cost_2，cost_3就表示第二种，第三种资源消耗量。与res_x一一对应</t>
-  </si>
-  <si>
-    <t>para1</t>
-  </si>
-  <si>
-    <t>武器的额外参数。具体每个武器再定义，一般可参考des</t>
-  </si>
-  <si>
     <t>mon</t>
   </si>
   <si>
-    <t>敌方飞行器id</t>
-  </si>
-  <si>
-    <t>飞行器描述</t>
-  </si>
-  <si>
-    <t>使用的武器，从equipment表中读出来，逻辑等都使用该武器表的</t>
-  </si>
-  <si>
-    <t>dmgMultiple</t>
-  </si>
-  <si>
-    <t>武器的伤害乘该值，这样计算完后的就是这个飞行器的伤害</t>
-  </si>
-  <si>
-    <t>health</t>
-  </si>
-  <si>
-    <t>飞行器生命</t>
-  </si>
-  <si>
-    <t>res</t>
-  </si>
-  <si>
-    <t>掉落的资源</t>
-  </si>
-  <si>
-    <t>格式为｛id，数量，概率｝，id为res表的id，数量就是掉出来的数量，概率是被击毁时有多大概率掉落该资源</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>大小</t>
-  </si>
-  <si>
-    <t>战场中占据的格子数</t>
-  </si>
-  <si>
     <t>敌方飞行器组id</t>
   </si>
   <si>
@@ -238,316 +52,1672 @@
     <t>格式为{id1，id2....｝</t>
   </si>
   <si>
-    <t>战场从上到下一共是10个格子，这里的id是mon表的id，1-10分别对应10个格子的位置</t>
-  </si>
-  <si>
-    <t>资源id</t>
-  </si>
-  <si>
-    <t>资源名</t>
-  </si>
-  <si>
-    <t>config</t>
-  </si>
-  <si>
-    <t>这个配置的名字</t>
-  </si>
-  <si>
-    <t>配置的描述</t>
-  </si>
-  <si>
-    <t>para_1</t>
-  </si>
-  <si>
-    <t>配置的参数</t>
-  </si>
-  <si>
-    <t>支持可扩展，会以para_1,para_2等方式不断扩张</t>
-  </si>
-  <si>
-    <t>hightech</t>
-  </si>
-  <si>
-    <t>这个高科技的名字</t>
-  </si>
-  <si>
-    <t>高科技的效果</t>
-  </si>
-  <si>
-    <t>timeCostBase</t>
-  </si>
-  <si>
-    <t>升级高科技需要的基础时间</t>
-  </si>
-  <si>
-    <t>timeCostMutiple</t>
-  </si>
-  <si>
-    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为1.2，则2级12秒，3级14秒...四舍五入取整</t>
-  </si>
-  <si>
-    <t>通过第几关后解锁</t>
-  </si>
-  <si>
-    <t>可变参数，可能有多个，具体效果参看高科技的效果des</t>
-  </si>
-  <si>
     <t>如上</t>
   </si>
   <si>
-    <t>{2|0.1，2|0.2，2|0.3，2|0.4，2|0.5，2|0.6，2|0.7，2|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{2|0.1，5|0.2，2|0.3，5|0.4，2|0.5，5|0.6，2|0.7，5|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，1|0.4，2|0.5，3|0.6，1|0.7，2|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{4|0.1，5|0.2，4|0.3，5|0.4，4|0.5，5|0.6，4|0.7，5|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，4|0.4，5|0.5，1|0.6，2|0.7，3|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{2|0.1，5|0.2，2|0.3，5|0.4，2|0.5，5|0.6，2|0.7，5|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，1|0.4，2|0.5，3|0.6，1|0.7，2|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{4|0.1，5|0.2，4|0.3，5|0.4，4|0.5，5|0.6，4|0.7，5|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，4|0.4，5|0.5，1|0.6，2|0.7，3|0.8，8|0.9}</t>
-  </si>
-  <si>
-    <t>dmgtype</t>
-  </si>
-  <si>
-    <t>res_2</t>
-  </si>
-  <si>
-    <t>cost_2</t>
-  </si>
-  <si>
-    <t>para2</t>
-  </si>
-  <si>
-    <t>para3</t>
-  </si>
-  <si>
-    <t>伤害类型，1为能量，2为物理。</t>
-  </si>
-  <si>
-    <t>对应level表id，通关对应id的关卡后解锁该武器。不填则这行无意义</t>
-  </si>
-  <si>
-    <t>armour</t>
-  </si>
-  <si>
-    <t>这个是飞船的基础生命，如果没了，飞船就会爆炸！然后后退。额外参数para1是生命值，dmgtype表明护甲对这个类型的伤害有减伤</t>
-  </si>
-  <si>
-    <t>shield</t>
-  </si>
-  <si>
-    <t>这个是飞船的基础护盾，护盾会先于护甲被扣除，同时护盾会缓慢恢复。额外参数para1是护盾值，para2是每秒恢复的比例，para3是连续多少秒不受攻击后才开始恢复，被攻击会立即停止恢复，dmgtype表明护盾对这个类型的伤害有减伤</t>
-  </si>
-  <si>
-    <t>laser</t>
-  </si>
-  <si>
-    <t>激光武器，发射一个光束攻击锁定目标，para1是飞行速度/S</t>
-  </si>
-  <si>
-    <t>missile</t>
-  </si>
-  <si>
-    <t>导弹武器，导弹会锁定多个敌人，锁定数量为para1定义。但敌人数量不足则只会发射敌人数量的导弹，不会多发。para2是导弹飞行速度</t>
-  </si>
-  <si>
-    <t>导弹武器，导弹会锁定多个敌人，锁定数量为para1定义。但敌人数量不足则只会发射敌人数量的导弹，不会多发</t>
-  </si>
-  <si>
-    <t>cannon</t>
-  </si>
-  <si>
-    <t>火炮武器，与激光一样，发射一个炮弹攻击锁定目标敌人，para1是飞行速度/S</t>
-  </si>
-  <si>
-    <t>laser_mon</t>
-  </si>
-  <si>
-    <t>missile-mon</t>
-  </si>
-  <si>
-    <t>cannon-mon</t>
-  </si>
-  <si>
-    <t>armourType</t>
-  </si>
-  <si>
-    <t>使用的武器，从equipment表中读出来，逻辑等都使用该武器表的,格式为｛name|数量，name|数量...}</t>
-  </si>
-  <si>
-    <t>护甲类型</t>
-  </si>
-  <si>
-    <t>1为能量，2为物理</t>
+    <t>战场从上到下一共是10个格子，这里的id是mon表的id，1-10分别对应10个格子的位置，null表示此处无飞船｝</t>
   </si>
   <si>
     <t>激光飞船</t>
   </si>
   <si>
-    <t>｛laser_mon|1｝</t>
-  </si>
-  <si>
-    <t>{1,10,0.5}</t>
+    <t>{null,null,null,1,1,1,null,null,null,null}</t>
   </si>
   <si>
     <t>火炮飞船</t>
   </si>
   <si>
-    <t>｛cannon-mon|1｝</t>
-  </si>
-  <si>
-    <t>激光飞船-弱</t>
-  </si>
-  <si>
-    <t>{1,5,0.2}</t>
-  </si>
-  <si>
-    <t>火炮飞船-弱</t>
-  </si>
-  <si>
-    <t>BOSS-抵抗物理</t>
-  </si>
-  <si>
-    <t>｛laser_mon|2,cannon-mon|2｝</t>
-  </si>
-  <si>
-    <t>{2,1,1}</t>
-  </si>
-  <si>
-    <t>BOSS-抵抗能量</t>
-  </si>
-  <si>
-    <t>战场从上到下一共是10个格子，这里的id是mon表的id，1-10分别对应10个格子的位置，null表示此处无飞船｝</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，1，1，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，2，2，null，null，null，null}</t>
+    <t>{null,null,null,2,2,2,null,null,null,null}</t>
   </si>
   <si>
     <t>基础飞船组</t>
   </si>
   <si>
-    <t>｛null，null，null，null，1，2，null，null，null，null}</t>
+    <t>{null,null,null,3,1,2,4,null,null,null}</t>
   </si>
   <si>
     <t>激光飞船-弱*6</t>
   </si>
   <si>
-    <t>｛null，null，3，3，3，3，3，3，null，null}</t>
+    <t>{null,null,3,3,3,3,3,3,null,null}</t>
   </si>
   <si>
     <t>火炮飞船-弱*6</t>
   </si>
   <si>
-    <t>｛null，null，4，4，4，4，4，4，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-抵抗物理</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，5，null，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-抵抗能量</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，6，null，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-双BOSS</t>
-  </si>
-  <si>
-    <t>｛null，null，null，5，null，null，6，null，null，null}</t>
-  </si>
-  <si>
-    <t>铁</t>
-  </si>
-  <si>
-    <t>铝</t>
-  </si>
-  <si>
-    <t>startEquip</t>
-  </si>
-  <si>
-    <t>飞船初始具有的装备，格式为name,name，equipment表的名字。默认为1级。</t>
-  </si>
-  <si>
-    <t>armour,laser</t>
-  </si>
-  <si>
-    <t>dmgReduce</t>
-  </si>
-  <si>
-    <t>护甲类型对应时，减少的伤害</t>
-  </si>
-  <si>
-    <t>movement</t>
-  </si>
-  <si>
-    <t>飞船的移动速度，单位是秒</t>
-  </si>
-  <si>
-    <t>autoCollectReduce</t>
-  </si>
-  <si>
-    <t>自动拾取时的损耗</t>
-  </si>
-  <si>
-    <t>backRange</t>
-  </si>
-  <si>
-    <t>死亡时后退距离</t>
-  </si>
-  <si>
-    <t>hightechLimit</t>
-  </si>
-  <si>
-    <t>同时研发的高科技数量</t>
-  </si>
-  <si>
-    <t>这个神器的名字</t>
-  </si>
-  <si>
-    <t>神器的效果</t>
-  </si>
-  <si>
-    <t>升级神器需要的基础时间</t>
-  </si>
-  <si>
-    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为0.2，则2级12秒，3级14秒...四舍五入取整</t>
-  </si>
-  <si>
-    <t>可变参数，具体效果参看神器的效果des</t>
-  </si>
-  <si>
-    <t>反物质炼铁炉</t>
-  </si>
-  <si>
-    <t>每para1秒在屏幕中生成一个铁块，总共含有根据过去一分钟的铁生成量*para2*等级的铁，点击获取，10秒后消失</t>
-  </si>
-  <si>
-    <t>正电子聚焦装置</t>
-  </si>
-  <si>
-    <t>提高所有能量武器的伤害，效果为原伤害*（1+para1*等级）.</t>
+    <t>{null,null,4,4,4,4,4,4,null,null}</t>
+  </si>
+  <si>
+    <t>中型飞船-抵抗物理</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,5,null,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>中型飞船-抵抗能量</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,6,null,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>中型飞船-混合</t>
+  </si>
+  <si>
+    <t>{null,null,null,5,null,null,6,null,null,null}</t>
+  </si>
+  <si>
+    <t>中型飞船-双抵抗物理</t>
+  </si>
+  <si>
+    <t>{null,null,null,5,null,5,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>中型飞船-双抵抗能量</t>
+  </si>
+  <si>
+    <t>{null,null,null,6,null,6,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>激光飞船-弱*4+强2</t>
+  </si>
+  <si>
+    <t>{null,null,3,3,1,1,3,3,null,null}</t>
+  </si>
+  <si>
+    <t>火炮飞船-弱*4+强2</t>
+  </si>
+  <si>
+    <t>{null,null,4,4,2,2,4,4,null,null}</t>
+  </si>
+  <si>
+    <t>大型飞船-抵抗物理</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,8,null,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>大型飞船-抵抗能量</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,7,null,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>大型飞船-混合</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,7,8,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×7</t>
+  </si>
+  <si>
+    <t>{4,null,4,4,null,4,4,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-深渊级战争旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,12,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,null,null,6,null,null,4,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×3、裂星级突击舰×2</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,1,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,null,null,5,null,null,6,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×8</t>
+  </si>
+  <si>
+    <t>{3,3,null,3,3,3,3,null,3,3}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×6</t>
+  </si>
+  <si>
+    <t>{2,null,2,null,2,2,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×5</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,1,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×6</t>
+  </si>
+  <si>
+    <t>{4,null,4,null,4,4,null,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×1、猎隼级轻炮艇×3</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,null,4,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、猎隼级轻炮艇×8</t>
+  </si>
+  <si>
+    <t>{4,4,4,4,4,4,4,4,3,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、猎隼级轻炮艇×4</t>
+  </si>
+  <si>
+    <t>{4,null,4,null,4,4,null,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×10</t>
+  </si>
+  <si>
+    <t>{3,3,3,3,3,3,3,3,3,3}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×6、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{2,null,2,2,null,6,2,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×4</t>
+  </si>
+  <si>
+    <t>{null,5,null,5,null,null,5,null,5,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×3</t>
+  </si>
+  <si>
+    <t>{null,4,null,null,null,4,null,null,4,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×6</t>
+  </si>
+  <si>
+    <t>{1,null,1,null,1,1,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、猎隼级轻炮艇×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,5,null,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×8</t>
+  </si>
+  <si>
+    <t>{4,4,null,4,4,4,4,null,4,4}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×4、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,5,null,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2</t>
+  </si>
+  <si>
+    <t>{null,null,2,null,null,null,null,2,null,null}</t>
+  </si>
+  <si>
+    <t>混合-圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,7,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×2、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,null,null,7,null,null,4,null}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×2</t>
+  </si>
+  <si>
+    <t>{null,null,5,null,null,null,null,5,null,null}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,null,null,7,null,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×4、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,8,null,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×1、猎隼级轻炮艇×5</t>
+  </si>
+  <si>
+    <t>{4,null,4,null,4,4,null,4,null,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,null,3,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×2</t>
+  </si>
+  <si>
+    <t>{null,null,4,null,null,null,null,4,null,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×4、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,10,null,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×4</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,null,4,null,4,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2</t>
+  </si>
+  <si>
+    <t>{null,null,1,null,null,null,null,1,null,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×2、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,null,null,10,null,null,4,null}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×2</t>
+  </si>
+  <si>
+    <t>{null,null,6,null,null,null,null,6,null,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,null,null,6,null,null,1,null}</t>
+  </si>
+  <si>
+    <t>混合-钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,8,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,9,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×3、裂星级突击舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,null,1,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,5,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×5</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,2,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×5、裂星级突击舰×1</t>
+  </si>
+  <si>
+    <t>{1,null,1,null,1,1,null,1,null,2}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,6,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×7</t>
+  </si>
+  <si>
+    <t>{3,null,3,3,null,3,3,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×8、猎隼级轻炮艇×1</t>
+  </si>
+  <si>
+    <t>{3,3,3,3,null,3,3,3,3,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×6、猎隼级轻炮艇×1</t>
+  </si>
+  <si>
+    <t>{3,null,3,3,null,3,3,3,null,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×5、猎隼级轻炮艇×3</t>
+  </si>
+  <si>
+    <t>{3,3,null,3,3,4,3,null,4,4}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、裂星级突击舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,null,null,1,null,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×5</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,4,null,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,null,null,5,null,null,4,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,null,null,10,null,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×3、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,5,null,null,5,null,6,null}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,2,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×5</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,3,null,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×3</t>
+  </si>
+  <si>
+    <t>{null,2,null,null,null,2,null,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×1、猎隼级轻炮艇×2</t>
+  </si>
+  <si>
+    <t>{null,4,null,null,null,4,null,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×2、深渊级战争旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,null,null,12,null,null,4,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、猎隼级轻炮艇×7</t>
+  </si>
+  <si>
+    <t>{4,4,4,4,null,4,4,4,3,3}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×10</t>
+  </si>
+  <si>
+    <t>{4,4,4,4,4,4,4,4,4,4}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,null,null,10,null,null,1,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×3</t>
+  </si>
+  <si>
+    <t>{null,1,null,null,null,1,null,null,1,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×7、猎隼级轻炮艇×2</t>
+  </si>
+  <si>
+    <t>{3,3,3,3,null,3,3,3,4,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,null,null,5,null,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×3、猎隼级轻炮艇×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,null,4,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,null,null,6,null,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×6、猎隼级轻炮艇×2</t>
+  </si>
+  <si>
+    <t>{3,3,null,3,3,3,3,null,4,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,null,null,8,null,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×6、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{3,null,3,3,null,6,3,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×1、裂星级突击舰×3</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,null,1,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×3、裂星级突击舰×5</t>
+  </si>
+  <si>
+    <t>{2,2,null,2,2,1,1,null,2,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4、猎隼级轻炮艇×6</t>
+  </si>
+  <si>
+    <t>{4,4,4,4,4,4,3,3,3,3}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,null,null,7,null,null,1,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×1、裂星级突击舰×7</t>
+  </si>
+  <si>
+    <t>{2,2,null,2,2,2,2,null,2,1}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×1、辉盾级能防舰×2</t>
+  </si>
+  <si>
+    <t>{null,6,null,null,null,6,null,null,5,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×3、猎隼级轻炮艇×5</t>
+  </si>
+  <si>
+    <t>{4,4,null,4,4,3,4,null,3,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×3</t>
+  </si>
+  <si>
+    <t>{null,3,null,null,null,3,null,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,3,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、裂星级突击舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,1,null,2,null,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4、猎隼级轻炮艇×2</t>
+  </si>
+  <si>
+    <t>{3,null,3,null,3,3,null,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、猎隼级轻炮艇×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{1,null,1,1,null,6,1,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×4、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,8,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,10,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×6、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{4,null,4,4,null,6,4,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×9</t>
+  </si>
+  <si>
+    <t>{4,4,4,4,null,4,4,4,4,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×6、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{3,null,3,3,null,5,3,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×4</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,null,2,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×4、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,5,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2</t>
+  </si>
+  <si>
+    <t>{null,null,3,null,null,null,null,3,null,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×6、裂星级突击舰×1</t>
+  </si>
+  <si>
+    <t>{1,null,1,1,null,1,2,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,null,null,7,null,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×4、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,6,null,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×3</t>
+  </si>
+  <si>
+    <t>{null,6,null,null,null,6,null,null,6,null}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×2、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,6,null,null,null,8,null,null,6,null}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×7</t>
+  </si>
+  <si>
+    <t>{2,null,2,2,null,2,2,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、裂星级突击舰×4</t>
+  </si>
+  <si>
+    <t>{2,null,2,null,2,2,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、猎隼级轻炮艇×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,5,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×3、猎隼级轻炮艇×2</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,3,null,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、猎隼级轻炮艇×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,6,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,null,null,5,null,null,1,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,null,1,null,1,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、猎隼级轻炮艇×6</t>
+  </si>
+  <si>
+    <t>{4,4,null,4,4,4,4,null,3,3}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×4、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,7,null,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×1、猎隼级轻炮艇×6</t>
+  </si>
+  <si>
+    <t>{4,null,4,4,null,4,4,4,null,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、猎隼级轻炮艇×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,null,null,3,null,null,4,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×8、猎隼级轻炮艇×2</t>
+  </si>
+  <si>
+    <t>{3,3,3,3,3,3,3,3,4,4}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,4,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,1,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,10,null,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、猎隼级轻炮艇×3</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,4,null,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、裂星级突击舰×2</t>
+  </si>
+  <si>
+    <t>{1,null,1,null,1,1,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×9</t>
+  </si>
+  <si>
+    <t>{3,3,3,3,null,3,3,3,3,3}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,6,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、深渊级战争旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,null,null,12,null,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,7,null,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、裂星级突击舰×6</t>
+  </si>
+  <si>
+    <t>{2,2,null,2,2,2,2,null,1,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,5,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×1、猎隼级轻炮艇×9</t>
+  </si>
+  <si>
+    <t>{4,4,4,4,4,4,4,4,4,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×6</t>
+  </si>
+  <si>
+    <t>{3,null,3,null,3,3,null,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,null,null,9,null,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、微光级侦察艇×4、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{3,null,3,3,null,6,3,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,null,null,8,null,null,1,null}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×4、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,6,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4、猎隼级轻炮艇×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,3,null,3,null,4}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、裂星级突击舰×3</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,2,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×5、猎隼级轻炮艇×2</t>
+  </si>
+  <si>
+    <t>{3,null,3,3,null,3,4,3,null,4}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×1、裂星级突击舰×4</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,2,null,2,null,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×1、裂星级突击舰×5</t>
+  </si>
+  <si>
+    <t>{2,null,2,null,2,2,null,2,null,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、裂星级突击舰×5</t>
+  </si>
+  <si>
+    <t>{2,null,2,2,null,2,2,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×1、猎隼级轻炮艇×4</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,4,null,4,null,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、猎隼级轻炮艇×5</t>
+  </si>
+  <si>
+    <t>{4,null,4,4,null,4,3,4,null,3}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×2、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,null,null,8,null,null,5,null}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×3</t>
+  </si>
+  <si>
+    <t>{null,5,null,null,null,5,null,null,5,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,9,null,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,null,null,8,null,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×7、猎隼级轻炮艇×3</t>
+  </si>
+  <si>
+    <t>{3,3,3,3,3,3,3,4,4,4}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、裂星级突击舰×4、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{2,null,2,2,null,6,2,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×5、裂星级突击舰×3</t>
+  </si>
+  <si>
+    <t>{1,1,null,1,1,1,2,null,2,2}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×2、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,null,null,8,null,null,4,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×1、猎隼级轻炮艇×8</t>
+  </si>
+  <si>
+    <t>{4,4,4,4,null,4,4,4,4,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×3、猎隼级轻炮艇×7</t>
+  </si>
+  <si>
+    <t>{4,4,4,4,4,4,3,4,3,3}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,null,null,10,null,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×6、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{4,null,4,4,null,5,4,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×5、猎隼级轻炮艇×1</t>
+  </si>
+  <si>
+    <t>{3,null,3,null,3,3,null,3,null,4}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×1、裂星级突击舰×6</t>
+  </si>
+  <si>
+    <t>{2,null,2,2,null,2,2,2,null,1}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、微光级侦察艇×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,6,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×5、裂星级突击舰×2</t>
+  </si>
+  <si>
+    <t>{1,null,1,1,null,1,1,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、裂星级突击舰×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,5,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、猎隼级轻炮艇×4、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{4,null,4,4,null,6,4,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×7、猎隼级轻炮艇×1</t>
+  </si>
+  <si>
+    <t>{3,3,null,3,3,3,3,null,3,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,5,null,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×4、微光级侦察艇×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{2,null,2,2,null,5,2,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,8,null,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,8,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、猎隼级轻炮艇×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,6,null,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,null,null,6,null,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,6,null,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×9、猎隼级轻炮艇×1</t>
+  </si>
+  <si>
+    <t>{3,3,3,3,3,3,3,3,3,4}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,null,null,5,null,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×6、猎隼级轻炮艇×3</t>
+  </si>
+  <si>
+    <t>{3,3,3,3,null,3,3,4,4,4}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×1、猎隼级轻炮艇×7</t>
+  </si>
+  <si>
+    <t>{4,4,null,4,4,4,4,null,4,3}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×2、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,null,null,9,null,null,4,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×1、裂星级突击舰×2</t>
+  </si>
+  <si>
+    <t>{null,2,null,null,null,2,null,null,1,null}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、微光级侦察艇×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,3,null,5,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×3、猎隼级轻炮艇×6</t>
+  </si>
+  <si>
+    <t>{4,4,4,4,null,4,3,4,3,3}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4、猎隼级轻炮艇×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{3,null,3,3,null,6,3,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、裂星级突击舰×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,6,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×6、猎隼级轻炮艇×4</t>
+  </si>
+  <si>
+    <t>{3,3,3,3,3,3,4,4,4,4}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、微光级侦察艇×4、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{3,null,3,3,null,5,3,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、猎隼级轻炮艇×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{1,null,1,1,null,5,1,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×4、微光级侦察艇×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{2,null,2,2,null,6,2,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、裂星级突击舰×4、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{2,null,2,2,null,5,1,2,null,1}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、猎隼级轻炮艇×4、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{4,null,4,4,null,5,4,3,null,3}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、裂星级突击舰×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{1,null,1,1,null,5,1,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×4、猎隼级轻炮艇×2、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{3,null,3,3,null,5,3,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、猎隼级轻炮艇×4、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{4,null,4,4,null,5,4,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×4</t>
+  </si>
+  <si>
+    <t>{null,6,null,6,null,null,6,null,6,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×8</t>
+  </si>
+  <si>
+    <t>{1,1,null,1,1,1,1,null,1,1}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×1、辉盾级能防舰×3</t>
+  </si>
+  <si>
+    <t>{null,6,null,6,null,null,6,null,5,null}</t>
+  </si>
+  <si>
+    <t>混合-太阳神级旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,null,null,null,null,11,null,null,null,null}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×6、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{2,null,2,2,null,5,2,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,null,null,9,null,null,1,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×7</t>
+  </si>
+  <si>
+    <t>{1,null,1,1,null,1,1,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×2、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,6,null,null,null,7,null,null,6,null}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×3、辉盾级能防舰×2</t>
+  </si>
+  <si>
+    <t>{null,5,null,5,null,5,null,6,null,6}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,null,null,9,null,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,7,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×2、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,null,null,7,null,null,5,null}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×4、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,4,null,9,null,4,null,4}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×8</t>
+  </si>
+  <si>
+    <t>{2,2,null,2,2,2,2,null,2,2}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×4、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,7,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×6、裂星级突击舰×2</t>
+  </si>
+  <si>
+    <t>{1,1,null,1,1,1,1,null,2,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×6、裂星级突击舰×3</t>
+  </si>
+  <si>
+    <t>{1,1,1,1,null,1,1,2,2,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×6、玄武级装甲舰×1</t>
+  </si>
+  <si>
+    <t>{1,null,1,1,null,5,1,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×1、裂星级突击舰×8</t>
+  </si>
+  <si>
+    <t>{2,2,2,2,null,2,2,2,1,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、裂星级突击舰×2、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{1,null,1,1,null,6,1,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×4、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,5,null,5,null,5,null,6}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×3、裂星级突击舰×6</t>
+  </si>
+  <si>
+    <t>{2,2,2,2,null,2,2,1,1,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×7、裂星级突击舰×1</t>
+  </si>
+  <si>
+    <t>{1,1,null,1,1,1,1,null,1,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×6、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{1,null,1,1,null,6,1,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×7、裂星级突击舰×2</t>
+  </si>
+  <si>
+    <t>{1,1,1,1,null,1,1,1,2,2}</t>
+  </si>
+  <si>
+    <t>混合-微光级侦察艇×2、太阳神级旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,3,null,null,null,11,null,null,3,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、裂星级突击舰×7</t>
+  </si>
+  <si>
+    <t>{2,2,2,2,null,2,2,2,1,1}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×2、辉盾级能防舰×3</t>
+  </si>
+  <si>
+    <t>{null,6,null,6,null,6,null,5,null,5}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×9</t>
+  </si>
+  <si>
+    <t>{2,2,2,2,null,2,2,2,2,2}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、太阳神级旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,null,null,11,null,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×2、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,6,null,null,null,10,null,null,6,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×9、裂星级突击舰×1</t>
+  </si>
+  <si>
+    <t>{1,1,1,1,1,1,1,1,2,1}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×4、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,10,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×9</t>
+  </si>
+  <si>
+    <t>{1,1,1,1,null,1,1,1,1,1}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×1、辉盾级能防舰×4</t>
+  </si>
+  <si>
+    <t>{null,6,null,6,null,6,null,6,null,5}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×2、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,null,null,10,null,null,5,null}</t>
+  </si>
+  <si>
+    <t>能量-裂星级突击舰×10</t>
+  </si>
+  <si>
+    <t>{2,2,2,2,2,2,2,2,2,2}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×5</t>
+  </si>
+  <si>
+    <t>{null,5,null,5,null,5,null,5,null,5}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×2、深渊级战争旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,null,null,12,null,null,2,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×10</t>
+  </si>
+  <si>
+    <t>{1,1,1,1,1,1,1,1,1,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、太阳神级旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,null,null,11,null,null,1,null}</t>
+  </si>
+  <si>
+    <t>能量-曙光级截击舰×1、裂星级突击舰×9</t>
+  </si>
+  <si>
+    <t>{2,2,2,2,2,2,2,2,2,1}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×2、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,6,null,null,null,9,null,null,6,null}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×5、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{5,null,5,null,5,5,null,5,null,6}</t>
+  </si>
+  <si>
+    <t>混合-猎隼级轻炮艇×2、太阳神级旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,4,null,null,null,11,null,null,4,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、裂星级突击舰×6</t>
+  </si>
+  <si>
+    <t>{2,2,2,2,2,1,2,1,1,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、深渊级战争旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,null,null,12,null,null,1,null}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×3、裂星级突击舰×7</t>
+  </si>
+  <si>
+    <t>{2,2,2,2,2,2,2,1,1,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,9,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>物理-曙光级截击舰×8、裂星级突击舰×2</t>
+  </si>
+  <si>
+    <t>{1,1,1,1,1,1,1,1,2,2}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×2、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,null,null,9,null,null,5,null}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×5</t>
+  </si>
+  <si>
+    <t>{null,6,null,6,null,6,null,6,null,6}</t>
+  </si>
+  <si>
+    <t>物理-曙光级截击舰×7、裂星级突击舰×3</t>
+  </si>
+  <si>
+    <t>{1,1,1,1,1,2,1,1,2,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×4、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,1,null,1,null,10,null,1,null,1}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×8、裂星级突击舰×1</t>
+  </si>
+  <si>
+    <t>{1,1,1,1,null,1,1,1,1,2}</t>
+  </si>
+  <si>
+    <t>混合-曙光级截击舰×2、裂星级突击舰×8</t>
+  </si>
+  <si>
+    <t>{2,2,2,2,2,2,2,2,1,1}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×1、辉盾级能防舰×5</t>
+  </si>
+  <si>
+    <t>{6,null,6,null,6,6,null,6,null,5}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×6、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{5,null,5,5,null,5,5,5,null,6}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×2、辉盾级能防舰×4</t>
+  </si>
+  <si>
+    <t>{6,null,6,null,6,6,null,5,null,5}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×5、辉盾级能防舰×2</t>
+  </si>
+  <si>
+    <t>{5,null,5,5,null,5,6,5,null,6}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×4、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,5,null,7,null,5,null,5}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×6</t>
+  </si>
+  <si>
+    <t>{6,null,6,null,6,6,null,6,null,6}</t>
+  </si>
+  <si>
+    <t>混合-裂星级突击舰×4、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,2,null,2,null,9,null,2,null,2}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×4、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,6,null,6,null,10,null,6,null,6}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×4、辉盾级能防舰×2</t>
+  </si>
+  <si>
+    <t>{5,null,5,null,5,5,null,6,null,6}</t>
+  </si>
+  <si>
+    <t>物理-玄武级装甲舰×2、太阳神级旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,null,null,11,null,null,5,null}</t>
+  </si>
+  <si>
+    <t>能量-玄武级装甲舰×6</t>
+  </si>
+  <si>
+    <t>{5,null,5,null,5,5,null,5,null,5}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×4、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,6,null,6,null,8,null,6,null,6}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×2、深渊级战争旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,6,null,null,null,12,null,null,6,null}</t>
+  </si>
+  <si>
+    <t>混合-辉盾级能防舰×4、圣辉级巡洋舰×1</t>
+  </si>
+  <si>
+    <t>{null,6,null,6,null,7,null,6,null,6}</t>
+  </si>
+  <si>
+    <t>物理-辉盾级能防舰×2、太阳神级旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,6,null,null,null,11,null,null,6,null}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×2、深渊级战争旗舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,null,null,12,null,null,5,null}</t>
+  </si>
+  <si>
+    <t>能量-玄武级装甲舰×4、钢铁级重巡舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,5,null,8,null,5,null,5}</t>
+  </si>
+  <si>
+    <t>物理-玄武级装甲舰×1、辉盾级能防舰×6</t>
+  </si>
+  <si>
+    <t>{6,null,6,6,null,6,6,6,null,5}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×4、泰坦级攻城舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,5,null,10,null,5,null,5}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×2、辉盾级能防舰×5</t>
+  </si>
+  <si>
+    <t>{6,null,6,6,null,6,6,5,null,5}</t>
+  </si>
+  <si>
+    <t>物理-辉盾级能防舰×4、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,6,null,6,null,9,null,6,null,6}</t>
+  </si>
+  <si>
+    <t>物理-辉盾级能防舰×7</t>
+  </si>
+  <si>
+    <t>{6,null,6,6,null,6,6,6,null,6}</t>
+  </si>
+  <si>
+    <t>混合-玄武级装甲舰×4、天穹级歼星舰×1</t>
+  </si>
+  <si>
+    <t>{null,5,null,5,null,9,null,5,null,5}</t>
+  </si>
+  <si>
+    <t>能量-玄武级装甲舰×7、辉盾级能防舰×1</t>
+  </si>
+  <si>
+    <t>{5,5,null,5,5,5,5,null,5,6}</t>
+  </si>
+  <si>
+    <t>能量-玄武级装甲舰×7</t>
+  </si>
+  <si>
+    <t>{5,null,5,5,null,5,5,5,null,5}</t>
+  </si>
+  <si>
+    <t>能量-玄武级装甲舰×6、辉盾级能防舰×2</t>
+  </si>
+  <si>
+    <t>{5,5,null,5,5,6,5,null,5,6}</t>
+  </si>
+  <si>
+    <t>物理-玄武级装甲舰×5、辉盾级能防舰×3</t>
+  </si>
+  <si>
+    <t>{5,5,null,5,5,5,6,null,6,6}</t>
+  </si>
+  <si>
+    <t>物理-玄武级装甲舰×3、辉盾级能防舰×5</t>
+  </si>
+  <si>
+    <t>{6,6,null,6,6,6,5,null,5,5}</t>
+  </si>
+  <si>
+    <t>能量-玄武级装甲舰×8</t>
+  </si>
+  <si>
+    <t>{5,5,null,5,5,5,5,null,5,5}</t>
+  </si>
+  <si>
+    <t>物理-辉盾级能防舰×8</t>
+  </si>
+  <si>
+    <t>{6,6,null,6,6,6,6,null,6,6}</t>
+  </si>
+  <si>
+    <t>物理-玄武级装甲舰×1、辉盾级能防舰×7</t>
+  </si>
+  <si>
+    <t>{6,6,null,6,6,6,6,null,6,5}</t>
+  </si>
+  <si>
+    <t>物理-玄武级装甲舰×2、辉盾级能防舰×6</t>
+  </si>
+  <si>
+    <t>{6,6,null,6,6,6,6,null,5,5}</t>
   </si>
 </sst>
 </file>
@@ -560,13 +1730,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF1F2937"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1033,16 +2209,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -1051,130 +2224,130 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1484,272 +2657,3094 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C280"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="50.7777777777778" customWidth="1"/>
     <col min="3" max="3" width="62.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">激光飞船</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,null,1,1,1,null,null,null,null}</t>
-        </is>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火炮飞船</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,null,2,2,2,null,null,null,null}</t>
-        </is>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">基础飞船组</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,null,3,1,2,4,null,null,null}</t>
-        </is>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">激光飞船-弱*6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,3,3,3,3,3,3,null,null}</t>
-        </is>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火炮飞船-弱*6</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,4,4,4,4,4,4,null,null}</t>
-        </is>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中型飞船-抵抗物理</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,null,null,5,null,null,null,null,null}</t>
-        </is>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中型飞船-抵抗能量</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,null,null,6,null,null,null,null,null}</t>
-        </is>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中型飞船-混合</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,null,5,null,null,6,null,null,null}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中型飞船-双抵抗物理</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,null,5,null,5,null,null,null,null}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中型飞船-双抵抗能量</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,null,6,null,6,null,null,null,null}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">激光飞船-弱*4+强2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,3,3,1,1,3,3,null,null}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火炮飞船-弱*4+强2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,4,4,2,2,4,4,null,null}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">大型飞船-抵抗物理</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,null,null,8,null,null,null,null,null}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">大型飞船-抵抗能量</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,null,null,7,null,null,null,null,null}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">大型飞船-混合</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{null,null,null,null,7,8,null,null,null,null}</t>
-        </is>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A19" s="1">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A20" s="1">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A21" s="1">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A22" s="1">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A23" s="1">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A24" s="1">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A25" s="1">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A26" s="1">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A27" s="1">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A28" s="1">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A29" s="1">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A30" s="1">
+        <v>27</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A31" s="1">
+        <v>28</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A32" s="1">
+        <v>29</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A33" s="1">
+        <v>30</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A34" s="1">
+        <v>31</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A35" s="1">
+        <v>32</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A36" s="1">
+        <v>33</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A37" s="1">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A38" s="1">
+        <v>35</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A39" s="1">
+        <v>36</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A40" s="1">
+        <v>37</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A41" s="1">
+        <v>38</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A42" s="1">
+        <v>39</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A43" s="1">
+        <v>40</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A44" s="1">
+        <v>41</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A45" s="1">
+        <v>42</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A46" s="1">
+        <v>43</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A47" s="1">
+        <v>44</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A48" s="1">
+        <v>45</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A49" s="1">
+        <v>46</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A50" s="1">
+        <v>47</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A51" s="1">
+        <v>48</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A52" s="1">
+        <v>49</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A53" s="1">
+        <v>50</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A54" s="1">
+        <v>51</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A55" s="1">
+        <v>52</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A56" s="1">
+        <v>53</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A57" s="1">
+        <v>54</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A58" s="1">
+        <v>55</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A59" s="1">
+        <v>56</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A60" s="1">
+        <v>57</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A61" s="1">
+        <v>58</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A62" s="1">
+        <v>59</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A63" s="1">
+        <v>60</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A64" s="1">
+        <v>61</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A65" s="1">
+        <v>62</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A66" s="1">
+        <v>63</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A67" s="1">
+        <v>64</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A68" s="1">
+        <v>65</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A69" s="1">
+        <v>66</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A70" s="1">
+        <v>67</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A71" s="1">
+        <v>68</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A72" s="1">
+        <v>69</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A73" s="1">
+        <v>70</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A74" s="1">
+        <v>71</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A75" s="1">
+        <v>72</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A76" s="1">
+        <v>73</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A77" s="1">
+        <v>74</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="78" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A78" s="1">
+        <v>75</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A79" s="1">
+        <v>76</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A80" s="1">
+        <v>77</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A81" s="1">
+        <v>78</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A82" s="1">
+        <v>79</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A83" s="1">
+        <v>80</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A84" s="1">
+        <v>81</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A85" s="1">
+        <v>82</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="86" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A86" s="1">
+        <v>83</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="87" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A87" s="1">
+        <v>84</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="88" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A88" s="1">
+        <v>85</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="89" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A89" s="1">
+        <v>86</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="90" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A90" s="1">
+        <v>87</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A91" s="1">
+        <v>88</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A92" s="1">
+        <v>89</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A93" s="1">
+        <v>90</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A94" s="1">
+        <v>91</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="95" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A95" s="1">
+        <v>92</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="96" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A96" s="1">
+        <v>93</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="97" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A97" s="1">
+        <v>94</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="98" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A98" s="1">
+        <v>95</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="99" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A99" s="1">
+        <v>96</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A100" s="1">
+        <v>97</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A101" s="1">
+        <v>98</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A102" s="1">
+        <v>99</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A103" s="1">
+        <v>100</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A104" s="1">
+        <v>101</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A105" s="1">
+        <v>102</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="106" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A106" s="1">
+        <v>103</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="107" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A107" s="1">
+        <v>104</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A108" s="1">
+        <v>105</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="109" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A109" s="1">
+        <v>106</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="110" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A110" s="1">
+        <v>107</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="111" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A111" s="1">
+        <v>108</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="112" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A112" s="1">
+        <v>109</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="113" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A113" s="1">
+        <v>110</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="114" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A114" s="1">
+        <v>111</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="115" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A115" s="1">
+        <v>112</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="116" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A116" s="1">
+        <v>113</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="117" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A117" s="1">
+        <v>114</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="118" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A118" s="1">
+        <v>115</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="119" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A119" s="1">
+        <v>116</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="120" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A120" s="1">
+        <v>117</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="121" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A121" s="1">
+        <v>118</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="122" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A122" s="1">
+        <v>119</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="123" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A123" s="1">
+        <v>120</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="124" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A124" s="1">
+        <v>121</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="125" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A125" s="1">
+        <v>122</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="126" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A126" s="1">
+        <v>123</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="127" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A127" s="1">
+        <v>124</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="128" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A128" s="1">
+        <v>125</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="129" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A129" s="1">
+        <v>126</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="130" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A130" s="1">
+        <v>127</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="131" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A131" s="1">
+        <v>128</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="132" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A132" s="1">
+        <v>129</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="133" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A133" s="1">
+        <v>130</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="134" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A134" s="1">
+        <v>131</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="135" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A135" s="1">
+        <v>132</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="136" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A136" s="1">
+        <v>133</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="137" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A137" s="1">
+        <v>134</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="138" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A138" s="1">
+        <v>135</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="139" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A139" s="1">
+        <v>136</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="140" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A140" s="1">
+        <v>137</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="141" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A141" s="1">
+        <v>138</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="142" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A142" s="1">
+        <v>139</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="143" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A143" s="1">
+        <v>140</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="144" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A144" s="1">
+        <v>141</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="145" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A145" s="1">
+        <v>142</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="146" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A146" s="1">
+        <v>143</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="147" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A147" s="1">
+        <v>144</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="148" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A148" s="1">
+        <v>145</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="149" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A149" s="1">
+        <v>146</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="150" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A150" s="1">
+        <v>147</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="151" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A151" s="1">
+        <v>148</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="152" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A152" s="1">
+        <v>149</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="153" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A153" s="1">
+        <v>150</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="154" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A154" s="1">
+        <v>151</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="155" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A155" s="1">
+        <v>152</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="156" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A156" s="1">
+        <v>153</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="157" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A157" s="1">
+        <v>154</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="158" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A158" s="1">
+        <v>155</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="159" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A159" s="1">
+        <v>156</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="160" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A160" s="1">
+        <v>157</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="161" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A161" s="1">
+        <v>158</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="162" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A162" s="1">
+        <v>159</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="163" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A163" s="1">
+        <v>160</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="164" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A164" s="1">
+        <v>161</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="165" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A165" s="1">
+        <v>162</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="166" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A166" s="1">
+        <v>163</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="167" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A167" s="1">
+        <v>164</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="168" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A168" s="1">
+        <v>165</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="169" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A169" s="1">
+        <v>166</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="170" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A170" s="1">
+        <v>167</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="171" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A171" s="1">
+        <v>168</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="172" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A172" s="1">
+        <v>169</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="173" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A173" s="1">
+        <v>170</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="174" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A174" s="1">
+        <v>171</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="175" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A175" s="1">
+        <v>172</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="176" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A176" s="1">
+        <v>173</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="177" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A177" s="1">
+        <v>174</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="178" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A178" s="1">
+        <v>175</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="179" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A179" s="1">
+        <v>176</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="180" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A180" s="1">
+        <v>177</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="181" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A181" s="1">
+        <v>178</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="182" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A182" s="1">
+        <v>179</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="183" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A183" s="1">
+        <v>180</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="184" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A184" s="1">
+        <v>181</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="185" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A185" s="1">
+        <v>182</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="186" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A186" s="1">
+        <v>183</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="187" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A187" s="1">
+        <v>184</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="188" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A188" s="1">
+        <v>185</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="189" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A189" s="1">
+        <v>186</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="190" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A190" s="1">
+        <v>187</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="191" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A191" s="1">
+        <v>188</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="192" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A192" s="1">
+        <v>189</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="193" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A193" s="1">
+        <v>190</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="194" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A194" s="1">
+        <v>191</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="195" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A195" s="1">
+        <v>192</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="196" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A196" s="1">
+        <v>193</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="197" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A197" s="1">
+        <v>194</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="198" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A198" s="1">
+        <v>195</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="199" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A199" s="1">
+        <v>196</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="200" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A200" s="1">
+        <v>197</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="201" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A201" s="1">
+        <v>198</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="202" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A202" s="1">
+        <v>199</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="203" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A203" s="1">
+        <v>200</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="204" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A204" s="1">
+        <v>201</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="205" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A205" s="1">
+        <v>202</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="206" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A206" s="1">
+        <v>203</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="207" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A207" s="1">
+        <v>204</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="208" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A208" s="1">
+        <v>205</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="209" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A209" s="1">
+        <v>206</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="210" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A210" s="1">
+        <v>207</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="211" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A211" s="1">
+        <v>208</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A212" s="1">
+        <v>209</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="213" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A213" s="1">
+        <v>210</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="214" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A214" s="1">
+        <v>211</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="215" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A215" s="1">
+        <v>212</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="216" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A216" s="1">
+        <v>213</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="217" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A217" s="1">
+        <v>214</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="218" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A218" s="1">
+        <v>215</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="219" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A219" s="1">
+        <v>216</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="220" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A220" s="1">
+        <v>217</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="221" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A221" s="1">
+        <v>218</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="222" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A222" s="1">
+        <v>219</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="223" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A223" s="1">
+        <v>220</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="224" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A224" s="1">
+        <v>221</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="225" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A225" s="1">
+        <v>222</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="226" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A226" s="1">
+        <v>223</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="227" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A227" s="1">
+        <v>224</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="228" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A228" s="1">
+        <v>225</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="229" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A229" s="1">
+        <v>226</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="230" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A230" s="1">
+        <v>227</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="231" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A231" s="1">
+        <v>228</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="232" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A232" s="1">
+        <v>229</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="233" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A233" s="1">
+        <v>230</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="234" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A234" s="1">
+        <v>231</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="235" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A235" s="1">
+        <v>232</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="236" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A236" s="1">
+        <v>233</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="237" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A237" s="1">
+        <v>234</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="238" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A238" s="1">
+        <v>235</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="239" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A239" s="1">
+        <v>236</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="240" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A240" s="1">
+        <v>237</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="241" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A241" s="1">
+        <v>238</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="242" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A242" s="1">
+        <v>239</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="243" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A243" s="1">
+        <v>240</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="244" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A244" s="1">
+        <v>241</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="245" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A245" s="1">
+        <v>242</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="246" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A246" s="1">
+        <v>243</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="247" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A247" s="1">
+        <v>244</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="248" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A248" s="1">
+        <v>245</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="249" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A249" s="1">
+        <v>246</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="250" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A250" s="1">
+        <v>247</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="251" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A251" s="1">
+        <v>248</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="252" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A252" s="1">
+        <v>249</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="253" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A253" s="1">
+        <v>250</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="254" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A254" s="1">
+        <v>251</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="255" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A255" s="1">
+        <v>252</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="256" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A256" s="1">
+        <v>253</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="257" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A257" s="1">
+        <v>254</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="258" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A258" s="1">
+        <v>255</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="259" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A259" s="1">
+        <v>256</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="260" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A260" s="1">
+        <v>257</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="261" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A261" s="1">
+        <v>258</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="262" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A262" s="1">
+        <v>259</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="263" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A263" s="1">
+        <v>260</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="264" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A264" s="1">
+        <v>261</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="265" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A265" s="1">
+        <v>262</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="266" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A266" s="1">
+        <v>263</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="267" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A267" s="1">
+        <v>264</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="268" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A268" s="1">
+        <v>265</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="269" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A269" s="1">
+        <v>266</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="270" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A270" s="1">
+        <v>267</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="271" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A271" s="1">
+        <v>268</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="272" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A272" s="1">
+        <v>269</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="273" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A273" s="1">
+        <v>270</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="274" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A274" s="1">
+        <v>271</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="275" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A275" s="1">
+        <v>272</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="276" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A276" s="1">
+        <v>273</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="277" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A277" s="1">
+        <v>274</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="278" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A278" s="1">
+        <v>275</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="279" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A279" s="1">
+        <v>276</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="280" s="1" customFormat="1" ht="19.8" spans="1:3">
+      <c r="A280" s="1">
+        <v>277</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -5417,7 +5417,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,1067,1068,null,1068,1067,null,1069,null,1069,null}</t>
+          <t>{null,null,null,null,null,1067,null,1068,null,1067,null,1069,null,1069,null}</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,1072,1073,null,1073,1072,null,1074,null,1074,null}</t>
+          <t>{null,null,null,null,null,1072,null,1073,null,1072,null,1074,null,1074,null}</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,1077,1078,null,1078,1077,null,1079,null,1079,null}</t>
+          <t>{null,null,null,null,null,1077,null,1078,null,1077,null,1079,null,1079,null}</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,1082,1083,null,1083,1082,null,1084,null,1084,null}</t>
+          <t>{null,null,null,null,null,1082,null,1083,null,1082,null,1084,null,1084,null}</t>
         </is>
       </c>
     </row>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C300"/>
+  <dimension ref="A1:C320"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="50.7777777777778" customWidth="1" style="3" min="2" max="2"/>
@@ -5226,7 +5226,7 @@
         </is>
       </c>
     </row>
-    <row r="281">
+    <row r="281" s="3">
       <c r="A281" s="2" t="n">
         <v>1001</v>
       </c>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
     </row>
-    <row r="282">
+    <row r="282" s="3">
       <c r="A282" s="2" t="n">
         <v>1002</v>
       </c>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
     </row>
-    <row r="283">
+    <row r="283" s="3">
       <c r="A283" s="2" t="n">
         <v>1003</v>
       </c>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
     </row>
-    <row r="284">
+    <row r="284" s="3">
       <c r="A284" s="2" t="n">
         <v>1004</v>
       </c>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
     </row>
-    <row r="285">
+    <row r="285" s="3">
       <c r="A285" s="2" t="n">
         <v>1005</v>
       </c>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
     </row>
-    <row r="286">
+    <row r="286" s="3">
       <c r="A286" s="2" t="n">
         <v>1006</v>
       </c>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
     </row>
-    <row r="287">
+    <row r="287" s="3">
       <c r="A287" s="2" t="n">
         <v>1007</v>
       </c>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
     </row>
-    <row r="288">
+    <row r="288" s="3">
       <c r="A288" s="2" t="n">
         <v>1008</v>
       </c>
@@ -5346,7 +5346,7 @@
         </is>
       </c>
     </row>
-    <row r="289">
+    <row r="289" s="3">
       <c r="A289" s="2" t="n">
         <v>1009</v>
       </c>
@@ -5361,7 +5361,7 @@
         </is>
       </c>
     </row>
-    <row r="290">
+    <row r="290" s="3">
       <c r="A290" s="2" t="n">
         <v>1010</v>
       </c>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
     </row>
-    <row r="291">
+    <row r="291" s="3">
       <c r="A291" s="2" t="n">
         <v>1011</v>
       </c>
@@ -5391,7 +5391,7 @@
         </is>
       </c>
     </row>
-    <row r="292">
+    <row r="292" s="3">
       <c r="A292" s="2" t="n">
         <v>1012</v>
       </c>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
     </row>
-    <row r="293">
+    <row r="293" s="3">
       <c r="A293" s="2" t="n">
         <v>1013</v>
       </c>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
     </row>
-    <row r="294">
+    <row r="294" s="3">
       <c r="A294" s="2" t="n">
         <v>1014</v>
       </c>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
     </row>
-    <row r="295">
+    <row r="295" s="3">
       <c r="A295" s="2" t="n">
         <v>1015</v>
       </c>
@@ -5451,7 +5451,7 @@
         </is>
       </c>
     </row>
-    <row r="296">
+    <row r="296" s="3">
       <c r="A296" s="2" t="n">
         <v>1016</v>
       </c>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
     </row>
-    <row r="297">
+    <row r="297" s="3">
       <c r="A297" s="2" t="n">
         <v>1017</v>
       </c>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
     </row>
-    <row r="298">
+    <row r="298" s="3">
       <c r="A298" s="2" t="n">
         <v>1018</v>
       </c>
@@ -5496,7 +5496,7 @@
         </is>
       </c>
     </row>
-    <row r="299">
+    <row r="299" s="3">
       <c r="A299" s="2" t="n">
         <v>1019</v>
       </c>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
     </row>
-    <row r="300">
+    <row r="300" s="3">
       <c r="A300" s="2" t="n">
         <v>1020</v>
       </c>
@@ -5523,6 +5523,306 @@
       <c r="C300" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,1090,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>草案-normal-laser（现有防御，仅探索性） · 物理攻击版（配对原组1001）</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>{null,2001,2002,2001,null,null,2003,2004,2003,null,null,2005,2006,2005,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>草案-normal-missile（现有防御，仅探索性） · 物理攻击版（配对原组1002）</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>{2007,2008,2009,2008,2007,2010,2011,2012,2011,2010,2013,2014,2015,2014,2013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>草案-normal-cannon（现有防御，仅探索性） · 物理攻击版（配对原组1003）</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,2016,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>草案-normal-longLaser（现有防御，仅探索性） · 物理攻击版（配对原组1004）</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,2017,2018,2017,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>草案-normal-neutral1（现有防御，仅探索性） · 物理攻击版（配对原组1005）</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,2019,2020,2019,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>草案-normal-neutral2（现有防御，仅探索性） · 物理攻击版（配对原组1006）</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,2025,2026,2025,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>草案-normal-neutral3（现有防御，仅探索性） · 物理攻击版（配对原组1007）</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,2031,2032,2031,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>草案-normal-neutral4（现有防御，仅探索性） · 物理攻击版（配对原组1008）</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,2037,2038,2037,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>草案-elite-laser（现有防御，仅探索性） · 物理攻击版（配对原组1009）</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>{2043,2044,2045,2044,2043,2046,2047,2047,2047,2046,2047,2047,2047,2047,2047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>草案-elite-missile（现有防御，仅探索性） · 物理攻击版（配对原组1010）</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>{2048,2049,2050,2049,2048,2051,2052,2053,2052,2051,2054,2055,2056,2055,2054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>草案-elite-cannon（现有防御，仅探索性） · 物理攻击版（配对原组1011）</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,2057,null,2058,null,2057,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>草案-elite-longLaser（现有防御，仅探索性） · 物理攻击版（配对原组1012）</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,2062,null,2063,null,2062,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>草案-elite-neutral1（现有防御，仅探索性） · 物理攻击版（配对原组1013）</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,2067,null,2068,null,2067,null,2069,null,2069,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>草案-elite-neutral2（现有防御，仅探索性） · 物理攻击版（配对原组1014）</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,2072,null,2073,null,2072,null,2074,null,2074,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>草案-elite-neutral3（现有防御，仅探索性） · 物理攻击版（配对原组1015）</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,2077,null,2078,null,2077,null,2079,null,2079,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>草案-elite-neutral4（现有防御，仅探索性） · 物理攻击版（配对原组1016）</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,2082,null,2083,null,2082,null,2084,null,2084,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>草案-boss-physical（现有防御，仅探索性） · 物理攻击版（配对原组1017）</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,2087,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>草案-boss-energy（现有防御，仅探索性） · 物理攻击版（配对原组1018）</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,2088,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>草案-ultimate-physical（现有防御，仅探索性） · 物理攻击版（配对原组1019）</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,2089,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>草案-ultimate-energy（现有防御，仅探索性） · 物理攻击版（配对原组1020）</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,2090,null,null,null,null,null,null,null}</t>
         </is>
       </c>
     </row>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C320"/>
+  <dimension ref="A1:C390"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="50.7777777777778" customWidth="1" style="3" min="2" max="2"/>
@@ -5826,6 +5826,1056 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>30011</v>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关1-层1-normal-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>{null,41021,41022,41023,null,null,41026,41027,41028,null,null,41031,41032,41033,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>30012</v>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关1-层2-normal-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>{null,41041,41042,41043,null,null,41046,41047,41048,null,null,41051,41052,41053,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>30013</v>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关1-层3-normal-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>{null,41061,41062,41063,null,null,41066,41067,41068,null,null,41071,41072,41073,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n">
+        <v>30014</v>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关1-层4-normal-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>{null,41081,41082,41083,null,null,41086,41087,41088,null,null,41091,41092,41093,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n">
+        <v>30015</v>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关1-层5-elite-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>{41100,41101,41102,41103,41104,41105,41106,41107,41108,41109,41110,41111,41112,41113,41114}</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n">
+        <v>30021</v>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关2-层1-normal-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>{42020,42021,42022,42023,42024,42025,42026,42027,42028,42029,42030,42031,42032,42033,42034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n">
+        <v>30022</v>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关2-层2-normal-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>{42040,42041,42042,42043,42044,42045,42046,42047,42048,42049,42050,42051,42052,42053,42054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n">
+        <v>30023</v>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关2-层3-normal-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>{42060,42061,42062,42063,42064,42065,42066,42067,42068,42069,42070,42071,42072,42073,42074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="n">
+        <v>30024</v>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关2-层4-normal-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>{42080,42081,42082,42083,42084,42085,42086,42087,42088,42089,42090,42091,42092,42093,42094}</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="n">
+        <v>30025</v>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关2-层5-elite-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>{42100,42101,42102,42103,42104,42105,42106,42107,42108,42109,42110,42111,42112,42113,42114}</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="n">
+        <v>30031</v>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关3-层1-normal-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,43027,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="n">
+        <v>30032</v>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关3-层2-normal-cannon-energy_attack</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,43047,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关3-层3-normal-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,43067,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="n">
+        <v>30034</v>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关3-层4-normal-cannon-energy_attack</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,43087,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="n">
+        <v>30035</v>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关3-层5-elite-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,43105,null,43107,null,43109,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="n">
+        <v>30041</v>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关4-层1-normal-neutral1-energy_attack</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,44026,44027,44028,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="n">
+        <v>30042</v>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关4-层2-normal-neutral1-physical_attack</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,44046,44047,44048,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="n">
+        <v>30043</v>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关4-层3-normal-neutral1-energy_attack</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,44066,44067,44068,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="n">
+        <v>30044</v>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关4-层4-normal-neutral1-physical_attack</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,44086,44087,44088,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="n">
+        <v>30045</v>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关4-层5-elite-neutral1-energy_attack</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,44105,null,44107,null,44109,null,44111,null,44113,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="n">
+        <v>30051</v>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关5-层1-normal-neutral2-physical_attack</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,45026,45027,45028,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>30052</v>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关5-层2-normal-neutral2-energy_attack</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,45046,45047,45048,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="n">
+        <v>30053</v>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关5-层3-normal-neutral2-physical_attack</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,45066,45067,45068,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="n">
+        <v>30054</v>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关5-层4-normal-neutral2-energy_attack</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,45086,45087,45088,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="n">
+        <v>30055</v>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关5-层5-elite-neutral2-physical_attack</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,45105,null,45107,null,45109,null,45111,null,45113,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="n">
+        <v>30061</v>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关6-层1-normal-longLaser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,46026,46027,46028,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="n">
+        <v>30062</v>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关6-层2-normal-longLaser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,46046,46047,46048,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="n">
+        <v>30063</v>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关6-层3-normal-longLaser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,46066,46067,46068,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="n">
+        <v>30064</v>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关6-层4-normal-longLaser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,46086,46087,46088,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="n">
+        <v>30065</v>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关6-层5-normal-longLaser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,46106,46107,46108,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="n">
+        <v>30066</v>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关6-层6-elite-longLaser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,46125,null,46127,null,46129,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="n">
+        <v>30067</v>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关6-层7-elite-longLaser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,46145,null,46147,null,46149,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="n">
+        <v>30068</v>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关6-层8-elite-longLaser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,46165,null,46167,null,46169,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="n">
+        <v>30069</v>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关6-层9-boss-longLaser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,46187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="n">
+        <v>30071</v>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关7-层1-normal-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>{null,47021,47022,47023,null,null,47026,47027,47028,null,null,47031,47032,47033,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="n">
+        <v>30072</v>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关7-层2-normal-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>{null,47041,47042,47043,null,null,47046,47047,47048,null,null,47051,47052,47053,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="n">
+        <v>30073</v>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关7-层3-normal-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>{null,47061,47062,47063,null,null,47066,47067,47068,null,null,47071,47072,47073,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="n">
+        <v>30074</v>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关7-层4-normal-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>{null,47081,47082,47083,null,null,47086,47087,47088,null,null,47091,47092,47093,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="n">
+        <v>30075</v>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关7-层5-normal-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>{null,47101,47102,47103,null,null,47106,47107,47108,null,null,47111,47112,47113,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="n">
+        <v>30076</v>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关7-层6-elite-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>{47120,47121,47122,47123,47124,47125,47126,47127,47128,47129,47130,47131,47132,47133,47134}</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="n">
+        <v>30077</v>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关7-层7-elite-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>{47140,47141,47142,47143,47144,47145,47146,47147,47148,47149,47150,47151,47152,47153,47154}</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="n">
+        <v>30078</v>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关7-层8-elite-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>{47160,47161,47162,47163,47164,47165,47166,47167,47168,47169,47170,47171,47172,47173,47174}</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="n">
+        <v>30079</v>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关7-层9-boss-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,47187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="n">
+        <v>30081</v>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关8-层1-normal-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>{48020,48021,48022,48023,48024,48025,48026,48027,48028,48029,48030,48031,48032,48033,48034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="n">
+        <v>30082</v>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关8-层2-normal-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>{48040,48041,48042,48043,48044,48045,48046,48047,48048,48049,48050,48051,48052,48053,48054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="n">
+        <v>30083</v>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关8-层3-normal-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>{48060,48061,48062,48063,48064,48065,48066,48067,48068,48069,48070,48071,48072,48073,48074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="n">
+        <v>30084</v>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关8-层4-normal-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>{48080,48081,48082,48083,48084,48085,48086,48087,48088,48089,48090,48091,48092,48093,48094}</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="n">
+        <v>30085</v>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关8-层5-normal-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>{48100,48101,48102,48103,48104,48105,48106,48107,48108,48109,48110,48111,48112,48113,48114}</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="n">
+        <v>30086</v>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关8-层6-elite-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>{48120,48121,48122,48123,48124,48125,48126,48127,48128,48129,48130,48131,48132,48133,48134}</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="n">
+        <v>30087</v>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关8-层7-elite-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>{48140,48141,48142,48143,48144,48145,48146,48147,48148,48149,48150,48151,48152,48153,48154}</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="n">
+        <v>30088</v>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关8-层8-elite-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>{48160,48161,48162,48163,48164,48165,48166,48167,48168,48169,48170,48171,48172,48173,48174}</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="n">
+        <v>30089</v>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关8-层9-boss-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,48187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="n">
+        <v>30091</v>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关9-层1-normal-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,49027,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="n">
+        <v>30092</v>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关9-层2-normal-cannon-energy_attack</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,49047,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="n">
+        <v>30093</v>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关9-层3-normal-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,49067,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="n">
+        <v>30094</v>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关9-层4-normal-cannon-energy_attack</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,49087,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="n">
+        <v>30095</v>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关9-层5-normal-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,49107,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="n">
+        <v>30096</v>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关9-层6-elite-cannon-energy_attack</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,49125,null,49127,null,49129,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="n">
+        <v>30097</v>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关9-层7-elite-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,49145,null,49147,null,49149,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="n">
+        <v>30098</v>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关9-层8-elite-cannon-energy_attack</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,49165,null,49167,null,49169,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="n">
+        <v>30099</v>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关9-层9-boss-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,49187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="n">
+        <v>30101</v>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关10-层1-normal-neutral3-energy_attack</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,50026,50027,50028,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="n">
+        <v>30102</v>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关10-层2-normal-neutral3-physical_attack</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,50046,50047,50048,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="n">
+        <v>30103</v>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关10-层3-normal-neutral3-energy_attack</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,50066,50067,50068,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="n">
+        <v>30104</v>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关10-层4-normal-neutral3-physical_attack</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,50086,50087,50088,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="n">
+        <v>30105</v>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关10-层5-normal-neutral3-energy_attack</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,50106,50107,50108,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="n">
+        <v>30106</v>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关10-层6-elite-neutral3-physical_attack</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,50125,null,50127,null,50129,null,50131,null,50133,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="n">
+        <v>30107</v>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关10-层7-elite-neutral3-energy_attack</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,50145,null,50147,null,50149,null,50151,null,50153,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="n">
+        <v>30108</v>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关10-层8-elite-neutral3-physical_attack</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,50165,null,50167,null,50169,null,50171,null,50173,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="n">
+        <v>30109</v>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>校准early-v3-关10-层9-boss-neutral3-energy_attack</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,50187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C390"/>
+  <dimension ref="A1:C480"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="50.7777777777778" customWidth="1" style="3" min="2" max="2"/>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关1-层1-normal-laser-physical_attack</t>
+          <t>校准progression-v4-关1-层1-normal-laser-physical_attack</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关1-层2-normal-laser-energy_attack</t>
+          <t>校准progression-v4-关1-层2-normal-laser-energy_attack</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关1-层3-normal-laser-physical_attack</t>
+          <t>校准progression-v4-关1-层3-normal-laser-physical_attack</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关1-层4-normal-laser-energy_attack</t>
+          <t>校准progression-v4-关1-层4-normal-laser-energy_attack</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关1-层5-elite-laser-physical_attack</t>
+          <t>校准progression-v4-关1-层5-elite-laser-physical_attack</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关2-层1-normal-missile-energy_attack</t>
+          <t>校准progression-v4-关2-层1-normal-missile-energy_attack</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关2-层2-normal-missile-physical_attack</t>
+          <t>校准progression-v4-关2-层2-normal-missile-physical_attack</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关2-层3-normal-missile-energy_attack</t>
+          <t>校准progression-v4-关2-层3-normal-missile-energy_attack</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关2-层4-normal-missile-physical_attack</t>
+          <t>校准progression-v4-关2-层4-normal-missile-physical_attack</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关2-层5-elite-missile-energy_attack</t>
+          <t>校准progression-v4-关2-层5-elite-missile-energy_attack</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关3-层1-normal-cannon-physical_attack</t>
+          <t>校准progression-v4-关3-层1-normal-cannon-physical_attack</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关3-层2-normal-cannon-energy_attack</t>
+          <t>校准progression-v4-关3-层2-normal-cannon-energy_attack</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关3-层3-normal-cannon-physical_attack</t>
+          <t>校准progression-v4-关3-层3-normal-cannon-physical_attack</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关3-层4-normal-cannon-energy_attack</t>
+          <t>校准progression-v4-关3-层4-normal-cannon-energy_attack</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关3-层5-elite-cannon-physical_attack</t>
+          <t>校准progression-v4-关3-层5-elite-cannon-physical_attack</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关4-层1-normal-neutral1-energy_attack</t>
+          <t>校准progression-v4-关4-层1-normal-neutral1-energy_attack</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关4-层2-normal-neutral1-physical_attack</t>
+          <t>校准progression-v4-关4-层2-normal-neutral1-physical_attack</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关4-层3-normal-neutral1-energy_attack</t>
+          <t>校准progression-v4-关4-层3-normal-neutral1-energy_attack</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关4-层4-normal-neutral1-physical_attack</t>
+          <t>校准progression-v4-关4-层4-normal-neutral1-physical_attack</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关4-层5-elite-neutral1-energy_attack</t>
+          <t>校准progression-v4-关4-层5-elite-neutral1-energy_attack</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关5-层1-normal-neutral2-physical_attack</t>
+          <t>校准progression-v4-关5-层1-normal-neutral2-physical_attack</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关5-层2-normal-neutral2-energy_attack</t>
+          <t>校准progression-v4-关5-层2-normal-neutral2-energy_attack</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关5-层3-normal-neutral2-physical_attack</t>
+          <t>校准progression-v4-关5-层3-normal-neutral2-physical_attack</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关5-层4-normal-neutral2-energy_attack</t>
+          <t>校准progression-v4-关5-层4-normal-neutral2-energy_attack</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关5-层5-elite-neutral2-physical_attack</t>
+          <t>校准progression-v4-关5-层5-elite-neutral2-physical_attack</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关6-层1-normal-longLaser-energy_attack</t>
+          <t>校准progression-v4-关6-层1-normal-longLaser-energy_attack</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关6-层2-normal-longLaser-physical_attack</t>
+          <t>校准progression-v4-关6-层2-normal-longLaser-physical_attack</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关6-层3-normal-longLaser-energy_attack</t>
+          <t>校准progression-v4-关6-层3-normal-longLaser-energy_attack</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关6-层4-normal-longLaser-physical_attack</t>
+          <t>校准progression-v4-关6-层4-normal-longLaser-physical_attack</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关6-层5-normal-longLaser-energy_attack</t>
+          <t>校准progression-v4-关6-层5-normal-longLaser-energy_attack</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关6-层6-elite-longLaser-physical_attack</t>
+          <t>校准progression-v4-关6-层6-elite-longLaser-physical_attack</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关6-层7-elite-longLaser-energy_attack</t>
+          <t>校准progression-v4-关6-层7-elite-longLaser-energy_attack</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关6-层8-elite-longLaser-physical_attack</t>
+          <t>校准progression-v4-关6-层8-elite-longLaser-physical_attack</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关6-层9-boss-longLaser-energy_attack</t>
+          <t>校准progression-v4-关6-层9-boss-longLaser-energy_attack</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关7-层1-normal-laser-physical_attack</t>
+          <t>校准progression-v4-关7-层1-normal-laser-physical_attack</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关7-层2-normal-laser-energy_attack</t>
+          <t>校准progression-v4-关7-层2-normal-laser-energy_attack</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关7-层3-normal-laser-physical_attack</t>
+          <t>校准progression-v4-关7-层3-normal-laser-physical_attack</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关7-层4-normal-laser-energy_attack</t>
+          <t>校准progression-v4-关7-层4-normal-laser-energy_attack</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关7-层5-normal-laser-physical_attack</t>
+          <t>校准progression-v4-关7-层5-normal-laser-physical_attack</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关7-层6-elite-laser-energy_attack</t>
+          <t>校准progression-v4-关7-层6-elite-laser-energy_attack</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关7-层7-elite-laser-physical_attack</t>
+          <t>校准progression-v4-关7-层7-elite-laser-physical_attack</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关7-层8-elite-laser-energy_attack</t>
+          <t>校准progression-v4-关7-层8-elite-laser-energy_attack</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关7-层9-boss-laser-physical_attack</t>
+          <t>校准progression-v4-关7-层9-boss-laser-physical_attack</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关8-层1-normal-missile-energy_attack</t>
+          <t>校准progression-v4-关8-层1-normal-missile-energy_attack</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关8-层2-normal-missile-physical_attack</t>
+          <t>校准progression-v4-关8-层2-normal-missile-physical_attack</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关8-层3-normal-missile-energy_attack</t>
+          <t>校准progression-v4-关8-层3-normal-missile-energy_attack</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关8-层4-normal-missile-physical_attack</t>
+          <t>校准progression-v4-关8-层4-normal-missile-physical_attack</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关8-层5-normal-missile-energy_attack</t>
+          <t>校准progression-v4-关8-层5-normal-missile-energy_attack</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关8-层6-elite-missile-physical_attack</t>
+          <t>校准progression-v4-关8-层6-elite-missile-physical_attack</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关8-层7-elite-missile-energy_attack</t>
+          <t>校准progression-v4-关8-层7-elite-missile-energy_attack</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关8-层8-elite-missile-physical_attack</t>
+          <t>校准progression-v4-关8-层8-elite-missile-physical_attack</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关8-层9-boss-missile-energy_attack</t>
+          <t>校准progression-v4-关8-层9-boss-missile-energy_attack</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关9-层1-normal-cannon-physical_attack</t>
+          <t>校准progression-v4-关9-层1-normal-cannon-physical_attack</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关9-层2-normal-cannon-energy_attack</t>
+          <t>校准progression-v4-关9-层2-normal-cannon-energy_attack</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关9-层3-normal-cannon-physical_attack</t>
+          <t>校准progression-v4-关9-层3-normal-cannon-physical_attack</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关9-层4-normal-cannon-energy_attack</t>
+          <t>校准progression-v4-关9-层4-normal-cannon-energy_attack</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关9-层5-normal-cannon-physical_attack</t>
+          <t>校准progression-v4-关9-层5-normal-cannon-physical_attack</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关9-层6-elite-cannon-energy_attack</t>
+          <t>校准progression-v4-关9-层6-elite-cannon-energy_attack</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关9-层7-elite-cannon-physical_attack</t>
+          <t>校准progression-v4-关9-层7-elite-cannon-physical_attack</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关9-层8-elite-cannon-energy_attack</t>
+          <t>校准progression-v4-关9-层8-elite-cannon-energy_attack</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关9-层9-boss-cannon-physical_attack</t>
+          <t>校准progression-v4-关9-层9-boss-cannon-physical_attack</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关10-层1-normal-neutral3-energy_attack</t>
+          <t>校准progression-v4-关10-层1-normal-neutral3-energy_attack</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关10-层2-normal-neutral3-physical_attack</t>
+          <t>校准progression-v4-关10-层2-normal-neutral3-physical_attack</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关10-层3-normal-neutral3-energy_attack</t>
+          <t>校准progression-v4-关10-层3-normal-neutral3-energy_attack</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关10-层4-normal-neutral3-physical_attack</t>
+          <t>校准progression-v4-关10-层4-normal-neutral3-physical_attack</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关10-层5-normal-neutral3-energy_attack</t>
+          <t>校准progression-v4-关10-层5-normal-neutral3-energy_attack</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关10-层6-elite-neutral3-physical_attack</t>
+          <t>校准progression-v4-关10-层6-elite-neutral3-physical_attack</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关10-层7-elite-neutral3-energy_attack</t>
+          <t>校准progression-v4-关10-层7-elite-neutral3-energy_attack</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关10-层8-elite-neutral3-physical_attack</t>
+          <t>校准progression-v4-关10-层8-elite-neutral3-physical_attack</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
@@ -6867,12 +6867,1362 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>校准early-v3-关10-层9-boss-neutral3-energy_attack</t>
+          <t>校准progression-v4-关10-层9-boss-neutral3-energy_attack</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,50187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="n">
+        <v>30111</v>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关11-层1-normal-neutral1-physical_attack</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,51026,51027,51028,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="n">
+        <v>30112</v>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关11-层2-normal-neutral1-energy_attack</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,51046,51047,51048,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="n">
+        <v>30113</v>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关11-层3-normal-neutral1-physical_attack</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,51066,51067,51068,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="n">
+        <v>30114</v>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关11-层4-normal-neutral1-energy_attack</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,51086,51087,51088,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="n">
+        <v>30115</v>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关11-层5-normal-neutral1-physical_attack</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,51106,51107,51108,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="n">
+        <v>30116</v>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关11-层6-elite-neutral1-energy_attack</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,51125,null,51127,null,51129,null,51131,null,51133,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="n">
+        <v>30117</v>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关11-层7-elite-neutral1-physical_attack</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,51145,null,51147,null,51149,null,51151,null,51153,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="n">
+        <v>30118</v>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关11-层8-elite-neutral1-energy_attack</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,51165,null,51167,null,51169,null,51171,null,51173,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="n">
+        <v>30119</v>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关11-层9-boss-neutral1-physical_attack</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,51187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="n">
+        <v>30121</v>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关12-层1-normal-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>{52020,52021,52022,52023,52024,52025,52026,52027,52028,52029,52030,52031,52032,52033,52034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="n">
+        <v>30122</v>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关12-层2-normal-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>{52040,52041,52042,52043,52044,52045,52046,52047,52048,52049,52050,52051,52052,52053,52054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="n">
+        <v>30123</v>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关12-层3-normal-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>{52060,52061,52062,52063,52064,52065,52066,52067,52068,52069,52070,52071,52072,52073,52074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="n">
+        <v>30124</v>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关12-层4-normal-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>{52080,52081,52082,52083,52084,52085,52086,52087,52088,52089,52090,52091,52092,52093,52094}</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="n">
+        <v>30125</v>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关12-层5-normal-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>{52100,52101,52102,52103,52104,52105,52106,52107,52108,52109,52110,52111,52112,52113,52114}</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="n">
+        <v>30126</v>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关12-层6-elite-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>{52120,52121,52122,52123,52124,52125,52126,52127,52128,52129,52130,52131,52132,52133,52134}</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="n">
+        <v>30127</v>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关12-层7-elite-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>{52140,52141,52142,52143,52144,52145,52146,52147,52148,52149,52150,52151,52152,52153,52154}</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="n">
+        <v>30128</v>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关12-层8-elite-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>{52160,52161,52162,52163,52164,52165,52166,52167,52168,52169,52170,52171,52172,52173,52174}</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="n">
+        <v>30129</v>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关12-层9-boss-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,52187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="n">
+        <v>30131</v>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关13-层1-normal-neutral2-physical_attack</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,53026,53027,53028,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="n">
+        <v>30132</v>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关13-层2-normal-neutral2-energy_attack</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,53046,53047,53048,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="n">
+        <v>30133</v>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关13-层3-normal-neutral2-physical_attack</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,53066,53067,53068,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="n">
+        <v>30134</v>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关13-层4-normal-neutral2-energy_attack</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,53086,53087,53088,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="n">
+        <v>30135</v>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关13-层5-normal-neutral2-physical_attack</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,53106,53107,53108,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="n">
+        <v>30136</v>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关13-层6-elite-neutral2-energy_attack</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,53125,null,53127,null,53129,null,53131,null,53133,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="n">
+        <v>30137</v>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关13-层7-elite-neutral2-physical_attack</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,53145,null,53147,null,53149,null,53151,null,53153,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="n">
+        <v>30138</v>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关13-层8-elite-neutral2-energy_attack</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,53165,null,53167,null,53169,null,53171,null,53173,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="n">
+        <v>30139</v>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关13-层9-boss-neutral2-physical_attack</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,53187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="n">
+        <v>30141</v>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关14-层1-normal-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>{null,54021,54022,54023,null,null,54026,54027,54028,null,null,54031,54032,54033,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="n">
+        <v>30142</v>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关14-层2-normal-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>{null,54041,54042,54043,null,null,54046,54047,54048,null,null,54051,54052,54053,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="n">
+        <v>30143</v>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关14-层3-normal-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>{null,54061,54062,54063,null,null,54066,54067,54068,null,null,54071,54072,54073,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="n">
+        <v>30144</v>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关14-层4-normal-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>{null,54081,54082,54083,null,null,54086,54087,54088,null,null,54091,54092,54093,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="n">
+        <v>30145</v>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关14-层5-normal-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>{null,54101,54102,54103,null,null,54106,54107,54108,null,null,54111,54112,54113,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="n">
+        <v>30146</v>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关14-层6-elite-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>{54120,54121,54122,54123,54124,54125,54126,54127,54128,54129,54130,54131,54132,54133,54134}</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="n">
+        <v>30147</v>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关14-层7-elite-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>{54140,54141,54142,54143,54144,54145,54146,54147,54148,54149,54150,54151,54152,54153,54154}</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="n">
+        <v>30148</v>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关14-层8-elite-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>{54160,54161,54162,54163,54164,54165,54166,54167,54168,54169,54170,54171,54172,54173,54174}</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="n">
+        <v>30149</v>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关14-层9-boss-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,54187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="n">
+        <v>30151</v>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关15-层1-normal-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,55027,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="n">
+        <v>30152</v>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关15-层2-normal-cannon-energy_attack</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,55047,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="n">
+        <v>30153</v>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关15-层3-normal-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,55067,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="n">
+        <v>30154</v>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关15-层4-normal-cannon-energy_attack</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,55087,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n">
+        <v>30155</v>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关15-层5-normal-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,55107,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="n">
+        <v>30156</v>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关15-层6-elite-cannon-energy_attack</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,55125,null,55127,null,55129,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="n">
+        <v>30157</v>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关15-层7-elite-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,55145,null,55147,null,55149,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="n">
+        <v>30158</v>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关15-层8-elite-cannon-energy_attack</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,55165,null,55167,null,55169,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n">
+        <v>30159</v>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关15-层9-boss-cannon-physical_attack</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,55187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n">
+        <v>30161</v>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关16-层1-normal-neutral4-energy_attack</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,56026,56027,56028,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n">
+        <v>30162</v>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关16-层2-normal-neutral4-physical_attack</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,56046,56047,56048,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="n">
+        <v>30163</v>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关16-层3-normal-neutral4-energy_attack</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,56066,56067,56068,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="n">
+        <v>30164</v>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关16-层4-normal-neutral4-physical_attack</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,56086,56087,56088,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="n">
+        <v>30165</v>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关16-层5-normal-neutral4-energy_attack</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,56106,56107,56108,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="n">
+        <v>30166</v>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关16-层6-elite-neutral4-physical_attack</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,56125,null,56127,null,56129,null,56131,null,56133,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="n">
+        <v>30167</v>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关16-层7-elite-neutral4-energy_attack</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,56145,null,56147,null,56149,null,56151,null,56153,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="n">
+        <v>30168</v>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关16-层8-elite-neutral4-physical_attack</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,56165,null,56167,null,56169,null,56171,null,56173,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="n">
+        <v>30169</v>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关16-层9-boss-neutral4-energy_attack</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,56187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="n">
+        <v>30171</v>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关17-层1-normal-longLaser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,57026,57027,57028,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="n">
+        <v>30172</v>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关17-层2-normal-longLaser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,57046,57047,57048,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="n">
+        <v>30173</v>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关17-层3-normal-longLaser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,57066,57067,57068,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="n">
+        <v>30174</v>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关17-层4-normal-longLaser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,57086,57087,57088,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="n">
+        <v>30175</v>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关17-层5-normal-longLaser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,57106,57107,57108,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="n">
+        <v>30176</v>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关17-层6-elite-longLaser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,57125,null,57127,null,57129,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="n">
+        <v>30177</v>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关17-层7-elite-longLaser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,57145,null,57147,null,57149,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="n">
+        <v>30178</v>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关17-层8-elite-longLaser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,57165,null,57167,null,57169,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="n">
+        <v>30179</v>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关17-层9-boss-longLaser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,57187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="n">
+        <v>30181</v>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关18-层1-normal-neutral3-energy_attack</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,58026,58027,58028,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="n">
+        <v>30182</v>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关18-层2-normal-neutral3-physical_attack</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,58046,58047,58048,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="n">
+        <v>30183</v>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关18-层3-normal-neutral3-energy_attack</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,58066,58067,58068,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="n">
+        <v>30184</v>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关18-层4-normal-neutral3-physical_attack</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,58086,58087,58088,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="n">
+        <v>30185</v>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关18-层5-normal-neutral3-energy_attack</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,58106,58107,58108,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="n">
+        <v>30186</v>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关18-层6-elite-neutral3-physical_attack</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,58125,null,58127,null,58129,null,58131,null,58133,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="n">
+        <v>30187</v>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关18-层7-elite-neutral3-energy_attack</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,58145,null,58147,null,58149,null,58151,null,58153,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="n">
+        <v>30188</v>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关18-层8-elite-neutral3-physical_attack</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,58165,null,58167,null,58169,null,58171,null,58173,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="n">
+        <v>30189</v>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关18-层9-boss-neutral3-energy_attack</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,58187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="n">
+        <v>30191</v>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关19-层1-normal-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>{59020,59021,59022,59023,59024,59025,59026,59027,59028,59029,59030,59031,59032,59033,59034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="n">
+        <v>30192</v>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关19-层2-normal-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>{59040,59041,59042,59043,59044,59045,59046,59047,59048,59049,59050,59051,59052,59053,59054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="n">
+        <v>30193</v>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关19-层3-normal-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>{59060,59061,59062,59063,59064,59065,59066,59067,59068,59069,59070,59071,59072,59073,59074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="n">
+        <v>30194</v>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关19-层4-normal-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>{59080,59081,59082,59083,59084,59085,59086,59087,59088,59089,59090,59091,59092,59093,59094}</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="n">
+        <v>30195</v>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关19-层5-normal-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>{59100,59101,59102,59103,59104,59105,59106,59107,59108,59109,59110,59111,59112,59113,59114}</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="n">
+        <v>30196</v>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关19-层6-elite-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>{59120,59121,59122,59123,59124,59125,59126,59127,59128,59129,59130,59131,59132,59133,59134}</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="n">
+        <v>30197</v>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关19-层7-elite-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>{59140,59141,59142,59143,59144,59145,59146,59147,59148,59149,59150,59151,59152,59153,59154}</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="n">
+        <v>30198</v>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关19-层8-elite-missile-energy_attack</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>{59160,59161,59162,59163,59164,59165,59166,59167,59168,59169,59170,59171,59172,59173,59174}</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="n">
+        <v>30199</v>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关19-层9-boss-missile-physical_attack</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,59187,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="n">
+        <v>30201</v>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关20-层1-elite-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>{60020,60021,60022,60023,60024,60025,60026,60027,60028,60029,60030,60031,60032,60033,60034}</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="n">
+        <v>30202</v>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关20-层2-elite-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>{60040,60041,60042,60043,60044,60045,60046,60047,60048,60049,60050,60051,60052,60053,60054}</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="n">
+        <v>30203</v>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关20-层3-elite-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>{60060,60061,60062,60063,60064,60065,60066,60067,60068,60069,60070,60071,60072,60073,60074}</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="n">
+        <v>30204</v>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关20-层4-elite-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>{60080,60081,60082,60083,60084,60085,60086,60087,60088,60089,60090,60091,60092,60093,60094}</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="n">
+        <v>30205</v>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关20-层5-elite-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>{60100,60101,60102,60103,60104,60105,60106,60107,60108,60109,60110,60111,60112,60113,60114}</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="n">
+        <v>30206</v>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关20-层6-boss-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,60127,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="n">
+        <v>30207</v>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关20-层7-boss-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,60147,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="n">
+        <v>30208</v>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关20-层8-boss-laser-physical_attack</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,60167,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="n">
+        <v>30209</v>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>校准progression-v4-关20-层9-ultimate-laser-energy_attack</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,60187,null,null,null,null,null,null,null}</t>
         </is>
       </c>
     </row>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2280"/>
+  <dimension ref="A1:F2280"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="50.7777777777778" customWidth="1" style="3" min="2" max="2"/>
@@ -1041,6 +1041,16 @@
           <t>combatTier</t>
         </is>
       </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>atkMultiplier</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>lifeMultiplier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1063,6 +1073,16 @@
           <t>Runtime wave tier, separate from final-wave completion</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>本波攻击倍率；空白为1，仅影响本波，不改变奖励或下关</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>本波生命及护盾倍率；空白为1，仅影响本波，不改变奖励或下关</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1083,6 +1103,16 @@
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
@@ -7780,6 +7810,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E407" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F407" s="2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
@@ -7800,6 +7836,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E408" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F408" s="2" t="n">
+        <v>1024</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
@@ -8320,6 +8362,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E434" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F434" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
@@ -8340,6 +8388,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E435" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F435" s="2" t="n">
+        <v>1024</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
@@ -8860,6 +8914,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E461" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F461" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
@@ -8880,6 +8940,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E462" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F462" s="2" t="n">
+        <v>256</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
@@ -9220,6 +9286,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E479" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F479" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
@@ -9239,6 +9311,12 @@
         <is>
           <t>ultimate</t>
         </is>
+      </c>
+      <c r="E480" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F480" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="481">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2280"/>
+  <dimension ref="A1:F2280"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="50.7777777777778" customWidth="1" style="3" min="2" max="2"/>
@@ -1041,6 +1041,16 @@
           <t>combatTier</t>
         </is>
       </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>atkMultiplier</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>lifeMultiplier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1063,6 +1073,16 @@
           <t>Runtime wave tier, separate from final-wave completion</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>本波攻击倍率；空白为1，不改变跨关插值锚点</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>本波生命及护盾倍率；空白为1，不改变资源和跨关插值锚点</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1083,6 +1103,16 @@
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
         </is>
       </c>
     </row>
@@ -7460,6 +7490,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E391" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F391" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
@@ -7480,6 +7516,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E392" s="2" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="F392" s="2" t="n">
+        <v>1.375</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
@@ -7500,6 +7542,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E393" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F393" s="2" t="n">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
@@ -7520,6 +7568,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E394" s="2" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F394" s="2" t="n">
+        <v>2.125</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
@@ -7540,6 +7594,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E395" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F395" s="2" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
@@ -7560,6 +7620,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E396" s="2" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>2.875</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
@@ -7580,6 +7646,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E397" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F397" s="2" t="n">
+        <v>3.25</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
@@ -7600,6 +7672,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E398" s="2" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>3.625</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
@@ -7620,6 +7698,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E399" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F399" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
@@ -7640,6 +7724,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E400" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F400" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
@@ -7660,6 +7750,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E401" s="2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F401" s="2" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
@@ -7680,6 +7776,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E402" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F402" s="2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
@@ -7700,6 +7802,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E403" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F403" s="2" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
@@ -7720,6 +7828,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E404" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F404" s="2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
@@ -7740,6 +7854,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E405" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F405" s="2" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
@@ -7760,6 +7880,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E406" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
@@ -7780,6 +7906,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E407" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F407" s="2" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
@@ -7800,6 +7932,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E408" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F408" s="2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
@@ -7820,6 +7958,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E409" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F409" s="2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
@@ -7840,6 +7984,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E410" s="2" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="F410" s="2" t="n">
+        <v>7.75</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
@@ -7860,6 +8010,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E411" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F411" s="2" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
@@ -7880,6 +8036,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E412" s="2" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="F412" s="2" t="n">
+        <v>7.25</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
@@ -7900,6 +8062,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E413" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F413" s="2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
@@ -7920,6 +8088,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E414" s="2" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="F414" s="2" t="n">
+        <v>6.75</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
@@ -7940,6 +8114,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E415" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F415" s="2" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
@@ -7960,6 +8140,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E416" s="2" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="F416" s="2" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
@@ -7980,6 +8166,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E417" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F417" s="2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
@@ -8000,6 +8192,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E418" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F418" s="2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
@@ -8020,6 +8218,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E419" s="2" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="F419" s="2" t="n">
+        <v>6.75</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
@@ -8040,6 +8244,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E420" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F420" s="2" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
@@ -8060,6 +8270,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E421" s="2" t="n">
+        <v>4.125</v>
+      </c>
+      <c r="F421" s="2" t="n">
+        <v>8.25</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
@@ -8080,6 +8296,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E422" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F422" s="2" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
@@ -8100,6 +8322,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E423" s="2" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="F423" s="2" t="n">
+        <v>9.75</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
@@ -8120,6 +8348,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E424" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F424" s="2" t="n">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
@@ -8140,6 +8374,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E425" s="2" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="F425" s="2" t="n">
+        <v>11.25</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
@@ -8160,6 +8400,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E426" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F426" s="2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
@@ -8180,6 +8426,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E427" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F427" s="2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
@@ -8200,6 +8452,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E428" s="2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F428" s="2" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
@@ -8220,6 +8478,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E429" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F429" s="2" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
@@ -8240,6 +8504,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E430" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="F430" s="2" t="n">
+        <v>13.5</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
@@ -8260,6 +8530,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E431" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F431" s="2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
@@ -8280,6 +8556,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E432" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F432" s="2" t="n">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
@@ -8300,6 +8582,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E433" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F433" s="2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
@@ -8320,6 +8608,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E434" s="2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F434" s="2" t="n">
+        <v>15.5</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
@@ -8340,6 +8634,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E435" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F435" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
@@ -8360,6 +8660,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E436" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F436" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
@@ -8380,6 +8686,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E437" s="2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F437" s="2" t="n">
+        <v>15.5</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
@@ -8400,6 +8712,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E438" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F438" s="2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
@@ -8420,6 +8738,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E439" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F439" s="2" t="n">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
@@ -8440,6 +8764,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E440" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F440" s="2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
@@ -8460,6 +8790,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E441" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="F441" s="2" t="n">
+        <v>13.5</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
@@ -8480,6 +8816,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E442" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F442" s="2" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
@@ -8500,6 +8842,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E443" s="2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F443" s="2" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
@@ -8520,6 +8868,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E444" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F444" s="2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
@@ -8540,6 +8894,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E445" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F445" s="2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
@@ -8560,6 +8920,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E446" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F446" s="2" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
@@ -8580,6 +8946,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E447" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F447" s="2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
@@ -8600,6 +8972,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E448" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F448" s="2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
@@ -8620,6 +8998,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E449" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F449" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
@@ -8640,6 +9024,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E450" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F450" s="2" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
@@ -8660,6 +9050,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E451" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F451" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
@@ -8680,6 +9076,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E452" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F452" s="2" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
@@ -8700,6 +9102,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E453" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F453" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
@@ -8720,6 +9128,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E454" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F454" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
@@ -8740,6 +9154,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E455" s="2" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="F455" s="2" t="n">
+        <v>20.5</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
@@ -8760,6 +9180,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E456" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F456" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
@@ -8780,6 +9206,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E457" s="2" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="F457" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
@@ -8800,6 +9232,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E458" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F458" s="2" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
@@ -8820,6 +9258,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E459" s="2" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="F459" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
@@ -8840,6 +9284,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E460" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F460" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
@@ -8860,6 +9310,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E461" s="2" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F461" s="2" t="n">
+        <v>23.5</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
@@ -8880,6 +9336,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E462" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F462" s="2" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
@@ -8900,6 +9362,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E463" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F463" s="2" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
@@ -8920,6 +9388,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E464" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F464" s="2" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
@@ -8940,6 +9414,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E465" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F465" s="2" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
@@ -8960,6 +9440,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E466" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F466" s="2" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
@@ -8980,6 +9466,12 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="E467" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F467" s="2" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
@@ -9000,6 +9492,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E468" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F468" s="2" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
@@ -9020,6 +9518,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E469" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F469" s="2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
@@ -9040,6 +9544,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E470" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F470" s="2" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
@@ -9060,6 +9570,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E471" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F471" s="2" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
@@ -9080,6 +9596,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E472" t="n">
+        <v>16</v>
+      </c>
+      <c r="F472" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
@@ -9100,6 +9622,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E473" t="n">
+        <v>3.391110215352182</v>
+      </c>
+      <c r="F473" t="n">
+        <v>5.605023522991008</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
@@ -9120,6 +9648,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E474" t="n">
+        <v>2.127461929935275</v>
+      </c>
+      <c r="F474" t="n">
+        <v>3.156649161856778</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
@@ -9140,6 +9674,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E475" t="n">
+        <v>1.648015526593405</v>
+      </c>
+      <c r="F475" t="n">
+        <v>2.236366506256873</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
@@ -9160,6 +9700,12 @@
           <t>elite</t>
         </is>
       </c>
+      <c r="E476" t="n">
+        <v>1.395646246917129</v>
+      </c>
+      <c r="F476" t="n">
+        <v>1.753846098162387</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
@@ -9180,6 +9726,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E477" t="n">
+        <v>1.239919029849584</v>
+      </c>
+      <c r="F477" t="n">
+        <v>1.456750492140449</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
@@ -9200,6 +9752,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E478" t="n">
+        <v>1.134242642197337</v>
+      </c>
+      <c r="F478" t="n">
+        <v>1.255422883125648</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
@@ -9220,6 +9778,12 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="E479" t="n">
+        <v>1.057828295156404</v>
+      </c>
+      <c r="F479" t="n">
+        <v>1.109984786431736</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
@@ -9239,6 +9803,12 @@
         <is>
           <t>ultimate</t>
         </is>
+      </c>
+      <c r="E480" t="n">
+        <v>1</v>
+      </c>
+      <c r="F480" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="481">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>1.125</v>
+        <v>0.5324901793116744</v>
       </c>
       <c r="F392" s="2" t="n">
-        <v>1.375</v>
+        <v>0.4866262989023714</v>
       </c>
     </row>
     <row r="393">
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="E393" s="2" t="n">
-        <v>1.25</v>
+        <v>0.5685766072036965</v>
       </c>
       <c r="F393" s="2" t="n">
-        <v>1.75</v>
+        <v>0.5893697628939644</v>
       </c>
     </row>
     <row r="394">
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="E394" s="2" t="n">
-        <v>1.375</v>
+        <v>0.7330769879429946</v>
       </c>
       <c r="F394" s="2" t="n">
-        <v>2.125</v>
+        <v>0.8814634834042079</v>
       </c>
     </row>
     <row r="395">
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>1.5</v>
+        <v>1.033966733686373</v>
       </c>
       <c r="F395" s="2" t="n">
-        <v>2.5</v>
+        <v>1.452249478385389</v>
       </c>
     </row>
     <row r="396">
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>1.625</v>
+        <v>1.53731829326964</v>
       </c>
       <c r="F396" s="2" t="n">
-        <v>2.875</v>
+        <v>2.529921892018751</v>
       </c>
     </row>
     <row r="397">
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="E397" s="2" t="n">
-        <v>1.75</v>
+        <v>2.366494402833543</v>
       </c>
       <c r="F397" s="2" t="n">
-        <v>3.25</v>
+        <v>4.570446168006661</v>
       </c>
     </row>
     <row r="398">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>1.875</v>
+        <v>3.733702808621944</v>
       </c>
       <c r="F398" s="2" t="n">
-        <v>3.625</v>
+        <v>8.470668656818301</v>
       </c>
     </row>
     <row r="399">
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F399" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="400">
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="E400" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F400" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="401">
@@ -7751,10 +7751,10 @@
         </is>
       </c>
       <c r="E401" s="2" t="n">
-        <v>2.25</v>
+        <v>3.478938441688168</v>
       </c>
       <c r="F401" s="2" t="n">
-        <v>4.5</v>
+        <v>8.826387079624727</v>
       </c>
     </row>
     <row r="402">
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>2.5</v>
+        <v>3.259663030130004</v>
       </c>
       <c r="F402" s="2" t="n">
-        <v>5</v>
+        <v>9.427003419616131</v>
       </c>
     </row>
     <row r="403">
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>2.75</v>
+        <v>3.575145032011695</v>
       </c>
       <c r="F403" s="2" t="n">
-        <v>5.5</v>
+        <v>12.1047694889808</v>
       </c>
     </row>
     <row r="404">
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>3</v>
+        <v>4.245160408187956</v>
       </c>
       <c r="F404" s="2" t="n">
-        <v>6</v>
+        <v>16.97957173522325</v>
       </c>
     </row>
     <row r="405">
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>3.25</v>
+        <v>5.28854526470762</v>
       </c>
       <c r="F405" s="2" t="n">
-        <v>6.5</v>
+        <v>25.09140256607924</v>
       </c>
     </row>
     <row r="406">
@@ -7881,10 +7881,10 @@
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>3.5</v>
+        <v>6.803814155506166</v>
       </c>
       <c r="F406" s="2" t="n">
-        <v>7</v>
+        <v>38.37624408240584</v>
       </c>
     </row>
     <row r="407">
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="E407" s="2" t="n">
-        <v>3.75</v>
+        <v>8.957652652226891</v>
       </c>
       <c r="F407" s="2" t="n">
-        <v>7.5</v>
+        <v>60.14590712943249</v>
       </c>
     </row>
     <row r="408">
@@ -7933,10 +7933,10 @@
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F408" s="2" t="n">
-        <v>8</v>
+        <v>96</v>
       </c>
     </row>
     <row r="409">
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="E409" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F409" s="2" t="n">
-        <v>8</v>
+        <v>96</v>
       </c>
     </row>
     <row r="410">
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>3.875</v>
+        <v>6.065080688320603</v>
       </c>
       <c r="F410" s="2" t="n">
-        <v>7.75</v>
+        <v>35.59654231167815</v>
       </c>
     </row>
     <row r="411">
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>3.75</v>
+        <v>4.953616586983959</v>
       </c>
       <c r="F411" s="2" t="n">
-        <v>7.5</v>
+        <v>25.55477753400599</v>
       </c>
     </row>
     <row r="412">
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>3.625</v>
+        <v>4.735907262666692</v>
       </c>
       <c r="F412" s="2" t="n">
-        <v>7.25</v>
+        <v>22.05609168050223</v>
       </c>
     </row>
     <row r="413">
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>3.5</v>
+        <v>4.901889008840915</v>
       </c>
       <c r="F413" s="2" t="n">
-        <v>7</v>
+        <v>20.79564340114026</v>
       </c>
     </row>
     <row r="414">
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>3.375</v>
+        <v>5.323109957194588</v>
       </c>
       <c r="F414" s="2" t="n">
-        <v>6.75</v>
+        <v>20.65590191253872</v>
       </c>
     </row>
     <row r="415">
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>3.25</v>
+        <v>5.969548666013317</v>
       </c>
       <c r="F415" s="2" t="n">
-        <v>6.5</v>
+        <v>21.2351477360025</v>
       </c>
     </row>
     <row r="416">
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>3.125</v>
+        <v>6.850828815107059</v>
       </c>
       <c r="F416" s="2" t="n">
-        <v>6.25</v>
+        <v>22.3703352813583</v>
       </c>
     </row>
     <row r="417">
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F417" s="2" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="418">
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F418" s="2" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="419">
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>3.375</v>
+        <v>5.058412362836491</v>
       </c>
       <c r="F419" s="2" t="n">
-        <v>6.75</v>
+        <v>14.2268552436008</v>
       </c>
     </row>
     <row r="420">
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>3.75</v>
+        <v>5.168552623922572</v>
       </c>
       <c r="F420" s="2" t="n">
-        <v>7.5</v>
+        <v>16.32804888590069</v>
       </c>
     </row>
     <row r="421">
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>4.125</v>
+        <v>6.181852654835754</v>
       </c>
       <c r="F421" s="2" t="n">
-        <v>8.25</v>
+        <v>22.52951460951273</v>
       </c>
     </row>
     <row r="422">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>4.5</v>
+        <v>8.004751231611612</v>
       </c>
       <c r="F422" s="2" t="n">
-        <v>9</v>
+        <v>33.9591434704465</v>
       </c>
     </row>
     <row r="423">
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>4.875</v>
+        <v>10.87473567718933</v>
       </c>
       <c r="F423" s="2" t="n">
-        <v>9.75</v>
+        <v>53.92493348957762</v>
       </c>
     </row>
     <row r="424">
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>5.25</v>
+        <v>15.25680782244697</v>
       </c>
       <c r="F424" s="2" t="n">
-        <v>10.5</v>
+        <v>88.62613940585517</v>
       </c>
     </row>
     <row r="425">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>5.625</v>
+        <v>21.90454319924028</v>
       </c>
       <c r="F425" s="2" t="n">
-        <v>11.25</v>
+        <v>149.2588624793426</v>
       </c>
     </row>
     <row r="426">
@@ -8401,10 +8401,10 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F426" s="2" t="n">
-        <v>12</v>
+        <v>256</v>
       </c>
     </row>
     <row r="427">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F427" s="2" t="n">
-        <v>12</v>
+        <v>256</v>
       </c>
     </row>
     <row r="428">
@@ -8453,10 +8453,10 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>6.25</v>
+        <v>19.79125080161339</v>
       </c>
       <c r="F428" s="2" t="n">
-        <v>12.5</v>
+        <v>159.4681191773176</v>
       </c>
     </row>
     <row r="429">
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>6.5</v>
+        <v>18.62815390545874</v>
       </c>
       <c r="F429" s="2" t="n">
-        <v>13</v>
+        <v>157.3939522338765</v>
       </c>
     </row>
     <row r="430">
@@ -8505,10 +8505,10 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>6.75</v>
+        <v>20.30258310625938</v>
       </c>
       <c r="F430" s="2" t="n">
-        <v>13.5</v>
+        <v>181.2205985098322</v>
       </c>
     </row>
     <row r="431">
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>7</v>
+        <v>23.86341635273138</v>
       </c>
       <c r="F431" s="2" t="n">
-        <v>14</v>
+        <v>225.6220294016744</v>
       </c>
     </row>
     <row r="432">
@@ -8557,10 +8557,10 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>7.25</v>
+        <v>29.37418126443648</v>
       </c>
       <c r="F432" s="2" t="n">
-        <v>14.5</v>
+        <v>294.5450257663789</v>
       </c>
     </row>
     <row r="433">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>7.5</v>
+        <v>37.30257282907881</v>
       </c>
       <c r="F433" s="2" t="n">
-        <v>15</v>
+        <v>396.9735342831585</v>
       </c>
     </row>
     <row r="434">
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>7.75</v>
+        <v>48.44769535919042</v>
       </c>
       <c r="F434" s="2" t="n">
-        <v>15.5</v>
+        <v>547.4133448621855</v>
       </c>
     </row>
     <row r="435">
@@ -8635,10 +8635,10 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="F435" s="2" t="n">
-        <v>16</v>
+        <v>768</v>
       </c>
     </row>
     <row r="436">
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="F436" s="2" t="n">
-        <v>16</v>
+        <v>768</v>
       </c>
     </row>
     <row r="437">
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>7.75</v>
+        <v>32.10911954299499</v>
       </c>
       <c r="F437" s="2" t="n">
-        <v>15.5</v>
+        <v>333.3389504130951</v>
       </c>
     </row>
     <row r="438">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="E438" s="2" t="n">
-        <v>7.5</v>
+        <v>24.51602926425373</v>
       </c>
       <c r="F438" s="2" t="n">
-        <v>15</v>
+        <v>229.2404061781276</v>
       </c>
     </row>
     <row r="439">
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>7.25</v>
+        <v>21.67488338600252</v>
       </c>
       <c r="F439" s="2" t="n">
-        <v>14.5</v>
+        <v>183.9084252597998</v>
       </c>
     </row>
     <row r="440">
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>7</v>
+        <v>20.66632478255037</v>
       </c>
       <c r="F440" s="2" t="n">
-        <v>14</v>
+        <v>159.5388669749946</v>
       </c>
     </row>
     <row r="441">
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>6.75</v>
+        <v>20.63581193306492</v>
       </c>
       <c r="F441" s="2" t="n">
-        <v>13.5</v>
+        <v>145.1201210115109</v>
       </c>
     </row>
     <row r="442">
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>6.5</v>
+        <v>21.25786950161368</v>
       </c>
       <c r="F442" s="2" t="n">
-        <v>13</v>
+        <v>136.2788404861893</v>
       </c>
     </row>
     <row r="443">
@@ -8843,10 +8843,10 @@
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>6.25</v>
+        <v>22.3964523925201</v>
       </c>
       <c r="F443" s="2" t="n">
-        <v>12.5</v>
+        <v>130.9402582709814</v>
       </c>
     </row>
     <row r="444">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F444" s="2" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
     </row>
     <row r="445">
@@ -8895,10 +8895,10 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F445" s="2" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
     </row>
     <row r="446">
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>6.5</v>
+        <v>16.77956111598912</v>
       </c>
       <c r="F446" s="2" t="n">
-        <v>13</v>
+        <v>94.82031097088398</v>
       </c>
     </row>
     <row r="447">
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>7</v>
+        <v>17.8534957240967</v>
       </c>
       <c r="F447" s="2" t="n">
-        <v>14</v>
+        <v>111.2943309423256</v>
       </c>
     </row>
     <row r="448">
@@ -8973,10 +8973,10 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>7.5</v>
+        <v>21.9963608110104</v>
       </c>
       <c r="F448" s="2" t="n">
-        <v>15</v>
+        <v>152.3877516570505</v>
       </c>
     </row>
     <row r="449">
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>8</v>
+        <v>29.22659679188993</v>
       </c>
       <c r="F449" s="2" t="n">
-        <v>16</v>
+        <v>225.6220294016744</v>
       </c>
     </row>
     <row r="450">
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>8.5</v>
+        <v>40.66843793549465</v>
       </c>
       <c r="F450" s="2" t="n">
-        <v>17</v>
+        <v>350.2750403300375</v>
       </c>
     </row>
     <row r="451">
@@ -9051,10 +9051,10 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>9</v>
+        <v>58.38168153185204</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>18</v>
+        <v>561.4053560864236</v>
       </c>
     </row>
     <row r="452">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>9.5</v>
+        <v>85.7150389380769</v>
       </c>
       <c r="F452" s="2" t="n">
-        <v>19</v>
+        <v>920.6358387133145</v>
       </c>
     </row>
     <row r="453">
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="F453" s="2" t="n">
-        <v>20</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="454">
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="F454" s="2" t="n">
-        <v>20</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="455">
@@ -9155,10 +9155,10 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>10.25</v>
+        <v>72.59462802062869</v>
       </c>
       <c r="F455" s="2" t="n">
-        <v>20.5</v>
+        <v>701.3381552236845</v>
       </c>
     </row>
     <row r="456">
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>10.5</v>
+        <v>62.65739136757894</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>21</v>
+        <v>507.3924255641834</v>
       </c>
     </row>
     <row r="457">
@@ -9207,10 +9207,10 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>10.75</v>
+        <v>62.62172690043518</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>21.5</v>
+        <v>428.2189118107935</v>
       </c>
     </row>
     <row r="458">
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>11</v>
+        <v>67.49593410117721</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>22</v>
+        <v>390.7888182304993</v>
       </c>
     </row>
     <row r="459">
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>11.25</v>
+        <v>76.18720029841968</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>22.5</v>
+        <v>373.9509702999416</v>
       </c>
     </row>
     <row r="460">
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>11.5</v>
+        <v>88.7209700324954</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>23</v>
+        <v>369.4254999388413</v>
       </c>
     </row>
     <row r="461">
@@ -9311,10 +9311,10 @@
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>11.75</v>
+        <v>105.6651728380158</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>23.5</v>
+        <v>373.4075033600386</v>
       </c>
     </row>
     <row r="462">
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="F462" s="2" t="n">
-        <v>24</v>
+        <v>384</v>
       </c>
     </row>
     <row r="463">
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="F463" s="2" t="n">
-        <v>24</v>
+        <v>384</v>
       </c>
     </row>
     <row r="464">
@@ -9389,10 +9389,10 @@
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>12.5</v>
+        <v>55.9781105999381</v>
       </c>
       <c r="F464" s="2" t="n">
-        <v>25</v>
+        <v>152.8365826432048</v>
       </c>
     </row>
     <row r="465">
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>13</v>
+        <v>37.25630781091748</v>
       </c>
       <c r="F465" s="2" t="n">
-        <v>26</v>
+        <v>96.3837178932465</v>
       </c>
     </row>
     <row r="466">
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>13.5</v>
+        <v>28.71218838007889</v>
       </c>
       <c r="F466" s="2" t="n">
-        <v>27</v>
+        <v>70.90639107984764</v>
       </c>
     </row>
     <row r="467">
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>14</v>
+        <v>23.86341635273137</v>
       </c>
       <c r="F467" s="2" t="n">
-        <v>28</v>
+        <v>56.40550735041862</v>
       </c>
     </row>
     <row r="468">
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>14.5</v>
+        <v>20.77068276388587</v>
       </c>
       <c r="F468" s="2" t="n">
-        <v>29</v>
+        <v>47.04937827586711</v>
       </c>
     </row>
     <row r="469">
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>15</v>
+        <v>18.65128641453941</v>
       </c>
       <c r="F469" s="2" t="n">
-        <v>30</v>
+        <v>40.51594168262429</v>
       </c>
     </row>
     <row r="470">
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>15.5</v>
+        <v>17.12884696067179</v>
       </c>
       <c r="F470" s="2" t="n">
-        <v>31</v>
+        <v>35.69784104042281</v>
       </c>
     </row>
     <row r="471">
@@ -9596,10 +9596,10 @@
           <t>elite</t>
         </is>
       </c>
-      <c r="E472" t="n">
+      <c r="E472" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F472" t="n">
+      <c r="F472" s="2" t="n">
         <v>32</v>
       </c>
     </row>
@@ -9622,11 +9622,11 @@
           <t>elite</t>
         </is>
       </c>
-      <c r="E473" t="n">
-        <v>3.391110215352182</v>
-      </c>
-      <c r="F473" t="n">
-        <v>5.605023522991008</v>
+      <c r="E473" s="2" t="n">
+        <v>3.235952807469516</v>
+      </c>
+      <c r="F473" s="2" t="n">
+        <v>5.588455157324755</v>
       </c>
     </row>
     <row r="474">
@@ -9648,11 +9648,11 @@
           <t>elite</t>
         </is>
       </c>
-      <c r="E474" t="n">
-        <v>2.127461929935275</v>
-      </c>
-      <c r="F474" t="n">
-        <v>3.156649161856778</v>
+      <c r="E474" s="2" t="n">
+        <v>1.97621037190018</v>
+      </c>
+      <c r="F474" s="2" t="n">
+        <v>3.140985228833101</v>
       </c>
     </row>
     <row r="475">
@@ -9674,11 +9674,11 @@
           <t>elite</t>
         </is>
       </c>
-      <c r="E475" t="n">
-        <v>1.648015526593405</v>
-      </c>
-      <c r="F475" t="n">
-        <v>2.236366506256873</v>
+      <c r="E475" s="2" t="n">
+        <v>1.513142604888616</v>
+      </c>
+      <c r="F475" s="2" t="n">
+        <v>2.222770152728302</v>
       </c>
     </row>
     <row r="476">
@@ -9700,11 +9700,11 @@
           <t>elite</t>
         </is>
       </c>
-      <c r="E476" t="n">
-        <v>1.395646246917129</v>
-      </c>
-      <c r="F476" t="n">
-        <v>1.753846098162387</v>
+      <c r="E476" s="2" t="n">
+        <v>1.282015940389144</v>
+      </c>
+      <c r="F476" s="2" t="n">
+        <v>1.742688300058309</v>
       </c>
     </row>
     <row r="477">
@@ -9726,11 +9726,11 @@
           <t>boss</t>
         </is>
       </c>
-      <c r="E477" t="n">
-        <v>1.239919029849584</v>
-      </c>
-      <c r="F477" t="n">
-        <v>1.456750492140449</v>
+      <c r="E477" s="2" t="n">
+        <v>1.150725459593069</v>
+      </c>
+      <c r="F477" s="2" t="n">
+        <v>1.44821976633041</v>
       </c>
     </row>
     <row r="478">
@@ -9752,11 +9752,11 @@
           <t>boss</t>
         </is>
       </c>
-      <c r="E478" t="n">
-        <v>1.134242642197337</v>
-      </c>
-      <c r="F478" t="n">
-        <v>1.255422883125648</v>
+      <c r="E478" s="2" t="n">
+        <v>1.072187376389279</v>
+      </c>
+      <c r="F478" s="2" t="n">
+        <v>1.249643672739781</v>
       </c>
     </row>
     <row r="479">
@@ -9778,11 +9778,11 @@
           <t>boss</t>
         </is>
       </c>
-      <c r="E479" t="n">
-        <v>1.057828295156404</v>
-      </c>
-      <c r="F479" t="n">
-        <v>1.109984786431736</v>
+      <c r="E479" s="2" t="n">
+        <v>1.025492519529902</v>
+      </c>
+      <c r="F479" s="2" t="n">
+        <v>1.107053703990455</v>
       </c>
     </row>
     <row r="480">
@@ -9804,10 +9804,10 @@
           <t>ultimate</t>
         </is>
       </c>
-      <c r="E480" t="n">
+      <c r="E480" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F480" t="n">
+      <c r="F480" s="2" t="n">
         <v>1</v>
       </c>
     </row>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>0.5324901793116744</v>
+        <v>0.5676004044101436</v>
       </c>
       <c r="F392" s="2" t="n">
-        <v>0.4866262989023714</v>
+        <v>0.5306697418713109</v>
       </c>
     </row>
     <row r="393">
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="E393" s="2" t="n">
-        <v>0.5685766072036965</v>
+        <v>0.6460277524252244</v>
       </c>
       <c r="F393" s="2" t="n">
-        <v>0.5893697628939644</v>
+        <v>0.700882715400969</v>
       </c>
     </row>
     <row r="394">
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="E394" s="2" t="n">
-        <v>0.7330769879429946</v>
+        <v>0.8878566826756916</v>
       </c>
       <c r="F394" s="2" t="n">
-        <v>0.8814634834042079</v>
+        <v>1.143116711259041</v>
       </c>
     </row>
     <row r="395">
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>1.033966733686373</v>
+        <v>1.3348453133666</v>
       </c>
       <c r="F395" s="2" t="n">
-        <v>1.452249478385389</v>
+        <v>2.05379090828187</v>
       </c>
     </row>
     <row r="396">
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>1.53731829326964</v>
+        <v>2.115530366424058</v>
       </c>
       <c r="F396" s="2" t="n">
-        <v>2.529921892018751</v>
+        <v>3.901672929307857</v>
       </c>
     </row>
     <row r="397">
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="E397" s="2" t="n">
-        <v>2.366494402833543</v>
+        <v>3.471299164982791</v>
       </c>
       <c r="F397" s="2" t="n">
-        <v>4.570446168006661</v>
+        <v>7.686543597573756</v>
       </c>
     </row>
     <row r="398">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>3.733702808621944</v>
+        <v>5.837910093709082</v>
       </c>
       <c r="F398" s="2" t="n">
-        <v>8.470668656818301</v>
+        <v>15.53527481389893</v>
       </c>
     </row>
     <row r="399">
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F399" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="400">
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="E400" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F400" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="401">
@@ -7751,10 +7751,10 @@
         </is>
       </c>
       <c r="E401" s="2" t="n">
-        <v>3.478938441688168</v>
+        <v>6.70562466700849</v>
       </c>
       <c r="F401" s="2" t="n">
-        <v>8.826387079624727</v>
+        <v>20.99280462971563</v>
       </c>
     </row>
     <row r="402">
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>3.259663030130004</v>
+        <v>7.266226829631691</v>
       </c>
       <c r="F402" s="2" t="n">
-        <v>9.427003419616131</v>
+        <v>26.66359217711736</v>
       </c>
     </row>
     <row r="403">
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>3.575145032011695</v>
+        <v>9.216661891152189</v>
       </c>
       <c r="F403" s="2" t="n">
-        <v>12.1047694889808</v>
+        <v>40.71542908302596</v>
       </c>
     </row>
     <row r="404">
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>4.245160408187956</v>
+        <v>12.65662299746536</v>
       </c>
       <c r="F404" s="2" t="n">
-        <v>16.97957173522325</v>
+        <v>67.91828694089298</v>
       </c>
     </row>
     <row r="405">
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>5.28854526470762</v>
+        <v>18.23491368420642</v>
       </c>
       <c r="F405" s="2" t="n">
-        <v>25.09140256607924</v>
+        <v>119.3554978279158</v>
       </c>
     </row>
     <row r="406">
@@ -7881,10 +7881,10 @@
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>6.803814155506166</v>
+        <v>27.13086721357822</v>
       </c>
       <c r="F406" s="2" t="n">
-        <v>38.37624408240584</v>
+        <v>217.0888194171143</v>
       </c>
     </row>
     <row r="407">
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="E407" s="2" t="n">
-        <v>8.957652652226891</v>
+        <v>41.30942962945242</v>
       </c>
       <c r="F407" s="2" t="n">
-        <v>60.14590712943249</v>
+        <v>404.6118215785808</v>
       </c>
     </row>
     <row r="408">
@@ -7933,10 +7933,10 @@
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F408" s="2" t="n">
-        <v>96</v>
+        <v>768</v>
       </c>
     </row>
     <row r="409">
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="E409" s="2" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F409" s="2" t="n">
-        <v>96</v>
+        <v>768</v>
       </c>
     </row>
     <row r="410">
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>6.065080688320603</v>
+        <v>28.6147014703964</v>
       </c>
       <c r="F410" s="2" t="n">
-        <v>35.59654231167815</v>
+        <v>239.4640386025386</v>
       </c>
     </row>
     <row r="411">
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>4.953616586983959</v>
+        <v>20.67421049569029</v>
       </c>
       <c r="F411" s="2" t="n">
-        <v>25.55477753400599</v>
+        <v>144.5596518880741</v>
       </c>
     </row>
     <row r="412">
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>4.735907262666692</v>
+        <v>17.4849197301217</v>
       </c>
       <c r="F412" s="2" t="n">
-        <v>22.05609168050223</v>
+        <v>104.9170446224223</v>
       </c>
     </row>
     <row r="413">
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>4.901889008840915</v>
+        <v>16.00950246322323</v>
       </c>
       <c r="F413" s="2" t="n">
-        <v>20.79564340114026</v>
+        <v>83.18257360456101</v>
       </c>
     </row>
     <row r="414">
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>5.323109957194588</v>
+        <v>15.37919868190371</v>
       </c>
       <c r="F414" s="2" t="n">
-        <v>20.65590191253872</v>
+        <v>69.47789548834463</v>
       </c>
     </row>
     <row r="415">
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>5.969548666013317</v>
+        <v>15.25680782244698</v>
       </c>
       <c r="F415" s="2" t="n">
-        <v>21.2351477360025</v>
+        <v>60.06206785450212</v>
       </c>
     </row>
     <row r="416">
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>6.850828815107059</v>
+        <v>15.48885103497648</v>
       </c>
       <c r="F416" s="2" t="n">
-        <v>22.3703352813583</v>
+        <v>53.20592376317538</v>
       </c>
     </row>
     <row r="417">
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F417" s="2" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="418">
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F418" s="2" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="419">
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>5.058412362836491</v>
+        <v>11.60604854400072</v>
       </c>
       <c r="F419" s="2" t="n">
-        <v>14.2268552436008</v>
+        <v>32.64217322391502</v>
       </c>
     </row>
     <row r="420">
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>5.168552623922572</v>
+        <v>13.60439558584383</v>
       </c>
       <c r="F420" s="2" t="n">
-        <v>16.32804888590069</v>
+        <v>42.97784164190359</v>
       </c>
     </row>
     <row r="421">
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>6.181852654835754</v>
+        <v>18.6667673852378</v>
       </c>
       <c r="F421" s="2" t="n">
-        <v>22.52951460951273</v>
+        <v>68.03028671172113</v>
       </c>
     </row>
     <row r="422">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>8.004751231611612</v>
+        <v>27.72927167020172</v>
       </c>
       <c r="F422" s="2" t="n">
-        <v>33.9591434704465</v>
+        <v>117.6379237446685</v>
       </c>
     </row>
     <row r="423">
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>10.87473567718933</v>
+        <v>43.21648985876418</v>
       </c>
       <c r="F423" s="2" t="n">
-        <v>53.92493348957762</v>
+        <v>214.2991250973733</v>
       </c>
     </row>
     <row r="424">
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>15.25680782244697</v>
+        <v>69.55600219574146</v>
       </c>
       <c r="F424" s="2" t="n">
-        <v>88.62613940585517</v>
+        <v>404.0478204126096</v>
       </c>
     </row>
     <row r="425">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>21.90454319924028</v>
+        <v>114.5632417799229</v>
       </c>
       <c r="F425" s="2" t="n">
-        <v>149.2588624793426</v>
+        <v>780.6407554123412</v>
       </c>
     </row>
     <row r="426">
@@ -8401,10 +8401,10 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="F426" s="2" t="n">
-        <v>256</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="427">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="F427" s="2" t="n">
-        <v>256</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="428">
@@ -8453,10 +8453,10 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>19.79125080161339</v>
+        <v>123.0954030924953</v>
       </c>
       <c r="F428" s="2" t="n">
-        <v>159.4681191773176</v>
+        <v>956.8087150639058</v>
       </c>
     </row>
     <row r="429">
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>18.62815390545874</v>
+        <v>120.1035244331235</v>
       </c>
       <c r="F429" s="2" t="n">
-        <v>157.3939522338765</v>
+        <v>944.3637134032589</v>
       </c>
     </row>
     <row r="430">
@@ -8505,10 +8505,10 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>20.30258310625938</v>
+        <v>135.692103049277</v>
       </c>
       <c r="F430" s="2" t="n">
-        <v>181.2205985098322</v>
+        <v>1087.323591058993</v>
       </c>
     </row>
     <row r="431">
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>23.86341635273138</v>
+        <v>165.330598260403</v>
       </c>
       <c r="F431" s="2" t="n">
-        <v>225.6220294016744</v>
+        <v>1353.732176410047</v>
       </c>
     </row>
     <row r="432">
@@ -8557,10 +8557,10 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>29.37418126443648</v>
+        <v>210.9617557624764</v>
       </c>
       <c r="F432" s="2" t="n">
-        <v>294.5450257663789</v>
+        <v>1767.270154598273</v>
       </c>
     </row>
     <row r="433">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>37.30257282907881</v>
+        <v>277.7116442540056</v>
       </c>
       <c r="F433" s="2" t="n">
-        <v>396.9735342831585</v>
+        <v>2381.841205698951</v>
       </c>
     </row>
     <row r="434">
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>48.44769535919042</v>
+        <v>373.8916510707061</v>
       </c>
       <c r="F434" s="2" t="n">
-        <v>547.4133448621855</v>
+        <v>3284.480069173113</v>
       </c>
     </row>
     <row r="435">
@@ -8635,10 +8635,10 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>64</v>
+        <v>512</v>
       </c>
       <c r="F435" s="2" t="n">
-        <v>768</v>
+        <v>4608</v>
       </c>
     </row>
     <row r="436">
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>64</v>
+        <v>512</v>
       </c>
       <c r="F436" s="2" t="n">
-        <v>768</v>
+        <v>4608</v>
       </c>
     </row>
     <row r="437">
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>32.10911954299499</v>
+        <v>223.9124423997523</v>
       </c>
       <c r="F437" s="2" t="n">
-        <v>333.3389504130951</v>
+        <v>1834.038991718458</v>
       </c>
     </row>
     <row r="438">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="E438" s="2" t="n">
-        <v>24.51602926425373</v>
+        <v>149.0252312436699</v>
       </c>
       <c r="F438" s="2" t="n">
-        <v>229.2404061781276</v>
+        <v>1156.604614718958</v>
       </c>
     </row>
     <row r="439">
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>21.67488338600252</v>
+        <v>114.8487535203156</v>
       </c>
       <c r="F439" s="2" t="n">
-        <v>183.9084252597998</v>
+        <v>850.8766929581715</v>
       </c>
     </row>
     <row r="440">
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>20.66632478255037</v>
+        <v>95.4536654109255</v>
       </c>
       <c r="F440" s="2" t="n">
-        <v>159.5388669749946</v>
+        <v>676.8660882050235</v>
       </c>
     </row>
     <row r="441">
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>20.63581193306492</v>
+        <v>83.08273105554346</v>
       </c>
       <c r="F441" s="2" t="n">
-        <v>145.1201210115109</v>
+        <v>564.5925393104054</v>
       </c>
     </row>
     <row r="442">
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>21.25786950161368</v>
+        <v>74.60514565815761</v>
       </c>
       <c r="F442" s="2" t="n">
-        <v>136.2788404861893</v>
+        <v>486.1913001914915</v>
       </c>
     </row>
     <row r="443">
@@ -8843,10 +8843,10 @@
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>22.3964523925201</v>
+        <v>68.51538784268716</v>
       </c>
       <c r="F443" s="2" t="n">
-        <v>130.9402582709814</v>
+        <v>428.3740924850737</v>
       </c>
     </row>
     <row r="444">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="F444" s="2" t="n">
-        <v>128</v>
+        <v>384.0000000000001</v>
       </c>
     </row>
     <row r="445">
@@ -8895,10 +8895,10 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="F445" s="2" t="n">
-        <v>128</v>
+        <v>384.0000000000001</v>
       </c>
     </row>
     <row r="446">
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>16.77956111598912</v>
+        <v>51.3321537511015</v>
       </c>
       <c r="F446" s="2" t="n">
-        <v>94.82031097088398</v>
+        <v>294.8763703041248</v>
       </c>
     </row>
     <row r="447">
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>17.8534957240967</v>
+        <v>62.65739136757894</v>
       </c>
       <c r="F447" s="2" t="n">
-        <v>111.2943309423256</v>
+        <v>358.7806248391246</v>
       </c>
     </row>
     <row r="448">
@@ -8973,10 +8973,10 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>21.9963608110104</v>
+        <v>88.56049548181952</v>
       </c>
       <c r="F448" s="2" t="n">
-        <v>152.3877516570505</v>
+        <v>509.2409767041184</v>
       </c>
     </row>
     <row r="449">
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>29.22659679188993</v>
+        <v>134.9918682023545</v>
       </c>
       <c r="F449" s="2" t="n">
-        <v>225.6220294016744</v>
+        <v>781.5776364609985</v>
       </c>
     </row>
     <row r="450">
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>40.66843793549465</v>
+        <v>215.4899438825213</v>
       </c>
       <c r="F450" s="2" t="n">
-        <v>350.2750403300375</v>
+        <v>1257.816121623477</v>
       </c>
     </row>
     <row r="451">
@@ -9051,10 +9051,10 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>58.38168153185204</v>
+        <v>354.8838801299817</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>561.4053560864236</v>
+        <v>2089.786209199881</v>
       </c>
     </row>
     <row r="452">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>85.7150389380769</v>
+        <v>597.7324819920763</v>
       </c>
       <c r="F452" s="2" t="n">
-        <v>920.6358387133145</v>
+        <v>3552.470878329283</v>
       </c>
     </row>
     <row r="453">
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>128</v>
+        <v>1024</v>
       </c>
       <c r="F453" s="2" t="n">
-        <v>1536</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="454">
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>128</v>
+        <v>1024</v>
       </c>
       <c r="F454" s="2" t="n">
-        <v>1536</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="455">
@@ -9155,10 +9155,10 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>72.59462802062869</v>
+        <v>488.3564997537882</v>
       </c>
       <c r="F455" s="2" t="n">
-        <v>701.3381552236845</v>
+        <v>2445.385322291276</v>
       </c>
     </row>
     <row r="456">
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>62.65739136757894</v>
+        <v>354.4437306197962</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>507.3924255641834</v>
+        <v>1542.139486291944</v>
       </c>
     </row>
     <row r="457">
@@ -9207,10 +9207,10 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>62.62172690043518</v>
+        <v>297.8808127350192</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>428.2189118107935</v>
+        <v>1134.502257277562</v>
       </c>
     </row>
     <row r="458">
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>67.49593410117721</v>
+        <v>269.9837364047089</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>390.7888182304993</v>
+        <v>902.4881176066978</v>
       </c>
     </row>
     <row r="459">
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>76.18720029841968</v>
+        <v>256.2621744766313</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>373.9509702999416</v>
+        <v>752.7900524138739</v>
       </c>
     </row>
     <row r="460">
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>88.7209700324954</v>
+        <v>250.9407981737039</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>369.4254999388413</v>
+        <v>648.2550669219886</v>
       </c>
     </row>
     <row r="461">
@@ -9311,10 +9311,10 @@
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>105.6651728380158</v>
+        <v>251.3155506939212</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>373.4075033600386</v>
+        <v>571.1654566467648</v>
       </c>
     </row>
     <row r="462">
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F462" s="2" t="n">
-        <v>384</v>
+        <v>512</v>
       </c>
     </row>
     <row r="463">
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F463" s="2" t="n">
-        <v>384</v>
+        <v>512</v>
       </c>
     </row>
     <row r="464">
@@ -9389,10 +9389,10 @@
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>55.9781105999381</v>
+        <v>108.0017740826299</v>
       </c>
       <c r="F464" s="2" t="n">
-        <v>152.8365826432048</v>
+        <v>202.144749121721</v>
       </c>
     </row>
     <row r="465">
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>37.25630781091748</v>
+        <v>69.34180216208662</v>
       </c>
       <c r="F465" s="2" t="n">
-        <v>96.3837178932465</v>
+        <v>126.4547741947134</v>
       </c>
     </row>
     <row r="466">
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>28.71218838007889</v>
+        <v>51.55185107897695</v>
       </c>
       <c r="F466" s="2" t="n">
-        <v>70.90639107984764</v>
+        <v>92.28122413600921</v>
       </c>
     </row>
     <row r="467">
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>23.86341635273137</v>
+        <v>41.33264956510073</v>
       </c>
       <c r="F467" s="2" t="n">
-        <v>56.40550735041862</v>
+        <v>72.81919686751712</v>
       </c>
     </row>
     <row r="468">
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>20.77068276388587</v>
+        <v>34.70516056072824</v>
       </c>
       <c r="F468" s="2" t="n">
-        <v>47.04937827586711</v>
+        <v>60.25244476556771</v>
       </c>
     </row>
     <row r="469">
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>18.65128641453941</v>
+        <v>30.06316735633945</v>
       </c>
       <c r="F469" s="2" t="n">
-        <v>40.51594168262429</v>
+        <v>51.46869197815998</v>
       </c>
     </row>
     <row r="470">
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>17.12884696067179</v>
+        <v>26.63402053600463</v>
       </c>
       <c r="F470" s="2" t="n">
-        <v>35.69784104042281</v>
+        <v>44.98373942487196</v>
       </c>
     </row>
     <row r="471">
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F471" s="2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="472">
@@ -9597,10 +9597,10 @@
         </is>
       </c>
       <c r="E472" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F472" s="2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="473">
@@ -9623,10 +9623,10 @@
         </is>
       </c>
       <c r="E473" s="2" t="n">
-        <v>3.235952807469516</v>
+        <v>4.61404717992635</v>
       </c>
       <c r="F473" s="2" t="n">
-        <v>5.588455157324755</v>
+        <v>6.793413216515661</v>
       </c>
     </row>
     <row r="474">
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="E474" s="2" t="n">
-        <v>1.97621037190018</v>
+        <v>2.678561477405338</v>
       </c>
       <c r="F474" s="2" t="n">
-        <v>3.140985228833101</v>
+        <v>3.713200530214782</v>
       </c>
     </row>
     <row r="475">
@@ -9675,10 +9675,10 @@
         </is>
       </c>
       <c r="E475" s="2" t="n">
-        <v>1.513142604888616</v>
+        <v>1.949561306027979</v>
       </c>
       <c r="F475" s="2" t="n">
-        <v>2.222770152728302</v>
+        <v>2.555426031861377</v>
       </c>
     </row>
     <row r="476">
@@ -9701,10 +9701,10 @@
         </is>
       </c>
       <c r="E476" s="2" t="n">
-        <v>1.282015940389144</v>
+        <v>1.570142448033869</v>
       </c>
       <c r="F476" s="2" t="n">
-        <v>1.742688300058309</v>
+        <v>1.948384751261965</v>
       </c>
     </row>
     <row r="477">
@@ -9727,10 +9727,10 @@
         </is>
       </c>
       <c r="E477" s="2" t="n">
-        <v>1.150725459593069</v>
+        <v>1.339695023226408</v>
       </c>
       <c r="F477" s="2" t="n">
-        <v>1.44821976633041</v>
+        <v>1.574619863309849</v>
       </c>
     </row>
     <row r="478">
@@ -9753,10 +9753,10 @@
         </is>
       </c>
       <c r="E478" s="2" t="n">
-        <v>1.072187376389279</v>
+        <v>1.186570383980938</v>
       </c>
       <c r="F478" s="2" t="n">
-        <v>1.249643672739781</v>
+        <v>1.321337309095369</v>
       </c>
     </row>
     <row r="479">
@@ -9779,10 +9779,10 @@
         </is>
       </c>
       <c r="E479" s="2" t="n">
-        <v>1.025492519529902</v>
+        <v>1.078807368523075</v>
       </c>
       <c r="F479" s="2" t="n">
-        <v>1.107053703990455</v>
+        <v>1.138367375927505</v>
       </c>
     </row>
     <row r="480">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>0.5676004044101436</v>
+        <v>0.6027754510829806</v>
       </c>
       <c r="F392" s="2" t="n">
-        <v>0.5306697418713109</v>
+        <v>0.5600005631590167</v>
       </c>
     </row>
     <row r="393">
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="E393" s="2" t="n">
-        <v>0.6460277524252244</v>
+        <v>0.7285794139621287</v>
       </c>
       <c r="F393" s="2" t="n">
-        <v>0.700882715400969</v>
+        <v>0.7805012925108775</v>
       </c>
     </row>
     <row r="394">
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="E394" s="2" t="n">
-        <v>0.8878566826756916</v>
+        <v>1.06336276624705</v>
       </c>
       <c r="F394" s="2" t="n">
-        <v>1.143116711259041</v>
+        <v>1.343330850717981</v>
       </c>
     </row>
     <row r="395">
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>1.3348453133666</v>
+        <v>1.69778379120333</v>
       </c>
       <c r="F395" s="2" t="n">
-        <v>2.05379090828187</v>
+        <v>2.546905201566314</v>
       </c>
     </row>
     <row r="396">
@@ -7621,10 +7621,10 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>2.115530366424058</v>
+        <v>2.857482413024759</v>
       </c>
       <c r="F396" s="2" t="n">
-        <v>3.901672929307857</v>
+        <v>5.105891150979167</v>
       </c>
     </row>
     <row r="397">
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="E397" s="2" t="n">
-        <v>3.471299164982791</v>
+        <v>4.979310477016353</v>
       </c>
       <c r="F397" s="2" t="n">
-        <v>7.686543597573756</v>
+        <v>10.61490043353493</v>
       </c>
     </row>
     <row r="398">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>5.837910093709082</v>
+        <v>8.892982258863762</v>
       </c>
       <c r="F398" s="2" t="n">
-        <v>15.53527481389893</v>
+        <v>22.63955616989358</v>
       </c>
     </row>
     <row r="399">
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>10</v>
+        <v>16.17718246648805</v>
       </c>
       <c r="F399" s="2" t="n">
-        <v>32</v>
+        <v>49.21110139391978</v>
       </c>
     </row>
     <row r="400">
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="E400" s="2" t="n">
-        <v>10</v>
+        <v>16.17718246648805</v>
       </c>
       <c r="F400" s="2" t="n">
-        <v>32</v>
+        <v>49.21110139391978</v>
       </c>
     </row>
     <row r="401">
@@ -7751,10 +7751,10 @@
         </is>
       </c>
       <c r="E401" s="2" t="n">
-        <v>6.70562466700849</v>
+        <v>15.42909495998082</v>
       </c>
       <c r="F401" s="2" t="n">
-        <v>20.99280462971563</v>
+        <v>44.24628481726457</v>
       </c>
     </row>
     <row r="402">
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>7.266226829631691</v>
+        <v>23.77981594354123</v>
       </c>
       <c r="F402" s="2" t="n">
-        <v>26.66359217711736</v>
+        <v>77.02261237902138</v>
       </c>
     </row>
     <row r="403">
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>9.216661891152189</v>
+        <v>42.90140550832775</v>
       </c>
       <c r="F403" s="2" t="n">
-        <v>40.71542908302596</v>
+        <v>161.1951023061239</v>
       </c>
     </row>
     <row r="404">
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>12.65662299746536</v>
+        <v>83.79421474191265</v>
       </c>
       <c r="F404" s="2" t="n">
-        <v>67.91828694089298</v>
+        <v>368.5299510566441</v>
       </c>
     </row>
     <row r="405">
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>18.23491368420642</v>
+        <v>171.7110445842339</v>
       </c>
       <c r="F405" s="2" t="n">
-        <v>119.3554978279158</v>
+        <v>887.6090761267244</v>
       </c>
     </row>
     <row r="406">
@@ -7881,10 +7881,10 @@
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>27.13086721357822</v>
+        <v>363.3762351373805</v>
       </c>
       <c r="F406" s="2" t="n">
-        <v>217.0888194171143</v>
+        <v>2212.636144447598</v>
       </c>
     </row>
     <row r="407">
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="E407" s="2" t="n">
-        <v>41.30942962945242</v>
+        <v>786.9377343543295</v>
       </c>
       <c r="F407" s="2" t="n">
-        <v>404.6118215785808</v>
+        <v>5652.028628082166</v>
       </c>
     </row>
     <row r="408">
@@ -7933,10 +7933,10 @@
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>64</v>
+        <v>1734.081371631208</v>
       </c>
       <c r="F408" s="2" t="n">
-        <v>768</v>
+        <v>14703.48373037106</v>
       </c>
     </row>
     <row r="409">
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="E409" s="2" t="n">
-        <v>64</v>
+        <v>1734.081371631208</v>
       </c>
       <c r="F409" s="2" t="n">
-        <v>768</v>
+        <v>14703.48373037106</v>
       </c>
     </row>
     <row r="410">
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>28.6147014703964</v>
+        <v>815.9283346805465</v>
       </c>
       <c r="F410" s="2" t="n">
-        <v>239.4640386025386</v>
+        <v>4798.865672930985</v>
       </c>
     </row>
     <row r="411">
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>20.67421049569029</v>
+        <v>620.390339214493</v>
       </c>
       <c r="F411" s="2" t="n">
-        <v>144.5596518880741</v>
+        <v>3032.387168325816</v>
       </c>
     </row>
     <row r="412">
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>17.4849197301217</v>
+        <v>552.1702861222619</v>
       </c>
       <c r="F412" s="2" t="n">
-        <v>104.9170446224223</v>
+        <v>2303.683812768523</v>
       </c>
     </row>
     <row r="413">
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>16.00950246322323</v>
+        <v>532.0598915008038</v>
       </c>
       <c r="F413" s="2" t="n">
-        <v>83.18257360456101</v>
+        <v>1911.826339590628</v>
       </c>
     </row>
     <row r="414">
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>15.37919868190371</v>
+        <v>537.885318771933</v>
       </c>
       <c r="F414" s="2" t="n">
-        <v>69.47789548834463</v>
+        <v>1671.483170935145</v>
       </c>
     </row>
     <row r="415">
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>15.25680782244698</v>
+        <v>561.555849858323</v>
       </c>
       <c r="F415" s="2" t="n">
-        <v>60.06206785450212</v>
+        <v>1512.49831387441</v>
       </c>
     </row>
     <row r="416">
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>15.48885103497648</v>
+        <v>599.9592861488059</v>
       </c>
       <c r="F416" s="2" t="n">
-        <v>53.20592376317538</v>
+        <v>1402.470943645809</v>
       </c>
     </row>
     <row r="417">
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>16</v>
+        <v>652.2226194122828</v>
       </c>
       <c r="F417" s="2" t="n">
-        <v>48</v>
+        <v>1324.385409186241</v>
       </c>
     </row>
     <row r="418">
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>16</v>
+        <v>652.2226194122828</v>
       </c>
       <c r="F418" s="2" t="n">
-        <v>48</v>
+        <v>1324.385409186241</v>
       </c>
     </row>
     <row r="419">
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>11.60604854400072</v>
+        <v>694.9702902148998</v>
       </c>
       <c r="F419" s="2" t="n">
-        <v>32.64217322391502</v>
+        <v>1270.511559572846</v>
       </c>
     </row>
     <row r="420">
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>13.60439558584383</v>
+        <v>1196.649850021172</v>
       </c>
       <c r="F420" s="2" t="n">
-        <v>42.97784164190359</v>
+        <v>2359.774818971994</v>
       </c>
     </row>
     <row r="421">
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>18.6667673852378</v>
+        <v>2411.920213316881</v>
       </c>
       <c r="F421" s="2" t="n">
-        <v>68.03028671172113</v>
+        <v>5269.321145173129</v>
       </c>
     </row>
     <row r="422">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>27.72927167020172</v>
+        <v>5263.059343519646</v>
       </c>
       <c r="F422" s="2" t="n">
-        <v>117.6379237446685</v>
+        <v>12853.63972927639</v>
       </c>
     </row>
     <row r="423">
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>43.21648985876418</v>
+        <v>12049.11852611687</v>
       </c>
       <c r="F423" s="2" t="n">
-        <v>214.2991250973733</v>
+        <v>33031.29310677554</v>
       </c>
     </row>
     <row r="424">
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>69.55600219574146</v>
+        <v>28486.97812562146</v>
       </c>
       <c r="F424" s="2" t="n">
-        <v>404.0478204126096</v>
+        <v>87854.5688286629</v>
       </c>
     </row>
     <row r="425">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>114.5632417799229</v>
+        <v>68922.82128562266</v>
       </c>
       <c r="F425" s="2" t="n">
-        <v>780.6407554123412</v>
+        <v>239446.895065223</v>
       </c>
     </row>
     <row r="426">
@@ -8401,10 +8401,10 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>192</v>
+        <v>169677.7761697887</v>
       </c>
       <c r="F426" s="2" t="n">
-        <v>1536</v>
+        <v>664623.3728540518</v>
       </c>
     </row>
     <row r="427">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>192</v>
+        <v>169677.7761697887</v>
       </c>
       <c r="F427" s="2" t="n">
-        <v>1536</v>
+        <v>664623.3728540518</v>
       </c>
     </row>
     <row r="428">
@@ -8453,10 +8453,10 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>123.0954030924953</v>
+        <v>163384.1315216832</v>
       </c>
       <c r="F428" s="2" t="n">
-        <v>956.8087150639058</v>
+        <v>595744.0091406531</v>
       </c>
     </row>
     <row r="429">
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>120.1035244331235</v>
+        <v>239424.2277375267</v>
       </c>
       <c r="F429" s="2" t="n">
-        <v>944.3637134032589</v>
+        <v>846104.5284947836</v>
       </c>
     </row>
     <row r="430">
@@ -8505,10 +8505,10 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>135.692103049277</v>
+        <v>406266.6949501505</v>
       </c>
       <c r="F430" s="2" t="n">
-        <v>1087.323591058993</v>
+        <v>1401824.693623829</v>
       </c>
     </row>
     <row r="431">
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>165.330598260403</v>
+        <v>743454.1482799333</v>
       </c>
       <c r="F431" s="2" t="n">
-        <v>1353.732176410047</v>
+        <v>2511411.125006217</v>
       </c>
     </row>
     <row r="432">
@@ -8557,10 +8557,10 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>210.9617557624764</v>
+        <v>1424783.861636898</v>
       </c>
       <c r="F432" s="2" t="n">
-        <v>1767.270154598273</v>
+        <v>4717785.29365459</v>
       </c>
     </row>
     <row r="433">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>277.7116442540056</v>
+        <v>2816979.26326412</v>
       </c>
       <c r="F433" s="2" t="n">
-        <v>2381.841205698951</v>
+        <v>9149517.670550179</v>
       </c>
     </row>
     <row r="434">
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>373.8916510707061</v>
+        <v>5696126.58400094</v>
       </c>
       <c r="F434" s="2" t="n">
-        <v>3284.480069173113</v>
+        <v>18155248.33498522</v>
       </c>
     </row>
     <row r="435">
@@ -8635,10 +8635,10 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>512</v>
+        <v>11715157.44473026</v>
       </c>
       <c r="F435" s="2" t="n">
-        <v>4608</v>
+        <v>36652044.08523786</v>
       </c>
     </row>
     <row r="436">
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>512</v>
+        <v>11715157.44473026</v>
       </c>
       <c r="F436" s="2" t="n">
-        <v>4608</v>
+        <v>36652044.08523786</v>
       </c>
     </row>
     <row r="437">
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>223.9124423997523</v>
+        <v>5466390.319638171</v>
       </c>
       <c r="F437" s="2" t="n">
-        <v>1834.038991718458</v>
+        <v>15458807.36192416</v>
       </c>
     </row>
     <row r="438">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="E438" s="2" t="n">
-        <v>149.0252312436699</v>
+        <v>3881740.140855308</v>
       </c>
       <c r="F438" s="2" t="n">
-        <v>1156.604614718958</v>
+        <v>10330801.86883282</v>
       </c>
     </row>
     <row r="439">
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>114.8487535203156</v>
+        <v>3191811.117251148</v>
       </c>
       <c r="F439" s="2" t="n">
-        <v>850.8766929581715</v>
+        <v>8053736.7582355</v>
       </c>
     </row>
     <row r="440">
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>95.4536654109255</v>
+        <v>2830399.570762326</v>
       </c>
       <c r="F440" s="2" t="n">
-        <v>676.8660882050235</v>
+        <v>6789147.582477466</v>
       </c>
     </row>
     <row r="441">
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>83.08273105554346</v>
+        <v>2628513.104791808</v>
       </c>
       <c r="F441" s="2" t="n">
-        <v>564.5925393104054</v>
+        <v>6001078.659770884</v>
       </c>
     </row>
     <row r="442">
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>74.60514565815761</v>
+        <v>2518328.659726613</v>
       </c>
       <c r="F442" s="2" t="n">
-        <v>486.1913001914915</v>
+        <v>5476247.383946548</v>
       </c>
     </row>
     <row r="443">
@@ -8843,10 +8843,10 @@
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>68.51538784268716</v>
+        <v>2467606.971852489</v>
       </c>
       <c r="F443" s="2" t="n">
-        <v>428.3740924850737</v>
+        <v>5113058.523174551</v>
       </c>
     </row>
     <row r="444">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>64</v>
+        <v>2459303.256776251</v>
       </c>
       <c r="F444" s="2" t="n">
-        <v>384.0000000000001</v>
+        <v>4857026.59523688</v>
       </c>
     </row>
     <row r="445">
@@ -8895,10 +8895,10 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>64</v>
+        <v>2459303.256776251</v>
       </c>
       <c r="F445" s="2" t="n">
-        <v>384.0000000000001</v>
+        <v>4857026.59523688</v>
       </c>
     </row>
     <row r="446">
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>51.3321537511015</v>
+        <v>3162397.326773776</v>
       </c>
       <c r="F446" s="2" t="n">
-        <v>294.8763703041248</v>
+        <v>5689782.461285776</v>
       </c>
     </row>
     <row r="447">
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>62.65739136757894</v>
+        <v>6188623.961584205</v>
       </c>
       <c r="F447" s="2" t="n">
-        <v>358.7806248391246</v>
+        <v>10560904.24790799</v>
       </c>
     </row>
     <row r="448">
@@ -8973,10 +8973,10 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>88.56049548181952</v>
+        <v>14023507.76399199</v>
       </c>
       <c r="F448" s="2" t="n">
-        <v>509.2409767041184</v>
+        <v>22867142.52365892</v>
       </c>
     </row>
     <row r="449">
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>134.9918682023545</v>
+        <v>34270391.53577247</v>
       </c>
       <c r="F449" s="2" t="n">
-        <v>781.5776364609985</v>
+        <v>53539845.48003841</v>
       </c>
     </row>
     <row r="450">
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>215.4899438825213</v>
+        <v>87706807.56329431</v>
       </c>
       <c r="F450" s="2" t="n">
-        <v>1257.816121623477</v>
+        <v>131443337.8668317</v>
       </c>
     </row>
     <row r="451">
@@ -9051,10 +9051,10 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>354.8838801299817</v>
+        <v>231572724.437511</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>2089.786209199881</v>
+        <v>333149920.5720967</v>
       </c>
     </row>
     <row r="452">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>597.7324819920763</v>
+        <v>625320729.7944261</v>
       </c>
       <c r="F452" s="2" t="n">
-        <v>3552.470878329283</v>
+        <v>863942451.9009268</v>
       </c>
     </row>
     <row r="453">
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>1024</v>
+        <v>1717476339.055149</v>
       </c>
       <c r="F453" s="2" t="n">
-        <v>6144</v>
+        <v>2279407265.423798</v>
       </c>
     </row>
     <row r="454">
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>1024</v>
+        <v>1717476339.055149</v>
       </c>
       <c r="F454" s="2" t="n">
-        <v>6144</v>
+        <v>2279407265.423798</v>
       </c>
     </row>
     <row r="455">
@@ -9155,10 +9155,10 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>488.3564997537882</v>
+        <v>996630316.2979915</v>
       </c>
       <c r="F455" s="2" t="n">
-        <v>2445.385322291276</v>
+        <v>1081322530.116531</v>
       </c>
     </row>
     <row r="456">
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>354.4437306197962</v>
+        <v>880137926.5145465</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>1542.139486291944</v>
+        <v>812772194.5311005</v>
       </c>
     </row>
     <row r="457">
@@ -9207,10 +9207,10 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>297.8808127350192</v>
+        <v>900020252.8655517</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>1134.502257277562</v>
+        <v>712668845.9968609</v>
       </c>
     </row>
     <row r="458">
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>269.9837364047089</v>
+        <v>992552919.2990483</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>902.4881176066978</v>
+        <v>675711222.6800796</v>
       </c>
     </row>
     <row r="459">
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>256.2621744766313</v>
+        <v>1146322693.194041</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>752.7900524138739</v>
+        <v>671785677.7662393</v>
       </c>
     </row>
     <row r="460">
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>250.9407981737039</v>
+        <v>1365840459.634722</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>648.2550669219886</v>
+        <v>689509125.9290614</v>
       </c>
     </row>
     <row r="461">
@@ -9311,10 +9311,10 @@
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>251.3155506939212</v>
+        <v>1664387234.452982</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>571.1654566467648</v>
+        <v>724091187.8307656</v>
       </c>
     </row>
     <row r="462">
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>256</v>
+        <v>2062914813.819247</v>
       </c>
       <c r="F462" s="2" t="n">
-        <v>512</v>
+        <v>773639291.8273966</v>
       </c>
     </row>
     <row r="463">
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>256</v>
+        <v>2062914813.819247</v>
       </c>
       <c r="F463" s="2" t="n">
-        <v>512</v>
+        <v>773639291.8273966</v>
       </c>
     </row>
     <row r="464">
@@ -9389,10 +9389,10 @@
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>108.0017740826299</v>
+        <v>1322763995.548106</v>
       </c>
       <c r="F464" s="2" t="n">
-        <v>202.144749121721</v>
+        <v>444225268.8096915</v>
       </c>
     </row>
     <row r="465">
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>69.34180216208662</v>
+        <v>1290793432.415621</v>
       </c>
       <c r="F465" s="2" t="n">
-        <v>126.4547741947134</v>
+        <v>404155283.8286686</v>
       </c>
     </row>
     <row r="466">
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>51.55185107897695</v>
+        <v>1458532239.463664</v>
       </c>
       <c r="F466" s="2" t="n">
-        <v>92.28122413600921</v>
+        <v>428942041.0554438</v>
       </c>
     </row>
     <row r="467">
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>41.33264956510073</v>
+        <v>1777359016.136873</v>
       </c>
       <c r="F467" s="2" t="n">
-        <v>72.81919686751712</v>
+        <v>492270020.9630268</v>
       </c>
     </row>
     <row r="468">
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>34.70516056072824</v>
+        <v>2268224934.171155</v>
       </c>
       <c r="F468" s="2" t="n">
-        <v>60.25244476556771</v>
+        <v>592385491.2388648</v>
       </c>
     </row>
     <row r="469">
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>30.06316735633945</v>
+        <v>2986324129.519697</v>
       </c>
       <c r="F469" s="2" t="n">
-        <v>51.46869197815998</v>
+        <v>735944573.9449331</v>
       </c>
     </row>
     <row r="470">
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>26.63402053600463</v>
+        <v>4021139000.028463</v>
       </c>
       <c r="F470" s="2" t="n">
-        <v>44.98373942487196</v>
+        <v>935469791.32731</v>
       </c>
     </row>
     <row r="471">
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>24</v>
+        <v>5507236713.11497</v>
       </c>
       <c r="F471" s="2" t="n">
-        <v>40</v>
+        <v>1209780111.624298</v>
       </c>
     </row>
     <row r="472">
@@ -9597,10 +9597,10 @@
         </is>
       </c>
       <c r="E472" s="2" t="n">
-        <v>24</v>
+        <v>5507236713.11497</v>
       </c>
       <c r="F472" s="2" t="n">
-        <v>40</v>
+        <v>1209780111.624298</v>
       </c>
     </row>
     <row r="473">
@@ -9623,10 +9623,10 @@
         </is>
       </c>
       <c r="E473" s="2" t="n">
-        <v>4.61404717992635</v>
+        <v>2443821882.72761</v>
       </c>
       <c r="F473" s="2" t="n">
-        <v>6.793413216515661</v>
+        <v>434271245.7290222</v>
       </c>
     </row>
     <row r="474">
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="E474" s="2" t="n">
-        <v>2.678561477405338</v>
+        <v>3274569052.8913</v>
       </c>
       <c r="F474" s="2" t="n">
-        <v>3.713200530214782</v>
+        <v>501704550.2673191</v>
       </c>
     </row>
     <row r="475">
@@ -9675,10 +9675,10 @@
         </is>
       </c>
       <c r="E475" s="2" t="n">
-        <v>1.949561306027979</v>
+        <v>5501162163.562591</v>
       </c>
       <c r="F475" s="2" t="n">
-        <v>2.555426031861377</v>
+        <v>729775945.328842</v>
       </c>
     </row>
     <row r="476">
@@ -9701,10 +9701,10 @@
         </is>
       </c>
       <c r="E476" s="2" t="n">
-        <v>1.570142448033869</v>
+        <v>10226372819.29995</v>
       </c>
       <c r="F476" s="2" t="n">
-        <v>1.948384751261965</v>
+        <v>1176054762.613422</v>
       </c>
     </row>
     <row r="477">
@@ -9727,10 +9727,10 @@
         </is>
       </c>
       <c r="E477" s="2" t="n">
-        <v>1.339695023226408</v>
+        <v>20139724582.75352</v>
       </c>
       <c r="F477" s="2" t="n">
-        <v>1.574619863309849</v>
+        <v>2008885305.812436</v>
       </c>
     </row>
     <row r="478">
@@ -9753,10 +9753,10 @@
         </is>
       </c>
       <c r="E478" s="2" t="n">
-        <v>1.186570383980938</v>
+        <v>41172392447.82437</v>
       </c>
       <c r="F478" s="2" t="n">
-        <v>1.321337309095369</v>
+        <v>3563031876.379255</v>
       </c>
     </row>
     <row r="479">
@@ -9779,10 +9779,10 @@
         </is>
       </c>
       <c r="E479" s="2" t="n">
-        <v>1.078807368523075</v>
+        <v>86401547228.57439</v>
       </c>
       <c r="F479" s="2" t="n">
-        <v>1.138367375927505</v>
+        <v>6488062791.278718</v>
       </c>
     </row>
     <row r="480">
@@ -9805,10 +9805,10 @@
         </is>
       </c>
       <c r="E480" s="2" t="n">
-        <v>1</v>
+        <v>184859865072.0317</v>
       </c>
       <c r="F480" s="2" t="n">
-        <v>1</v>
+        <v>12046453173.55365</v>
       </c>
     </row>
     <row r="481">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>694.9702902148998</v>
+        <v>583.2087295123338</v>
       </c>
       <c r="F419" s="2" t="n">
-        <v>1270.511559572846</v>
+        <v>1110.237711083412</v>
       </c>
     </row>
     <row r="420">
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>1196.649850021172</v>
+        <v>842.7187260777221</v>
       </c>
       <c r="F420" s="2" t="n">
-        <v>2359.774818971994</v>
+        <v>1801.960515548529</v>
       </c>
     </row>
     <row r="421">
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>2411.920213316881</v>
+        <v>1425.39840290539</v>
       </c>
       <c r="F421" s="2" t="n">
-        <v>5269.321145173129</v>
+        <v>3516.144624883094</v>
       </c>
     </row>
     <row r="422">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>5263.059343519646</v>
+        <v>2610.173490046953</v>
       </c>
       <c r="F422" s="2" t="n">
-        <v>12853.63972927639</v>
+        <v>7495.067338943531</v>
       </c>
     </row>
     <row r="423">
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>12049.11852611687</v>
+        <v>5014.690810225376</v>
       </c>
       <c r="F423" s="2" t="n">
-        <v>33031.29310677554</v>
+        <v>16831.09401287439</v>
       </c>
     </row>
     <row r="424">
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>28486.97812562146</v>
+        <v>9949.311847531131</v>
       </c>
       <c r="F424" s="2" t="n">
-        <v>87854.5688286629</v>
+        <v>39119.06587803794</v>
       </c>
     </row>
     <row r="425">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>68922.82128562266</v>
+        <v>20200.74957401707</v>
       </c>
       <c r="F425" s="2" t="n">
-        <v>239446.895065223</v>
+        <v>93168.83992096882</v>
       </c>
     </row>
     <row r="426">
@@ -8401,10 +8401,10 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>169677.7761697887</v>
+        <v>41733.72776251628</v>
       </c>
       <c r="F426" s="2" t="n">
-        <v>664623.3728540518</v>
+        <v>225982.3092077873</v>
       </c>
     </row>
     <row r="427">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>169677.7761697887</v>
+        <v>41733.72776251628</v>
       </c>
       <c r="F427" s="2" t="n">
-        <v>664623.3728540518</v>
+        <v>225982.3092077873</v>
       </c>
     </row>
     <row r="428">
@@ -8453,10 +8453,10 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>163384.1315216832</v>
+        <v>30633.82530427614</v>
       </c>
       <c r="F428" s="2" t="n">
-        <v>595744.0091406531</v>
+        <v>161169.1054540616</v>
       </c>
     </row>
     <row r="429">
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>239424.2277375267</v>
+        <v>34220.67683617786</v>
       </c>
       <c r="F429" s="2" t="n">
-        <v>846104.5284947836</v>
+        <v>182124.9354110597</v>
       </c>
     </row>
     <row r="430">
@@ -8505,10 +8505,10 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>406266.6949501505</v>
+        <v>44265.04021406242</v>
       </c>
       <c r="F430" s="2" t="n">
-        <v>1401824.693623829</v>
+        <v>240083.5348901573</v>
       </c>
     </row>
     <row r="431">
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>743454.1482799333</v>
+        <v>61749.43289317845</v>
       </c>
       <c r="F431" s="2" t="n">
-        <v>2511411.125006217</v>
+        <v>342223.4492537044</v>
       </c>
     </row>
     <row r="432">
@@ -8557,10 +8557,10 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>1424783.861636898</v>
+        <v>90210.46343745851</v>
       </c>
       <c r="F432" s="2" t="n">
-        <v>4717785.29365459</v>
+        <v>511509.1446189569</v>
       </c>
     </row>
     <row r="433">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>2816979.26326412</v>
+        <v>135962.9938345435</v>
       </c>
       <c r="F433" s="2" t="n">
-        <v>9149517.670550179</v>
+        <v>789290.1987877744</v>
       </c>
     </row>
     <row r="434">
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>5696126.58400094</v>
+        <v>209578.07318589</v>
       </c>
       <c r="F434" s="2" t="n">
-        <v>18155248.33498522</v>
+        <v>1246131.811672945</v>
       </c>
     </row>
     <row r="435">
@@ -8635,10 +8635,10 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>11715157.44473026</v>
+        <v>328581.7839565452</v>
       </c>
       <c r="F435" s="2" t="n">
-        <v>36652044.08523786</v>
+        <v>2001627.546075745</v>
       </c>
     </row>
     <row r="436">
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>11715157.44473026</v>
+        <v>328581.7839565452</v>
       </c>
       <c r="F436" s="2" t="n">
-        <v>36652044.08523786</v>
+        <v>2001627.546075745</v>
       </c>
     </row>
     <row r="437">
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>5466390.319638171</v>
+        <v>156201.3328787747</v>
       </c>
       <c r="F437" s="2" t="n">
-        <v>15458807.36192416</v>
+        <v>865988.9475631206</v>
       </c>
     </row>
     <row r="438">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="E438" s="2" t="n">
-        <v>3881740.140855308</v>
+        <v>113005.4264854566</v>
       </c>
       <c r="F438" s="2" t="n">
-        <v>10330801.86883282</v>
+        <v>593637.9975864481</v>
       </c>
     </row>
     <row r="439">
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>3191811.117251148</v>
+        <v>94667.03309593175</v>
       </c>
       <c r="F439" s="2" t="n">
-        <v>8053736.7582355</v>
+        <v>474718.7489707069</v>
       </c>
     </row>
     <row r="440">
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>2830399.570762326</v>
+        <v>85525.9833469116</v>
       </c>
       <c r="F440" s="2" t="n">
-        <v>6789147.582477466</v>
+        <v>410492.7572049934</v>
       </c>
     </row>
     <row r="441">
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>2628513.104791808</v>
+        <v>80918.75950932644</v>
       </c>
       <c r="F441" s="2" t="n">
-        <v>6001078.659770884</v>
+        <v>372195.2821115094</v>
       </c>
     </row>
     <row r="442">
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>2518328.659726613</v>
+        <v>78984.19951064256</v>
       </c>
       <c r="F442" s="2" t="n">
-        <v>5476247.383946548</v>
+        <v>348398.1965499314</v>
       </c>
     </row>
     <row r="443">
@@ -8843,10 +8843,10 @@
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>2467606.971852489</v>
+        <v>78848.33825134594</v>
       </c>
       <c r="F443" s="2" t="n">
-        <v>5113058.523174551</v>
+        <v>333675.9443618188</v>
       </c>
     </row>
     <row r="444">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>2459303.256776251</v>
+        <v>80060.33157766196</v>
       </c>
       <c r="F444" s="2" t="n">
-        <v>4857026.59523688</v>
+        <v>325136.6384429052</v>
       </c>
     </row>
     <row r="445">
@@ -8895,10 +8895,10 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>2459303.256776251</v>
+        <v>80060.33157766196</v>
       </c>
       <c r="F445" s="2" t="n">
-        <v>4857026.59523688</v>
+        <v>325136.6384429052</v>
       </c>
     </row>
     <row r="446">
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>3162397.326773776</v>
+        <v>73669.77095405322</v>
       </c>
       <c r="F446" s="2" t="n">
-        <v>5689782.461285776</v>
+        <v>286442.2534907912</v>
       </c>
     </row>
     <row r="447">
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>6188623.961584205</v>
+        <v>103165.5186192836</v>
       </c>
       <c r="F447" s="2" t="n">
-        <v>10560904.24790799</v>
+        <v>399842.0949667247</v>
       </c>
     </row>
     <row r="448">
@@ -8973,10 +8973,10 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>14023507.76399199</v>
+        <v>167287.9720057605</v>
       </c>
       <c r="F448" s="2" t="n">
-        <v>22867142.52365892</v>
+        <v>651096.4051923612</v>
       </c>
     </row>
     <row r="449">
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>34270391.53577247</v>
+        <v>292546.3669700471</v>
       </c>
       <c r="F449" s="2" t="n">
-        <v>53539845.48003841</v>
+        <v>1146453.652119232</v>
       </c>
     </row>
     <row r="450">
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>87706807.56329431</v>
+        <v>535767.7056266126</v>
       </c>
       <c r="F450" s="2" t="n">
-        <v>131443337.8668317</v>
+        <v>2116722.652082936</v>
       </c>
     </row>
     <row r="451">
@@ -9051,10 +9051,10 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>231572724.437511</v>
+        <v>1012274.320400161</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>333149920.5720967</v>
+        <v>4034698.456719378</v>
       </c>
     </row>
     <row r="452">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>625320729.7944261</v>
+        <v>1956055.740709604</v>
       </c>
       <c r="F452" s="2" t="n">
-        <v>863942451.9009268</v>
+        <v>7868685.22739314</v>
       </c>
     </row>
     <row r="453">
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>1717476339.055149</v>
+        <v>3844472.413788395</v>
       </c>
       <c r="F453" s="2" t="n">
-        <v>2279407265.423798</v>
+        <v>15612961.03293186</v>
       </c>
     </row>
     <row r="454">
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>1717476339.055149</v>
+        <v>3844472.413788395</v>
       </c>
       <c r="F454" s="2" t="n">
-        <v>2279407265.423798</v>
+        <v>15612961.03293186</v>
       </c>
     </row>
     <row r="455">
@@ -9155,10 +9155,10 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>996630316.2979915</v>
+        <v>2315021.608712353</v>
       </c>
       <c r="F455" s="2" t="n">
-        <v>1081322530.116531</v>
+        <v>7846259.264164844</v>
       </c>
     </row>
     <row r="456">
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>880137926.5145465</v>
+        <v>2121517.704119835</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>812772194.5311005</v>
+        <v>6247701.835633707</v>
       </c>
     </row>
     <row r="457">
@@ -9207,10 +9207,10 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>900020252.8655517</v>
+        <v>2251247.149590914</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>712668845.9968609</v>
+        <v>5803410.439569656</v>
       </c>
     </row>
     <row r="458">
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>992552919.2990483</v>
+        <v>2576318.391251266</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>675711222.6800796</v>
+        <v>5829089.176058053</v>
       </c>
     </row>
     <row r="459">
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>1146322693.194041</v>
+        <v>3087647.559750664</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>671785677.7662393</v>
+        <v>6139236.485866043</v>
       </c>
     </row>
     <row r="460">
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>1365840459.634722</v>
+        <v>3817647.050025986</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>689509125.9290614</v>
+        <v>6675252.465644834</v>
       </c>
     </row>
     <row r="461">
@@ -9311,10 +9311,10 @@
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>1664387234.452982</v>
+        <v>4827531.833205524</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>724091187.8307656</v>
+        <v>7426171.837749272</v>
       </c>
     </row>
     <row r="462">
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>2062914813.819247</v>
+        <v>6209076.829557999</v>
       </c>
       <c r="F462" s="2" t="n">
-        <v>773639291.8273966</v>
+        <v>8405321.038996274</v>
       </c>
     </row>
     <row r="463">
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>2062914813.819247</v>
+        <v>6209076.829557999</v>
       </c>
       <c r="F463" s="2" t="n">
-        <v>773639291.8273966</v>
+        <v>8405321.038996274</v>
       </c>
     </row>
     <row r="464">
@@ -9389,10 +9389,10 @@
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>1322763995.548106</v>
+        <v>4011919.490687458</v>
       </c>
       <c r="F464" s="2" t="n">
-        <v>444225268.8096915</v>
+        <v>5082542.991611379</v>
       </c>
     </row>
     <row r="465">
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>1290793432.415621</v>
+        <v>3945033.502259679</v>
       </c>
       <c r="F465" s="2" t="n">
-        <v>404155283.8286686</v>
+        <v>4869541.573952398</v>
       </c>
     </row>
     <row r="466">
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>1458532239.463664</v>
+        <v>4491941.447956745</v>
       </c>
       <c r="F466" s="2" t="n">
-        <v>428942041.0554438</v>
+        <v>5442525.165719046</v>
       </c>
     </row>
     <row r="467">
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>1777359016.136873</v>
+        <v>5515911.884082857</v>
       </c>
       <c r="F467" s="2" t="n">
-        <v>492270020.9630268</v>
+        <v>6577596.601022505</v>
       </c>
     </row>
     <row r="468">
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>2268224934.171155</v>
+        <v>7093366.232010648</v>
       </c>
       <c r="F468" s="2" t="n">
-        <v>592385491.2388648</v>
+        <v>8335473.495320463</v>
       </c>
     </row>
     <row r="469">
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>2986324129.519697</v>
+        <v>9410816.624785341</v>
       </c>
       <c r="F469" s="2" t="n">
-        <v>735944573.9449331</v>
+        <v>10905183.66204279</v>
       </c>
     </row>
     <row r="470">
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>4021139000.028463</v>
+        <v>12769196.14545644</v>
       </c>
       <c r="F470" s="2" t="n">
-        <v>935469791.32731</v>
+        <v>14597539.50090802</v>
       </c>
     </row>
     <row r="471">
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>5507236713.11497</v>
+        <v>17622694.8409208</v>
       </c>
       <c r="F471" s="2" t="n">
-        <v>1209780111.624298</v>
+        <v>19880090.03811214</v>
       </c>
     </row>
     <row r="472">
@@ -9597,10 +9597,10 @@
         </is>
       </c>
       <c r="E472" s="2" t="n">
-        <v>5507236713.11497</v>
+        <v>17622694.8409208</v>
       </c>
       <c r="F472" s="2" t="n">
-        <v>1209780111.624298</v>
+        <v>19880090.03811214</v>
       </c>
     </row>
     <row r="473">
@@ -9623,10 +9623,10 @@
         </is>
       </c>
       <c r="E473" s="2" t="n">
-        <v>2443821882.72761</v>
+        <v>6215058.952198651</v>
       </c>
       <c r="F473" s="2" t="n">
-        <v>434271245.7290222</v>
+        <v>6193676.665663028</v>
       </c>
     </row>
     <row r="474">
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="E474" s="2" t="n">
-        <v>3274569052.8913</v>
+        <v>6618612.912963974</v>
       </c>
       <c r="F474" s="2" t="n">
-        <v>501704550.2673191</v>
+        <v>6210278.03366101</v>
       </c>
     </row>
     <row r="475">
@@ -9675,10 +9675,10 @@
         </is>
       </c>
       <c r="E475" s="2" t="n">
-        <v>5501162163.562591</v>
+        <v>8836990.792871492</v>
       </c>
       <c r="F475" s="2" t="n">
-        <v>729775945.328842</v>
+        <v>7840217.249174365</v>
       </c>
     </row>
     <row r="476">
@@ -9701,10 +9701,10 @@
         </is>
       </c>
       <c r="E476" s="2" t="n">
-        <v>10226372819.29995</v>
+        <v>13055956.75314689</v>
       </c>
       <c r="F476" s="2" t="n">
-        <v>1176054762.613422</v>
+        <v>10965833.47744089</v>
       </c>
     </row>
     <row r="477">
@@ -9727,10 +9727,10 @@
         </is>
       </c>
       <c r="E477" s="2" t="n">
-        <v>20139724582.75352</v>
+        <v>20435145.50667887</v>
       </c>
       <c r="F477" s="2" t="n">
-        <v>2008885305.812436</v>
+        <v>16257164.20991712</v>
       </c>
     </row>
     <row r="478">
@@ -9753,10 +9753,10 @@
         </is>
       </c>
       <c r="E478" s="2" t="n">
-        <v>41172392447.82437</v>
+        <v>33202244.01616731</v>
       </c>
       <c r="F478" s="2" t="n">
-        <v>3563031876.379255</v>
+        <v>25025623.52386186</v>
       </c>
     </row>
     <row r="479">
@@ -9779,10 +9779,10 @@
         </is>
       </c>
       <c r="E479" s="2" t="n">
-        <v>86401547228.57439</v>
+        <v>55375795.60839046</v>
       </c>
       <c r="F479" s="2" t="n">
-        <v>6488062791.278718</v>
+        <v>39550847.33806602</v>
       </c>
     </row>
     <row r="480">
@@ -9805,10 +9805,10 @@
         </is>
       </c>
       <c r="E480" s="2" t="n">
-        <v>184859865072.0317</v>
+        <v>94162551.30680417</v>
       </c>
       <c r="F480" s="2" t="n">
-        <v>12046453173.55365</v>
+        <v>63734633.61066098</v>
       </c>
     </row>
     <row r="481">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2280"/>
+  <dimension ref="A1:G2280"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="50.7777777777778" customWidth="1" style="3" min="2" max="2"/>
@@ -1051,6 +1051,11 @@
           <t>lifeMultiplier</t>
         </is>
       </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>authorAtkScale</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1083,6 +1088,11 @@
           <t>本波生命及护盾倍率；空白为1，不改变资源和跨关插值锚点</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Author-only attack shape; not projected. Tail multiplier includes this factor.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1111,6 +1121,11 @@
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -8323,10 +8338,13 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>5014.690810225376</v>
+        <v>626.8363512781719</v>
       </c>
       <c r="F423" s="2" t="n">
         <v>16831.09401287439</v>
+      </c>
+      <c r="G423" s="2" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="424">
@@ -8349,10 +8367,13 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>9949.311847531131</v>
+        <v>1243.663980941391</v>
       </c>
       <c r="F424" s="2" t="n">
         <v>39119.06587803794</v>
+      </c>
+      <c r="G424" s="2" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="425">
@@ -8375,10 +8396,13 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>20200.74957401707</v>
+        <v>2525.093696752134</v>
       </c>
       <c r="F425" s="2" t="n">
         <v>93168.83992096882</v>
+      </c>
+      <c r="G425" s="2" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="426">
@@ -8401,10 +8425,13 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>41733.72776251628</v>
+        <v>5216.715970314535</v>
       </c>
       <c r="F426" s="2" t="n">
         <v>225982.3092077873</v>
+      </c>
+      <c r="G426" s="2" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="427">
@@ -8427,7 +8454,7 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>41733.72776251628</v>
+        <v>5216.715970314535</v>
       </c>
       <c r="F427" s="2" t="n">
         <v>225982.3092077873</v>
@@ -8453,7 +8480,7 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>30633.82530427614</v>
+        <v>4965.894545606789</v>
       </c>
       <c r="F428" s="2" t="n">
         <v>161169.1054540616</v>
@@ -8479,7 +8506,7 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>34220.67683617786</v>
+        <v>7194.011119774445</v>
       </c>
       <c r="F429" s="2" t="n">
         <v>182124.9354110597</v>
@@ -8505,7 +8532,7 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>44265.04021406242</v>
+        <v>12067.84216004341</v>
       </c>
       <c r="F430" s="2" t="n">
         <v>240083.5348901573</v>
@@ -8531,7 +8558,7 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>61749.43289317845</v>
+        <v>21831.72136659507</v>
       </c>
       <c r="F431" s="2" t="n">
         <v>342223.4492537044</v>
@@ -8557,7 +8584,7 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>90210.46343745851</v>
+        <v>41361.67985575831</v>
       </c>
       <c r="F432" s="2" t="n">
         <v>511509.1446189569</v>
@@ -8583,7 +8610,7 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>135962.9938345435</v>
+        <v>80844.07982255514</v>
       </c>
       <c r="F433" s="2" t="n">
         <v>789290.1987877744</v>
@@ -8609,7 +8636,7 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>209578.07318589</v>
+        <v>161606.7866177086</v>
       </c>
       <c r="F434" s="2" t="n">
         <v>1246131.811672945</v>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2280"/>
+  <dimension ref="A1:I2284"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="50.7777777777778" customWidth="1" style="3" min="2" max="2"/>
@@ -1056,6 +1056,16 @@
           <t>authorAtkScale</t>
         </is>
       </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>rewardBinding</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>formation_positions</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1093,6 +1103,16 @@
           <t>Author-only attack shape; not projected. Tail multiplier includes this factor.</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Optional existing candidate reward contract</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Optional explicit existing formation contract</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1128,6 +1148,16 @@
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>float</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>json</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>json</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8350,7 @@
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>30146</v>
+        <v>34146</v>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
@@ -8349,7 +8379,7 @@
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>30147</v>
+        <v>34147</v>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
@@ -8378,7 +8408,7 @@
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>30148</v>
+        <v>34148</v>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
@@ -8407,7 +8437,7 @@
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>30149</v>
+        <v>34149</v>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
@@ -45835,6 +45865,162 @@
       <c r="D2280" s="2" t="inlineStr">
         <is>
           <t>ultimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" s="2" t="n">
+        <v>30146</v>
+      </c>
+      <c r="B2281" s="2" t="inlineStr">
+        <is>
+          <t>第14关第6战点：主舰与混合护卫</t>
+        </is>
+      </c>
+      <c r="C2281" s="2" t="inlineStr">
+        <is>
+          <t>{null,54920,54921,54922,null,null,54923,54924,54925,null,null,54926,54927,54928,null}</t>
+        </is>
+      </c>
+      <c r="D2281" s="2" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="E2281" s="2" t="n">
+        <v>626.8363512781719</v>
+      </c>
+      <c r="F2281" s="2" t="n">
+        <v>16831.09401287439</v>
+      </c>
+      <c r="G2281" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H2281" s="2" t="inlineStr">
+        <is>
+          <t>{"status":"BOUND","referenceGroupId":34146,"levelId":14,"resRatio":561545.6675019113,"jewelRatio":3.6}</t>
+        </is>
+      </c>
+      <c r="I2281" t="inlineStr">
+        <is>
+          <t>[null,[106,220],[226,220],[346,220],null,null,[466,220],[286,110],[106,330],null,null,[226,330],[346,330],[466,330],null]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" s="2" t="n">
+        <v>30147</v>
+      </c>
+      <c r="B2282" s="2" t="inlineStr">
+        <is>
+          <t>第14关第7战点：主舰与混合护卫</t>
+        </is>
+      </c>
+      <c r="C2282" s="2" t="inlineStr">
+        <is>
+          <t>{null,54940,54941,54942,null,null,54943,54944,54945,null,null,54946,54947,54948,null}</t>
+        </is>
+      </c>
+      <c r="D2282" s="2" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="E2282" s="2" t="n">
+        <v>1243.663980941391</v>
+      </c>
+      <c r="F2282" s="2" t="n">
+        <v>39119.06587803794</v>
+      </c>
+      <c r="G2282" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H2282" s="2" t="inlineStr">
+        <is>
+          <t>{"status":"BOUND","referenceGroupId":34147,"levelId":14,"resRatio":561545.6675019113,"jewelRatio":3.6}</t>
+        </is>
+      </c>
+      <c r="I2282" t="inlineStr">
+        <is>
+          <t>[null,[106,220],[226,220],[346,220],null,null,[466,220],[286,110],[106,330],null,null,[226,330],[346,330],[466,330],null]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="2" t="n">
+        <v>30148</v>
+      </c>
+      <c r="B2283" s="2" t="inlineStr">
+        <is>
+          <t>第14关第8战点：主舰与混合护卫</t>
+        </is>
+      </c>
+      <c r="C2283" s="2" t="inlineStr">
+        <is>
+          <t>{null,54960,54961,54962,null,null,54963,54964,54965,null,null,54966,54967,54968,null}</t>
+        </is>
+      </c>
+      <c r="D2283" s="2" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="E2283" s="2" t="n">
+        <v>2525.093696752134</v>
+      </c>
+      <c r="F2283" s="2" t="n">
+        <v>93168.83992096882</v>
+      </c>
+      <c r="G2283" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H2283" s="2" t="inlineStr">
+        <is>
+          <t>{"status":"BOUND","referenceGroupId":34148,"levelId":14,"resRatio":561545.6675019113,"jewelRatio":3.6}</t>
+        </is>
+      </c>
+      <c r="I2283" t="inlineStr">
+        <is>
+          <t>[null,[106,220],[226,220],[346,220],null,null,[466,220],[286,110],[106,330],null,null,[226,330],[346,330],[466,330],null]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="2" t="n">
+        <v>30149</v>
+      </c>
+      <c r="B2284" s="2" t="inlineStr">
+        <is>
+          <t>第14关尾波：主舰与两翼弱护卫</t>
+        </is>
+      </c>
+      <c r="C2284" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,54901,54987,54903,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2284" s="2" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="E2284" s="2" t="n">
+        <v>5216.715970314535</v>
+      </c>
+      <c r="F2284" s="2" t="n">
+        <v>225982.3092077873</v>
+      </c>
+      <c r="G2284" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H2284" s="2" t="inlineStr">
+        <is>
+          <t>{"status":"BOUND","referenceGroupId":34149,"levelId":14,"resRatio":561545.6675019113,"jewelRatio":3.6}</t>
+        </is>
+      </c>
+      <c r="I2284" t="inlineStr">
+        <is>
+          <t>[null,null,null,null,null,null,[126,250],[286,100],[446,250],null,null,null,null,null,null]</t>
         </is>
       </c>
     </row>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1061,7 +1061,7 @@
           <t>rewardBinding</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>formation_positions</t>
         </is>
@@ -1108,7 +1108,7 @@
           <t>Optional existing candidate reward contract</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Optional explicit existing formation contract</t>
         </is>
@@ -1155,7 +1155,7 @@
           <t>json</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>json</t>
         </is>
@@ -45901,9 +45901,9 @@
           <t>{"status":"BOUND","referenceGroupId":34146,"levelId":14,"resRatio":561545.6675019113,"jewelRatio":3.6}</t>
         </is>
       </c>
-      <c r="I2281" t="inlineStr">
-        <is>
-          <t>[null,[106,220],[226,220],[346,220],null,null,[466,220],[286,110],[106,330],null,null,[226,330],[346,330],[466,330],null]</t>
+      <c r="I2281" s="2" t="inlineStr">
+        <is>
+          <t>[null,[106,270],[226,270],[346,270],null,null,[466,270],[286,110],[106,350],null,null,[226,350],[346,350],[466,350],null]</t>
         </is>
       </c>
     </row>
@@ -45940,9 +45940,9 @@
           <t>{"status":"BOUND","referenceGroupId":34147,"levelId":14,"resRatio":561545.6675019113,"jewelRatio":3.6}</t>
         </is>
       </c>
-      <c r="I2282" t="inlineStr">
-        <is>
-          <t>[null,[106,220],[226,220],[346,220],null,null,[466,220],[286,110],[106,330],null,null,[226,330],[346,330],[466,330],null]</t>
+      <c r="I2282" s="2" t="inlineStr">
+        <is>
+          <t>[null,[106,270],[226,270],[346,270],null,null,[466,270],[286,110],[106,350],null,null,[226,350],[346,350],[466,350],null]</t>
         </is>
       </c>
     </row>
@@ -45979,9 +45979,9 @@
           <t>{"status":"BOUND","referenceGroupId":34148,"levelId":14,"resRatio":561545.6675019113,"jewelRatio":3.6}</t>
         </is>
       </c>
-      <c r="I2283" t="inlineStr">
-        <is>
-          <t>[null,[106,220],[226,220],[346,220],null,null,[466,220],[286,110],[106,330],null,null,[226,330],[346,330],[466,330],null]</t>
+      <c r="I2283" s="2" t="inlineStr">
+        <is>
+          <t>[null,[106,270],[226,270],[346,270],null,null,[466,270],[286,110],[106,350],null,null,[226,350],[346,350],[466,350],null]</t>
         </is>
       </c>
     </row>
@@ -46018,9 +46018,9 @@
           <t>{"status":"BOUND","referenceGroupId":34149,"levelId":14,"resRatio":561545.6675019113,"jewelRatio":3.6}</t>
         </is>
       </c>
-      <c r="I2284" t="inlineStr">
-        <is>
-          <t>[null,null,null,null,null,null,[126,250],[286,100],[446,250],null,null,null,null,null,null]</t>
+      <c r="I2284" s="2" t="inlineStr">
+        <is>
+          <t>[null,null,null,null,null,null,[126,350],[286,160],[446,350],null,null,null,null,null,null]</t>
         </is>
       </c>
     </row>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -8600,7 +8600,7 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>第15关第6战点</t>
+          <t>第15关第6战点：主舰与混合护卫</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
@@ -8618,6 +8618,11 @@
       </c>
       <c r="F432" s="2" t="n">
         <v>511509.1446189569</v>
+      </c>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>[null,null,null,null,null,[126,350],null,[286,110],null,[446,350],null,null,null,null,null]</t>
+        </is>
       </c>
     </row>
     <row r="433">
@@ -8626,7 +8631,7 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>第15关第7战点</t>
+          <t>第15关第7战点：主舰与混合护卫</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
@@ -8644,6 +8649,11 @@
       </c>
       <c r="F433" s="2" t="n">
         <v>789290.1987877744</v>
+      </c>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>[null,null,null,null,null,[126,350],null,[286,110],null,[446,350],null,null,null,null,null]</t>
+        </is>
       </c>
     </row>
     <row r="434">
@@ -8652,7 +8662,7 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>第15关第8战点</t>
+          <t>第15关第8战点：主舰与混合护卫</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
@@ -8670,6 +8680,11 @@
       </c>
       <c r="F434" s="2" t="n">
         <v>1246131.811672945</v>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>[null,null,null,null,null,[126,350],null,[286,110],null,[446,350],null,null,null,null,null]</t>
+        </is>
       </c>
     </row>
     <row r="435">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -8513,7 +8513,7 @@
         <v>4965.894545606789</v>
       </c>
       <c r="F428" s="2" t="n">
-        <v>161169.1054540616</v>
+        <v>124278.3695762839</v>
       </c>
     </row>
     <row r="429">
@@ -8539,7 +8539,7 @@
         <v>7194.011119774445</v>
       </c>
       <c r="F429" s="2" t="n">
-        <v>182124.9354110597</v>
+        <v>108292.1345051216</v>
       </c>
     </row>
     <row r="430">
@@ -8565,7 +8565,7 @@
         <v>12067.84216004341</v>
       </c>
       <c r="F430" s="2" t="n">
-        <v>240083.5348901573</v>
+        <v>110078.786100572</v>
       </c>
     </row>
     <row r="431">
@@ -8591,7 +8591,7 @@
         <v>21831.72136659507</v>
       </c>
       <c r="F431" s="2" t="n">
-        <v>342223.4492537044</v>
+        <v>120994.2608241724</v>
       </c>
     </row>
     <row r="432">
@@ -8617,7 +8617,7 @@
         <v>41361.67985575831</v>
       </c>
       <c r="F432" s="2" t="n">
-        <v>511509.1446189569</v>
+        <v>139451.169383991</v>
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>80844.07982255514</v>
       </c>
       <c r="F433" s="2" t="n">
-        <v>789290.1987877744</v>
+        <v>165927.8246888828</v>
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>161606.7866177086</v>
       </c>
       <c r="F434" s="2" t="n">
-        <v>1246131.811672945</v>
+        <v>202004.1279607996</v>
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>328581.7839565452</v>
       </c>
       <c r="F435" s="2" t="n">
-        <v>2001627.546075745</v>
+        <v>250203.4432594681</v>
       </c>
     </row>
     <row r="436">
@@ -8736,7 +8736,7 @@
         <v>328581.7839565452</v>
       </c>
       <c r="F436" s="2" t="n">
-        <v>2001627.546075745</v>
+        <v>250203.4432594681</v>
       </c>
     </row>
     <row r="437">
@@ -8762,7 +8762,7 @@
         <v>156201.3328787747</v>
       </c>
       <c r="F437" s="2" t="n">
-        <v>865988.9475631206</v>
+        <v>140381.0901363067</v>
       </c>
     </row>
     <row r="438">
@@ -8788,7 +8788,7 @@
         <v>113005.4264854566</v>
       </c>
       <c r="F438" s="2" t="n">
-        <v>593637.9975864481</v>
+        <v>124797.0160322093</v>
       </c>
     </row>
     <row r="439">
@@ -8814,7 +8814,7 @@
         <v>94667.03309593175</v>
       </c>
       <c r="F439" s="2" t="n">
-        <v>474718.7489707069</v>
+        <v>129421.1166484333</v>
       </c>
     </row>
     <row r="440">
@@ -8840,7 +8840,7 @@
         <v>85525.9833469116</v>
       </c>
       <c r="F440" s="2" t="n">
-        <v>410492.7572049934</v>
+        <v>145131.1061238069</v>
       </c>
     </row>
     <row r="441">
@@ -8866,7 +8866,7 @@
         <v>80918.75950932644</v>
       </c>
       <c r="F441" s="2" t="n">
-        <v>372195.2821115094</v>
+        <v>170652.2892789786</v>
       </c>
     </row>
     <row r="442">
@@ -8892,7 +8892,7 @@
         <v>78984.19951064256</v>
       </c>
       <c r="F442" s="2" t="n">
-        <v>348398.1965499314</v>
+        <v>207158.8070956474</v>
       </c>
     </row>
     <row r="443">
@@ -8918,7 +8918,7 @@
         <v>78848.33825134594</v>
       </c>
       <c r="F443" s="2" t="n">
-        <v>333675.9443618188</v>
+        <v>257299.3267865074</v>
       </c>
     </row>
     <row r="444">
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="E473" s="2" t="n">
-        <v>6215058.952198651</v>
+        <v>5226220.793494353</v>
       </c>
       <c r="F473" s="2" t="n">
-        <v>6193676.665663028</v>
+        <v>4379590.770767212</v>
       </c>
     </row>
     <row r="474">
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="E474" s="2" t="n">
-        <v>6618612.912963974</v>
+        <v>4680066.072805675</v>
       </c>
       <c r="F474" s="2" t="n">
-        <v>6210278.03366101</v>
+        <v>3105139.016830505</v>
       </c>
     </row>
     <row r="475">
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="E475" s="2" t="n">
-        <v>8836990.792871492</v>
+        <v>5254506.163048157</v>
       </c>
       <c r="F475" s="2" t="n">
-        <v>7840217.249174365</v>
+        <v>2771935.391433466</v>
       </c>
     </row>
     <row r="476">
@@ -9773,10 +9773,10 @@
         </is>
       </c>
       <c r="E476" s="2" t="n">
-        <v>13055956.75314689</v>
+        <v>6527978.376573443</v>
       </c>
       <c r="F476" s="2" t="n">
-        <v>10965833.47744089</v>
+        <v>2741458.369360223</v>
       </c>
     </row>
     <row r="477">
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="E477" s="2" t="n">
-        <v>20435145.50667887</v>
+        <v>8591920.300877156</v>
       </c>
       <c r="F477" s="2" t="n">
-        <v>16257164.20991712</v>
+        <v>2873887.763923908</v>
       </c>
     </row>
     <row r="478">
@@ -9825,10 +9825,10 @@
         </is>
       </c>
       <c r="E478" s="2" t="n">
-        <v>33202244.01616731</v>
+        <v>11738765.94722118</v>
       </c>
       <c r="F478" s="2" t="n">
-        <v>25025623.52386186</v>
+        <v>3128202.940482732</v>
       </c>
     </row>
     <row r="479">
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="E479" s="2" t="n">
-        <v>55375795.60839046</v>
+        <v>16463322.53410859</v>
       </c>
       <c r="F479" s="2" t="n">
-        <v>39550847.33806602</v>
+        <v>3495834.04430255</v>
       </c>
     </row>
     <row r="480">
@@ -9877,10 +9877,10 @@
         </is>
       </c>
       <c r="E480" s="2" t="n">
-        <v>94162551.30680417</v>
+        <v>23540637.82670104</v>
       </c>
       <c r="F480" s="2" t="n">
-        <v>63734633.61066098</v>
+        <v>3983414.600666311</v>
       </c>
     </row>
     <row r="481">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -8996,7 +8996,7 @@
         <v>73669.77095405322</v>
       </c>
       <c r="F446" s="2" t="n">
-        <v>286442.2534907912</v>
+        <v>220877.1720938719</v>
       </c>
     </row>
     <row r="447">
@@ -9022,7 +9022,7 @@
         <v>103165.5186192836</v>
       </c>
       <c r="F447" s="2" t="n">
-        <v>399842.0949667247</v>
+        <v>237747.5321060114</v>
       </c>
     </row>
     <row r="448">
@@ -9048,7 +9048,7 @@
         <v>167287.9720057605</v>
       </c>
       <c r="F448" s="2" t="n">
-        <v>651096.4051923612</v>
+        <v>298529.0180387111</v>
       </c>
     </row>
     <row r="449">
@@ -9074,7 +9074,7 @@
         <v>292546.3669700471</v>
       </c>
       <c r="F449" s="2" t="n">
-        <v>1146453.652119232</v>
+        <v>405332.5758647961</v>
       </c>
     </row>
     <row r="450">
@@ -9100,7 +9100,7 @@
         <v>535767.7056266126</v>
       </c>
       <c r="F450" s="2" t="n">
-        <v>2116722.652082936</v>
+        <v>577075.6050010385</v>
       </c>
     </row>
     <row r="451">
@@ -9126,7 +9126,7 @@
         <v>1012274.320400161</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>4034698.456719378</v>
+        <v>848190.8672212551</v>
       </c>
     </row>
     <row r="452">
@@ -9152,7 +9152,7 @@
         <v>1956055.740709604</v>
       </c>
       <c r="F452" s="2" t="n">
-        <v>7868685.22739314</v>
+        <v>1275552.780747687</v>
       </c>
     </row>
     <row r="453">
@@ -9178,7 +9178,7 @@
         <v>3844472.413788395</v>
       </c>
       <c r="F453" s="2" t="n">
-        <v>15612961.03293186</v>
+        <v>1951620.129116483</v>
       </c>
     </row>
     <row r="454">
@@ -9204,7 +9204,7 @@
         <v>3844472.413788395</v>
       </c>
       <c r="F454" s="2" t="n">
-        <v>15612961.03293186</v>
+        <v>1951620.129116483</v>
       </c>
     </row>
     <row r="455">
@@ -9230,7 +9230,7 @@
         <v>2315021.608712353</v>
       </c>
       <c r="F455" s="2" t="n">
-        <v>7846259.264164844</v>
+        <v>1271917.421226987</v>
       </c>
     </row>
     <row r="456">
@@ -9256,7 +9256,7 @@
         <v>2121517.704119835</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>6247701.835633707</v>
+        <v>1313417.51928961</v>
       </c>
     </row>
     <row r="457">
@@ -9282,7 +9282,7 @@
         <v>2251247.149590914</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>5803410.439569656</v>
+        <v>1582165.990045249</v>
       </c>
     </row>
     <row r="458">
@@ -9308,7 +9308,7 @@
         <v>2576318.391251266</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>5829089.176058053</v>
+        <v>2060894.242265878</v>
       </c>
     </row>
     <row r="459">
@@ -9334,7 +9334,7 @@
         <v>3087647.559750664</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>6139236.485866043</v>
+        <v>2814852.3398644</v>
       </c>
     </row>
     <row r="460">
@@ -9360,7 +9360,7 @@
         <v>3817647.050025986</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>6675252.465644834</v>
+        <v>3969128.863292147</v>
       </c>
     </row>
     <row r="461">
@@ -9386,7 +9386,7 @@
         <v>4827531.833205524</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>7426171.837749272</v>
+        <v>5726361.299758255</v>
       </c>
     </row>
     <row r="462">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>2315021.608712353</v>
+        <v>1946693.372001105</v>
       </c>
       <c r="F455" s="2" t="n">
-        <v>1271917.421226987</v>
+        <v>980782.4080206057</v>
       </c>
     </row>
     <row r="456">
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>2121517.704119835</v>
+        <v>1500139.55499045</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>1313417.51928961</v>
+        <v>780962.7294542136</v>
       </c>
     </row>
     <row r="457">
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>2251247.149590914</v>
+        <v>1338599.563961555</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>1582165.990045249</v>
+        <v>725426.3049462072</v>
       </c>
     </row>
     <row r="458">
@@ -9305,10 +9305,10 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>2576318.391251266</v>
+        <v>1288159.195625633</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>2060894.242265878</v>
+        <v>728636.1470072566</v>
       </c>
     </row>
     <row r="459">
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>3087647.559750664</v>
+        <v>1298195.882280606</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>2814852.3398644</v>
+        <v>767404.5607332553</v>
       </c>
     </row>
     <row r="460">
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>3817647.050025986</v>
+        <v>1349742.058625097</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>3969128.863292147</v>
+        <v>834406.5582056041</v>
       </c>
     </row>
     <row r="461">
@@ -9383,10 +9383,10 @@
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>4827531.833205524</v>
+        <v>1435233.800987535</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>5726361.299758255</v>
+        <v>928271.479718659</v>
       </c>
     </row>
     <row r="462">
@@ -9409,10 +9409,10 @@
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>6209076.829557999</v>
+        <v>1552269.2073895</v>
       </c>
       <c r="F462" s="2" t="n">
-        <v>8405321.038996274</v>
+        <v>1050665.129874534</v>
       </c>
     </row>
     <row r="463">
@@ -9435,10 +9435,10 @@
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>6209076.829557999</v>
+        <v>1552269.2073895</v>
       </c>
       <c r="F463" s="2" t="n">
-        <v>8405321.038996274</v>
+        <v>1050665.129874534</v>
       </c>
     </row>
     <row r="464">
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>4011919.490687458</v>
+        <v>1002979.872671865</v>
       </c>
       <c r="F464" s="2" t="n">
-        <v>5082542.991611379</v>
+        <v>635317.8739514224</v>
       </c>
     </row>
     <row r="465">
@@ -9487,10 +9487,10 @@
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>3945033.502259679</v>
+        <v>986258.3755649199</v>
       </c>
       <c r="F465" s="2" t="n">
-        <v>4869541.573952398</v>
+        <v>608692.6967440498</v>
       </c>
     </row>
     <row r="466">
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>4491941.447956745</v>
+        <v>1122985.361989187</v>
       </c>
       <c r="F466" s="2" t="n">
-        <v>5442525.165719046</v>
+        <v>680315.6457148808</v>
       </c>
     </row>
     <row r="467">
@@ -9539,10 +9539,10 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>5515911.884082857</v>
+        <v>1378977.971020714</v>
       </c>
       <c r="F467" s="2" t="n">
-        <v>6577596.601022505</v>
+        <v>822199.5751278132</v>
       </c>
     </row>
     <row r="468">
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>7093366.232010648</v>
+        <v>1773341.558002662</v>
       </c>
       <c r="F468" s="2" t="n">
-        <v>8335473.495320463</v>
+        <v>1041934.186915058</v>
       </c>
     </row>
     <row r="469">
@@ -9591,10 +9591,10 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>9410816.624785341</v>
+        <v>2352704.156196336</v>
       </c>
       <c r="F469" s="2" t="n">
-        <v>10905183.66204279</v>
+        <v>1363147.957755349</v>
       </c>
     </row>
     <row r="470">
@@ -9617,10 +9617,10 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>12769196.14545644</v>
+        <v>3192299.036364111</v>
       </c>
       <c r="F470" s="2" t="n">
-        <v>14597539.50090802</v>
+        <v>1824692.437613503</v>
       </c>
     </row>
     <row r="471">
@@ -9643,10 +9643,10 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>17622694.8409208</v>
+        <v>4405673.7102302</v>
       </c>
       <c r="F471" s="2" t="n">
-        <v>19880090.03811214</v>
+        <v>2485011.254764018</v>
       </c>
     </row>
     <row r="472">
@@ -9669,10 +9669,10 @@
         </is>
       </c>
       <c r="E472" s="2" t="n">
-        <v>17622694.8409208</v>
+        <v>4405673.7102302</v>
       </c>
       <c r="F472" s="2" t="n">
-        <v>19880090.03811214</v>
+        <v>2485011.254764018</v>
       </c>
     </row>
     <row r="473">
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="E473" s="2" t="n">
-        <v>5226220.793494353</v>
+        <v>1306555.198373588</v>
       </c>
       <c r="F473" s="2" t="n">
-        <v>4379590.770767212</v>
+        <v>547448.8463459016</v>
       </c>
     </row>
     <row r="474">
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="E474" s="2" t="n">
-        <v>4680066.072805675</v>
+        <v>1170016.518201419</v>
       </c>
       <c r="F474" s="2" t="n">
-        <v>3105139.016830505</v>
+        <v>388142.3771038132</v>
       </c>
     </row>
     <row r="475">
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="E475" s="2" t="n">
-        <v>5254506.163048157</v>
+        <v>1313626.540762039</v>
       </c>
       <c r="F475" s="2" t="n">
-        <v>2771935.391433466</v>
+        <v>346491.9239291833</v>
       </c>
     </row>
     <row r="476">
@@ -9773,10 +9773,10 @@
         </is>
       </c>
       <c r="E476" s="2" t="n">
-        <v>6527978.376573443</v>
+        <v>1631994.594143361</v>
       </c>
       <c r="F476" s="2" t="n">
-        <v>2741458.369360223</v>
+        <v>342682.2961700279</v>
       </c>
     </row>
     <row r="477">
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="E477" s="2" t="n">
-        <v>8591920.300877156</v>
+        <v>2147980.075219289</v>
       </c>
       <c r="F477" s="2" t="n">
-        <v>2873887.763923908</v>
+        <v>359235.9704904885</v>
       </c>
     </row>
     <row r="478">
@@ -9825,10 +9825,10 @@
         </is>
       </c>
       <c r="E478" s="2" t="n">
-        <v>11738765.94722118</v>
+        <v>2934691.486805297</v>
       </c>
       <c r="F478" s="2" t="n">
-        <v>3128202.940482732</v>
+        <v>391025.3675603415</v>
       </c>
     </row>
     <row r="479">
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="E479" s="2" t="n">
-        <v>16463322.53410859</v>
+        <v>4115830.633527148</v>
       </c>
       <c r="F479" s="2" t="n">
-        <v>3495834.04430255</v>
+        <v>436979.2555378187</v>
       </c>
     </row>
     <row r="480">
@@ -9877,10 +9877,10 @@
         </is>
       </c>
       <c r="E480" s="2" t="n">
-        <v>23540637.82670104</v>
+        <v>5885159.45667526</v>
       </c>
       <c r="F480" s="2" t="n">
-        <v>3983414.600666311</v>
+        <v>497926.8250832889</v>
       </c>
     </row>
     <row r="481">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>73669.77095405322</v>
+        <v>67555.47782682885</v>
       </c>
       <c r="F446" s="2" t="n">
-        <v>220877.1720938719</v>
+        <v>185734.8222251147</v>
       </c>
     </row>
     <row r="447">
@@ -9019,10 +9019,10 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>103165.5186192836</v>
+        <v>86751.51478474596</v>
       </c>
       <c r="F447" s="2" t="n">
-        <v>237747.5321060114</v>
+        <v>168112.8921625271</v>
       </c>
     </row>
     <row r="448">
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>167287.9720057605</v>
+        <v>128996.6606939122</v>
       </c>
       <c r="F448" s="2" t="n">
-        <v>298529.0180387111</v>
+        <v>177506.4161432054</v>
       </c>
     </row>
     <row r="449">
@@ -9071,10 +9071,10 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>292546.3669700471</v>
+        <v>206861.5198960085</v>
       </c>
       <c r="F449" s="2" t="n">
-        <v>405332.5758647961</v>
+        <v>202666.2879323981</v>
       </c>
     </row>
     <row r="450">
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>535767.7056266126</v>
+        <v>347402.3763806049</v>
       </c>
       <c r="F450" s="2" t="n">
-        <v>577075.6050010385</v>
+        <v>242630.4037878709</v>
       </c>
     </row>
     <row r="451">
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>1012274.320400161</v>
+        <v>601901.9120772079</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>848190.8672212551</v>
+        <v>299880.756976324</v>
       </c>
     </row>
     <row r="452">
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>1956055.740709604</v>
+        <v>1066546.955384046</v>
       </c>
       <c r="F452" s="2" t="n">
-        <v>1275552.780747687</v>
+        <v>379224.110606664</v>
       </c>
     </row>
     <row r="453">
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>3844472.413788395</v>
+        <v>1922236.206894198</v>
       </c>
       <c r="F453" s="2" t="n">
-        <v>1951620.129116483</v>
+        <v>487905.0322791208</v>
       </c>
     </row>
     <row r="454">
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>3844472.413788395</v>
+        <v>1922236.206894198</v>
       </c>
       <c r="F454" s="2" t="n">
-        <v>1951620.129116483</v>
+        <v>487905.0322791208</v>
       </c>
     </row>
     <row r="455">
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>1946693.372001105</v>
+        <v>1061442.087647705</v>
       </c>
       <c r="F455" s="2" t="n">
-        <v>980782.4080206057</v>
+        <v>291588.3544719016</v>
       </c>
     </row>
     <row r="456">
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>1500139.55499045</v>
+        <v>891988.3161458297</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>780962.7294542136</v>
+        <v>276112.0209255147</v>
       </c>
     </row>
     <row r="457">
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>1338599.563961555</v>
+        <v>867974.4311919694</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>725426.3049462072</v>
+        <v>305004.1896800068</v>
       </c>
     </row>
     <row r="458">
@@ -9305,10 +9305,10 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>1288159.195625633</v>
+        <v>910866.1024746936</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>728636.1470072566</v>
+        <v>364318.0735036284</v>
       </c>
     </row>
     <row r="459">
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>1298195.882280606</v>
+        <v>1001045.871576582</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>767404.5607332553</v>
+        <v>456301.4818547625</v>
       </c>
     </row>
     <row r="460">
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>1349742.058625097</v>
+        <v>1134993.258615013</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>834406.5582056041</v>
+        <v>590014.5355737103</v>
       </c>
     </row>
     <row r="461">
@@ -9383,10 +9383,10 @@
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>1435233.800987535</v>
+        <v>1316115.198449578</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>928271.479718659</v>
+        <v>780580.1596776814</v>
       </c>
     </row>
     <row r="462">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>1002979.872671865</v>
+        <v>843402.179501398</v>
       </c>
       <c r="F464" s="2" t="n">
-        <v>635317.8739514224</v>
+        <v>346409.5271222388</v>
       </c>
     </row>
     <row r="465">
@@ -9487,10 +9487,10 @@
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>986258.3755649199</v>
+        <v>697389.9853639835</v>
       </c>
       <c r="F465" s="2" t="n">
-        <v>608692.6967440498</v>
+        <v>180965.4214545544</v>
       </c>
     </row>
     <row r="466">
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>1122985.361989187</v>
+        <v>667731.0912607233</v>
       </c>
       <c r="F466" s="2" t="n">
-        <v>680315.6457148808</v>
+        <v>110282.529876375</v>
       </c>
     </row>
     <row r="467">
@@ -9539,10 +9539,10 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>1378977.971020714</v>
+        <v>689488.9855103572</v>
       </c>
       <c r="F467" s="2" t="n">
-        <v>822199.5751278132</v>
+        <v>72672.86188269686</v>
       </c>
     </row>
     <row r="468">
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>1773341.558002662</v>
+        <v>745598.2795724379</v>
       </c>
       <c r="F468" s="2" t="n">
-        <v>1041934.186915058</v>
+        <v>50215.06820071946</v>
       </c>
     </row>
     <row r="469">
@@ -9591,10 +9591,10 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>2352704.156196336</v>
+        <v>831806.5314861018</v>
       </c>
       <c r="F469" s="2" t="n">
-        <v>1363147.957755349</v>
+        <v>35820.81972302797</v>
       </c>
     </row>
     <row r="470">
@@ -9617,10 +9617,10 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>3192299.036364111</v>
+        <v>949076.1818151328</v>
       </c>
       <c r="F470" s="2" t="n">
-        <v>1824692.437613503</v>
+        <v>26144.5366077589</v>
       </c>
     </row>
     <row r="471">
@@ -9643,10 +9643,10 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>4405673.7102302</v>
+        <v>1101418.42755755</v>
       </c>
       <c r="F471" s="2" t="n">
-        <v>2485011.254764018</v>
+        <v>19414.15042784389</v>
       </c>
     </row>
     <row r="472">
@@ -9669,10 +9669,10 @@
         </is>
       </c>
       <c r="E472" s="2" t="n">
-        <v>4405673.7102302</v>
+        <v>1101418.42755755</v>
       </c>
       <c r="F472" s="2" t="n">
-        <v>2485011.254764018</v>
+        <v>19414.15042784389</v>
       </c>
     </row>
     <row r="473">
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="E473" s="2" t="n">
-        <v>1306555.198373588</v>
+        <v>326638.799593397</v>
       </c>
       <c r="F473" s="2" t="n">
-        <v>547448.8463459016</v>
+        <v>4276.944112077356</v>
       </c>
     </row>
     <row r="474">
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="E474" s="2" t="n">
-        <v>1170016.518201419</v>
+        <v>292504.1295503547</v>
       </c>
       <c r="F474" s="2" t="n">
-        <v>388142.3771038132</v>
+        <v>3032.362321123541</v>
       </c>
     </row>
     <row r="475">
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="E475" s="2" t="n">
-        <v>1313626.540762039</v>
+        <v>328406.6351905098</v>
       </c>
       <c r="F475" s="2" t="n">
-        <v>346491.9239291833</v>
+        <v>2706.968155696744</v>
       </c>
     </row>
     <row r="476">
@@ -9773,10 +9773,10 @@
         </is>
       </c>
       <c r="E476" s="2" t="n">
-        <v>1631994.594143361</v>
+        <v>407998.6485358402</v>
       </c>
       <c r="F476" s="2" t="n">
-        <v>342682.2961700279</v>
+        <v>2677.205438828343</v>
       </c>
     </row>
     <row r="477">
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="E477" s="2" t="n">
-        <v>2147980.075219289</v>
+        <v>536995.0188048223</v>
       </c>
       <c r="F477" s="2" t="n">
-        <v>359235.9704904885</v>
+        <v>2806.531019456942</v>
       </c>
     </row>
     <row r="478">
@@ -9825,10 +9825,10 @@
         </is>
       </c>
       <c r="E478" s="2" t="n">
-        <v>2934691.486805297</v>
+        <v>733672.871701324</v>
       </c>
       <c r="F478" s="2" t="n">
-        <v>391025.3675603415</v>
+        <v>3054.885684065168</v>
       </c>
     </row>
     <row r="479">
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="E479" s="2" t="n">
-        <v>4115830.633527148</v>
+        <v>1028957.658381787</v>
       </c>
       <c r="F479" s="2" t="n">
-        <v>436979.2555378187</v>
+        <v>3413.900433889209</v>
       </c>
     </row>
     <row r="480">
@@ -9877,10 +9877,10 @@
         </is>
       </c>
       <c r="E480" s="2" t="n">
-        <v>5885159.45667526</v>
+        <v>1471289.864168815</v>
       </c>
       <c r="F480" s="2" t="n">
-        <v>497926.8250832889</v>
+        <v>3890.053320963194</v>
       </c>
     </row>
     <row r="481">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -8996,7 +8996,7 @@
         <v>67555.47782682885</v>
       </c>
       <c r="F446" s="2" t="n">
-        <v>185734.8222251147</v>
+        <v>156183.7461968849</v>
       </c>
     </row>
     <row r="447">
@@ -9022,7 +9022,7 @@
         <v>86751.51478474596</v>
       </c>
       <c r="F447" s="2" t="n">
-        <v>168112.8921625271</v>
+        <v>118873.7660530057</v>
       </c>
     </row>
     <row r="448">
@@ -9048,7 +9048,7 @@
         <v>128996.6606939122</v>
       </c>
       <c r="F448" s="2" t="n">
-        <v>177506.4161432054</v>
+        <v>105545.9465180669</v>
       </c>
     </row>
     <row r="449">
@@ -9074,7 +9074,7 @@
         <v>206861.5198960085</v>
       </c>
       <c r="F449" s="2" t="n">
-        <v>202666.2879323981</v>
+        <v>101333.143966199</v>
       </c>
     </row>
     <row r="450">
@@ -9100,7 +9100,7 @@
         <v>347402.3763806049</v>
       </c>
       <c r="F450" s="2" t="n">
-        <v>242630.4037878709</v>
+        <v>102013.518388391</v>
       </c>
     </row>
     <row r="451">
@@ -9126,7 +9126,7 @@
         <v>601901.9120772079</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>299880.756976324</v>
+        <v>106023.8584026569</v>
       </c>
     </row>
     <row r="452">
@@ -9152,7 +9152,7 @@
         <v>1066546.955384046</v>
       </c>
       <c r="F452" s="2" t="n">
-        <v>379224.110606664</v>
+        <v>112744.0026285059</v>
       </c>
     </row>
     <row r="453">
@@ -9178,7 +9178,7 @@
         <v>1922236.206894198</v>
       </c>
       <c r="F453" s="2" t="n">
-        <v>487905.0322791208</v>
+        <v>121976.2580697802</v>
       </c>
     </row>
     <row r="454">
@@ -9204,7 +9204,7 @@
         <v>1922236.206894198</v>
       </c>
       <c r="F454" s="2" t="n">
-        <v>487905.0322791208</v>
+        <v>121976.2580697802</v>
       </c>
     </row>
     <row r="455">
@@ -9230,7 +9230,7 @@
         <v>1061442.087647705</v>
       </c>
       <c r="F455" s="2" t="n">
-        <v>291588.3544719016</v>
+        <v>72897.0886179754</v>
       </c>
     </row>
     <row r="456">
@@ -9256,7 +9256,7 @@
         <v>891988.3161458297</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>276112.0209255147</v>
+        <v>69028.0052313787</v>
       </c>
     </row>
     <row r="457">
@@ -9282,7 +9282,7 @@
         <v>867974.4311919694</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>305004.1896800068</v>
+        <v>76251.04742000171</v>
       </c>
     </row>
     <row r="458">
@@ -9308,7 +9308,7 @@
         <v>910866.1024746936</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>364318.0735036284</v>
+        <v>91079.51837590709</v>
       </c>
     </row>
     <row r="459">
@@ -9334,7 +9334,7 @@
         <v>1001045.871576582</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>456301.4818547625</v>
+        <v>114075.3704636906</v>
       </c>
     </row>
     <row r="460">
@@ -9360,7 +9360,7 @@
         <v>1134993.258615013</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>590014.5355737103</v>
+        <v>147503.6338934276</v>
       </c>
     </row>
     <row r="461">
@@ -9386,7 +9386,7 @@
         <v>1316115.198449578</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>780580.1596776814</v>
+        <v>195145.0399194203</v>
       </c>
     </row>
     <row r="462">
@@ -9412,7 +9412,7 @@
         <v>1552269.2073895</v>
       </c>
       <c r="F462" s="2" t="n">
-        <v>1050665.129874534</v>
+        <v>262666.2824686335</v>
       </c>
     </row>
     <row r="463">
@@ -9438,7 +9438,7 @@
         <v>1552269.2073895</v>
       </c>
       <c r="F463" s="2" t="n">
-        <v>1050665.129874534</v>
+        <v>262666.2824686335</v>
       </c>
     </row>
     <row r="464">
@@ -9464,7 +9464,7 @@
         <v>843402.179501398</v>
       </c>
       <c r="F464" s="2" t="n">
-        <v>346409.5271222388</v>
+        <v>102988.1685896236</v>
       </c>
     </row>
     <row r="465">
@@ -9490,7 +9490,7 @@
         <v>697389.9853639835</v>
       </c>
       <c r="F465" s="2" t="n">
-        <v>180965.4214545544</v>
+        <v>63980.93833539847</v>
       </c>
     </row>
     <row r="466">
@@ -9516,7 +9516,7 @@
         <v>667731.0912607233</v>
       </c>
       <c r="F466" s="2" t="n">
-        <v>110282.529876375</v>
+        <v>46368.0920190772</v>
       </c>
     </row>
     <row r="467">
@@ -9542,7 +9542,7 @@
         <v>689488.9855103572</v>
       </c>
       <c r="F467" s="2" t="n">
-        <v>72672.86188269686</v>
+        <v>36336.43094134843</v>
       </c>
     </row>
     <row r="468">
@@ -9568,7 +9568,7 @@
         <v>745598.2795724379</v>
       </c>
       <c r="F468" s="2" t="n">
-        <v>50215.06820071946</v>
+        <v>29858.05819232124</v>
       </c>
     </row>
     <row r="469">
@@ -9594,7 +9594,7 @@
         <v>831806.5314861018</v>
       </c>
       <c r="F469" s="2" t="n">
-        <v>35820.81972302797</v>
+        <v>25329.1445338139</v>
       </c>
     </row>
     <row r="470">
@@ -9620,7 +9620,7 @@
         <v>949076.1818151328</v>
       </c>
       <c r="F470" s="2" t="n">
-        <v>26144.5366077589</v>
+        <v>21984.84711193397</v>
       </c>
     </row>
     <row r="471">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="17700" windowHeight="13908" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monGroup" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="monGroup" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2280"/>
+  <dimension ref="A1:D2298"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="50.7777777777778" customWidth="1" style="3" min="2" max="2"/>
@@ -45241,6 +45241,366 @@
         </is>
       </c>
     </row>
+    <row r="2281">
+      <c r="A2281" t="n">
+        <v>33001</v>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>开局教学 1</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,270001,270001,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2281" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="n">
+        <v>33002</v>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>开局教学 2</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,270002,270002,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="n">
+        <v>33003</v>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>开局教学 3</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,270001,270001,270003,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2283" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="n">
+        <v>33004</v>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>开局教学 4</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,270003,270003,270003,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="n">
+        <v>33005</v>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>开局教学 5</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,270002,270002,270005,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2285" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="n">
+        <v>33006</v>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>开局教学 6</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>{null,null,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="n">
+        <v>33007</v>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>开局教学 7</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>{null,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,null,null}</t>
+        </is>
+      </c>
+      <c r="D2287" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="n">
+        <v>33008</v>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>开局教学 8</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>{null,null,270004,270004,270004,270004,270004,270004,270004,270004,270003,270003,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2288" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="n">
+        <v>33009</v>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>开局教学 9</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,270001,270001,270001,270001,270005,270005,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2289" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="n">
+        <v>33010</v>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>开局教学 10</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>{null,null,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,270005,null,null}</t>
+        </is>
+      </c>
+      <c r="D2290" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="n">
+        <v>33011</v>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>开局教学 11</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>{null,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,270005,270005,null,null}</t>
+        </is>
+      </c>
+      <c r="D2291" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="n">
+        <v>33012</v>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>开局教学 12</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,270005,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2292" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="n">
+        <v>33013</v>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>开局教学 13</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,270005,270005,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2293" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="n">
+        <v>33014</v>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>开局教学 14</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,270006,270002,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2294" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="n">
+        <v>33015</v>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>开局教学 15</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,270006,270006,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2295" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="n">
+        <v>33016</v>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>开局教学 16</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,270007,270005,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2296" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="n">
+        <v>33017</v>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>开局教学 17</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,270007,270007,270006,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2297" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="n">
+        <v>33018</v>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>开局教学 18</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,270008,270007,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2298" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -45247,12 +45247,12 @@
       </c>
       <c r="B2281" t="inlineStr">
         <is>
-          <t>开局教学 1</t>
+          <t>初见侦察，提示免费填槽</t>
         </is>
       </c>
       <c r="C2281" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,270001,270001,null,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,null,271001,271002,null,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2281" t="inlineStr">
@@ -45267,12 +45267,12 @@
       </c>
       <c r="B2282" t="inlineStr">
         <is>
-          <t>开局教学 2</t>
+          <t>物理来袭，比较装甲槽</t>
         </is>
       </c>
       <c r="C2282" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,270002,270002,null,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,271003,271003,271004,271004,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2282" t="inlineStr">
@@ -45287,12 +45287,12 @@
       </c>
       <c r="B2283" t="inlineStr">
         <is>
-          <t>开局教学 3</t>
+          <t>能量抗性首次出现</t>
         </is>
       </c>
       <c r="C2283" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,270001,270001,270003,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,271005,271005,271006,271007,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2283" t="inlineStr">
@@ -45307,12 +45307,12 @@
       </c>
       <c r="B2284" t="inlineStr">
         <is>
-          <t>开局教学 4</t>
+          <t>抗性与免费补槽复习</t>
         </is>
       </c>
       <c r="C2284" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,270003,270003,270003,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,271008,271009,271009,271010,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2284" t="inlineStr">
@@ -45327,12 +45327,12 @@
       </c>
       <c r="B2285" t="inlineStr">
         <is>
-          <t>开局教学 5</t>
+          <t>装甲锚舰，选择槽级投资</t>
         </is>
       </c>
       <c r="C2285" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,270002,270002,270005,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,null,271011,271010,271010,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2285" t="inlineStr">
@@ -45347,12 +45347,12 @@
       </c>
       <c r="B2286" t="inlineStr">
         <is>
-          <t>开局教学 6</t>
+          <t>十艇蜂群，免费换导弹</t>
         </is>
       </c>
       <c r="C2286" t="inlineStr">
         <is>
-          <t>{null,null,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,null,null,null}</t>
+          <t>{null,null,271012,271012,271012,271012,271012,271013,271013,271013,271013,271013,null,null,null}</t>
         </is>
       </c>
       <c r="D2286" t="inlineStr">
@@ -45367,12 +45367,12 @@
       </c>
       <c r="B2287" t="inlineStr">
         <is>
-          <t>开局教学 7</t>
+          <t>十二艇蜂群，检验多弹</t>
         </is>
       </c>
       <c r="C2287" t="inlineStr">
         <is>
-          <t>{null,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,null,null}</t>
+          <t>{null,271012,271012,271012,271012,271012,271012,271012,271013,271013,271013,271013,271013,null,null}</t>
         </is>
       </c>
       <c r="D2287" t="inlineStr">
@@ -45387,12 +45387,12 @@
       </c>
       <c r="B2288" t="inlineStr">
         <is>
-          <t>开局教学 8</t>
+          <t>十艇与拦截，自动转火</t>
         </is>
       </c>
       <c r="C2288" t="inlineStr">
         <is>
-          <t>{null,null,270004,270004,270004,270004,270004,270004,270004,270004,270003,270003,null,null,null}</t>
+          <t>{null,null,271014,271014,271014,271012,271012,271012,271012,271012,271012,271012,271015,null,null}</t>
         </is>
       </c>
       <c r="D2288" t="inlineStr">
@@ -45407,12 +45407,12 @@
       </c>
       <c r="B2289" t="inlineStr">
         <is>
-          <t>开局教学 9</t>
+          <t>厚单体与侦察，分炉选择</t>
         </is>
       </c>
       <c r="C2289" t="inlineStr">
         <is>
-          <t>{null,null,null,null,270001,270001,270001,270001,270005,270005,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,271016,271017,271017,271017,271018,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2289" t="inlineStr">
@@ -45427,12 +45427,12 @@
       </c>
       <c r="B2290" t="inlineStr">
         <is>
-          <t>开局教学 10</t>
+          <t>十二艇转厚舰</t>
         </is>
       </c>
       <c r="C2290" t="inlineStr">
         <is>
-          <t>{null,null,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,270005,null,null}</t>
+          <t>{null,271013,271013,271013,271013,271013,271013,271013,271013,271013,271013,271013,271013,271019,null}</t>
         </is>
       </c>
       <c r="D2290" t="inlineStr">
@@ -45447,12 +45447,12 @@
       </c>
       <c r="B2291" t="inlineStr">
         <is>
-          <t>开局教学 11</t>
+          <t>十四艇加厚舰</t>
         </is>
       </c>
       <c r="C2291" t="inlineStr">
         <is>
-          <t>{null,270004,270004,270004,270004,270004,270004,270004,270004,270004,270004,270005,270005,null,null}</t>
+          <t>{271013,271013,271013,271013,271013,271013,271013,271013,271013,271013,271013,271020,271020,271020,271019}</t>
         </is>
       </c>
       <c r="D2291" t="inlineStr">
@@ -45467,12 +45467,12 @@
       </c>
       <c r="B2292" t="inlineStr">
         <is>
-          <t>开局教学 12</t>
+          <t>磁轨大击或其他单体路线</t>
         </is>
       </c>
       <c r="C2292" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,null,270005,null,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,null,null,271021,null,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2292" t="inlineStr">
@@ -45487,12 +45487,12 @@
       </c>
       <c r="B2293" t="inlineStr">
         <is>
-          <t>开局教学 13</t>
+          <t>双锚舰持续输出</t>
         </is>
       </c>
       <c r="C2293" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,270005,270005,null,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,null,271022,271023,null,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2293" t="inlineStr">
@@ -45507,12 +45507,12 @@
       </c>
       <c r="B2294" t="inlineStr">
         <is>
-          <t>开局教学 14</t>
+          <t>反应机制首次单独呈现</t>
         </is>
       </c>
       <c r="C2294" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,270006,270002,null,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,null,271024,271025,null,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2294" t="inlineStr">
@@ -45527,12 +45527,12 @@
       </c>
       <c r="B2295" t="inlineStr">
         <is>
-          <t>开局教学 15</t>
+          <t>双反应机制复习</t>
         </is>
       </c>
       <c r="C2295" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,270006,270006,null,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,null,271026,271027,null,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2295" t="inlineStr">
@@ -45547,12 +45547,12 @@
       </c>
       <c r="B2296" t="inlineStr">
         <is>
-          <t>开局教学 16</t>
+          <t>护盾恢复首次单独呈现</t>
         </is>
       </c>
       <c r="C2296" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,270007,270005,null,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,null,null,271028,null,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2296" t="inlineStr">
@@ -45567,12 +45567,12 @@
       </c>
       <c r="B2297" t="inlineStr">
         <is>
-          <t>开局教学 17</t>
+          <t>护盾与反应组合</t>
         </is>
       </c>
       <c r="C2297" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,270007,270007,270006,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,null,271029,271030,null,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2297" t="inlineStr">
@@ -45587,12 +45587,12 @@
       </c>
       <c r="B2298" t="inlineStr">
         <is>
-          <t>开局教学 18</t>
+          <t>指挥舰与已学护盾</t>
         </is>
       </c>
       <c r="C2298" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,270008,270007,null,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,null,271031,271032,null,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2298" t="inlineStr">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -45242,360 +45242,360 @@
       </c>
     </row>
     <row r="2281">
-      <c r="A2281" t="n">
+      <c r="A2281" s="2" t="n">
         <v>33001</v>
       </c>
-      <c r="B2281" t="inlineStr">
+      <c r="B2281" s="2" t="inlineStr">
         <is>
           <t>初见侦察，提示免费填槽</t>
         </is>
       </c>
-      <c r="C2281" t="inlineStr">
-        <is>
-          <t>{null,null,null,null,null,null,271001,271002,null,null,null,null,null,null,null}</t>
-        </is>
-      </c>
-      <c r="D2281" t="inlineStr">
+      <c r="C2281" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,271001,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2281" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2282">
-      <c r="A2282" t="n">
+      <c r="A2282" s="2" t="n">
         <v>33002</v>
       </c>
-      <c r="B2282" t="inlineStr">
+      <c r="B2282" s="2" t="inlineStr">
         <is>
           <t>物理来袭，比较装甲槽</t>
         </is>
       </c>
-      <c r="C2282" t="inlineStr">
+      <c r="C2282" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,271003,271003,271004,271004,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2282" t="inlineStr">
+      <c r="D2282" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2283">
-      <c r="A2283" t="n">
+      <c r="A2283" s="2" t="n">
         <v>33003</v>
       </c>
-      <c r="B2283" t="inlineStr">
+      <c r="B2283" s="2" t="inlineStr">
         <is>
           <t>能量抗性首次出现</t>
         </is>
       </c>
-      <c r="C2283" t="inlineStr">
+      <c r="C2283" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,271005,271005,271006,271007,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2283" t="inlineStr">
+      <c r="D2283" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2284">
-      <c r="A2284" t="n">
+      <c r="A2284" s="2" t="n">
         <v>33004</v>
       </c>
-      <c r="B2284" t="inlineStr">
+      <c r="B2284" s="2" t="inlineStr">
         <is>
           <t>抗性与免费补槽复习</t>
         </is>
       </c>
-      <c r="C2284" t="inlineStr">
+      <c r="C2284" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,271008,271009,271009,271010,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2284" t="inlineStr">
+      <c r="D2284" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2285">
-      <c r="A2285" t="n">
+      <c r="A2285" s="2" t="n">
         <v>33005</v>
       </c>
-      <c r="B2285" t="inlineStr">
+      <c r="B2285" s="2" t="inlineStr">
         <is>
           <t>装甲锚舰，选择槽级投资</t>
         </is>
       </c>
-      <c r="C2285" t="inlineStr">
+      <c r="C2285" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,271011,271010,271010,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2285" t="inlineStr">
+      <c r="D2285" s="2" t="inlineStr">
         <is>
           <t>elite</t>
         </is>
       </c>
     </row>
     <row r="2286">
-      <c r="A2286" t="n">
+      <c r="A2286" s="2" t="n">
         <v>33006</v>
       </c>
-      <c r="B2286" t="inlineStr">
+      <c r="B2286" s="2" t="inlineStr">
         <is>
           <t>十艇蜂群，免费换导弹</t>
         </is>
       </c>
-      <c r="C2286" t="inlineStr">
+      <c r="C2286" s="2" t="inlineStr">
         <is>
           <t>{null,null,271012,271012,271012,271012,271012,271013,271013,271013,271013,271013,null,null,null}</t>
         </is>
       </c>
-      <c r="D2286" t="inlineStr">
+      <c r="D2286" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2287">
-      <c r="A2287" t="n">
+      <c r="A2287" s="2" t="n">
         <v>33007</v>
       </c>
-      <c r="B2287" t="inlineStr">
+      <c r="B2287" s="2" t="inlineStr">
         <is>
           <t>十二艇蜂群，检验多弹</t>
         </is>
       </c>
-      <c r="C2287" t="inlineStr">
+      <c r="C2287" s="2" t="inlineStr">
         <is>
           <t>{null,271012,271012,271012,271012,271012,271012,271012,271013,271013,271013,271013,271013,null,null}</t>
         </is>
       </c>
-      <c r="D2287" t="inlineStr">
+      <c r="D2287" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2288">
-      <c r="A2288" t="n">
+      <c r="A2288" s="2" t="n">
         <v>33008</v>
       </c>
-      <c r="B2288" t="inlineStr">
+      <c r="B2288" s="2" t="inlineStr">
         <is>
           <t>十艇与拦截，自动转火</t>
         </is>
       </c>
-      <c r="C2288" t="inlineStr">
+      <c r="C2288" s="2" t="inlineStr">
         <is>
           <t>{null,null,271014,271014,271014,271012,271012,271012,271012,271012,271012,271012,271015,null,null}</t>
         </is>
       </c>
-      <c r="D2288" t="inlineStr">
+      <c r="D2288" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2289">
-      <c r="A2289" t="n">
+      <c r="A2289" s="2" t="n">
         <v>33009</v>
       </c>
-      <c r="B2289" t="inlineStr">
+      <c r="B2289" s="2" t="inlineStr">
         <is>
           <t>厚单体与侦察，分炉选择</t>
         </is>
       </c>
-      <c r="C2289" t="inlineStr">
+      <c r="C2289" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,271016,271017,271017,271017,271018,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2289" t="inlineStr">
+      <c r="D2289" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2290">
-      <c r="A2290" t="n">
+      <c r="A2290" s="2" t="n">
         <v>33010</v>
       </c>
-      <c r="B2290" t="inlineStr">
+      <c r="B2290" s="2" t="inlineStr">
         <is>
           <t>十二艇转厚舰</t>
         </is>
       </c>
-      <c r="C2290" t="inlineStr">
+      <c r="C2290" s="2" t="inlineStr">
         <is>
           <t>{null,271013,271013,271013,271013,271013,271013,271013,271013,271013,271013,271013,271013,271019,null}</t>
         </is>
       </c>
-      <c r="D2290" t="inlineStr">
+      <c r="D2290" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2291">
-      <c r="A2291" t="n">
+      <c r="A2291" s="2" t="n">
         <v>33011</v>
       </c>
-      <c r="B2291" t="inlineStr">
+      <c r="B2291" s="2" t="inlineStr">
         <is>
           <t>十四艇加厚舰</t>
         </is>
       </c>
-      <c r="C2291" t="inlineStr">
+      <c r="C2291" s="2" t="inlineStr">
         <is>
           <t>{271013,271013,271013,271013,271013,271013,271013,271013,271013,271013,271013,271020,271020,271020,271019}</t>
         </is>
       </c>
-      <c r="D2291" t="inlineStr">
+      <c r="D2291" s="2" t="inlineStr">
         <is>
           <t>elite</t>
         </is>
       </c>
     </row>
     <row r="2292">
-      <c r="A2292" t="n">
+      <c r="A2292" s="2" t="n">
         <v>33012</v>
       </c>
-      <c r="B2292" t="inlineStr">
+      <c r="B2292" s="2" t="inlineStr">
         <is>
           <t>磁轨大击或其他单体路线</t>
         </is>
       </c>
-      <c r="C2292" t="inlineStr">
+      <c r="C2292" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,271021,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2292" t="inlineStr">
+      <c r="D2292" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2293">
-      <c r="A2293" t="n">
+      <c r="A2293" s="2" t="n">
         <v>33013</v>
       </c>
-      <c r="B2293" t="inlineStr">
+      <c r="B2293" s="2" t="inlineStr">
         <is>
           <t>双锚舰持续输出</t>
         </is>
       </c>
-      <c r="C2293" t="inlineStr">
+      <c r="C2293" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,271022,271023,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2293" t="inlineStr">
+      <c r="D2293" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2294">
-      <c r="A2294" t="n">
+      <c r="A2294" s="2" t="n">
         <v>33014</v>
       </c>
-      <c r="B2294" t="inlineStr">
-        <is>
-          <t>反应机制首次单独呈现</t>
-        </is>
-      </c>
-      <c r="C2294" t="inlineStr">
-        <is>
-          <t>{null,null,null,null,null,null,271024,271025,null,null,null,null,null,null,null}</t>
-        </is>
-      </c>
-      <c r="D2294" t="inlineStr">
+      <c r="B2294" s="2" t="inlineStr">
+        <is>
+          <t>慢射能量单体，展示玩家护盾恢复</t>
+        </is>
+      </c>
+      <c r="C2294" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,271024,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2294" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2295">
-      <c r="A2295" t="n">
+      <c r="A2295" s="2" t="n">
         <v>33015</v>
       </c>
-      <c r="B2295" t="inlineStr">
+      <c r="B2295" s="2" t="inlineStr">
         <is>
           <t>双反应机制复习</t>
         </is>
       </c>
-      <c r="C2295" t="inlineStr">
+      <c r="C2295" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,271026,271027,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2295" t="inlineStr">
+      <c r="D2295" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2296">
-      <c r="A2296" t="n">
+      <c r="A2296" s="2" t="n">
         <v>33016</v>
       </c>
-      <c r="B2296" t="inlineStr">
+      <c r="B2296" s="2" t="inlineStr">
         <is>
           <t>护盾恢复首次单独呈现</t>
         </is>
       </c>
-      <c r="C2296" t="inlineStr">
+      <c r="C2296" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,271028,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2296" t="inlineStr">
+      <c r="D2296" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2297">
-      <c r="A2297" t="n">
+      <c r="A2297" s="2" t="n">
         <v>33017</v>
       </c>
-      <c r="B2297" t="inlineStr">
+      <c r="B2297" s="2" t="inlineStr">
         <is>
           <t>护盾与反应组合</t>
         </is>
       </c>
-      <c r="C2297" t="inlineStr">
+      <c r="C2297" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,271029,271030,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2297" t="inlineStr">
+      <c r="D2297" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2298">
-      <c r="A2298" t="n">
+      <c r="A2298" s="2" t="n">
         <v>33018</v>
       </c>
-      <c r="B2298" t="inlineStr">
+      <c r="B2298" s="2" t="inlineStr">
         <is>
           <t>指挥舰与已学护盾</t>
         </is>
       </c>
-      <c r="C2298" t="inlineStr">
+      <c r="C2298" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,271031,271032,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2298" t="inlineStr">
+      <c r="D2298" s="2" t="inlineStr">
         <is>
           <t>elite</t>
         </is>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -45532,7 +45532,7 @@
       </c>
       <c r="C2295" s="2" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,271026,271027,null,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,271008,271026,271027,271008,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2295" s="2" t="inlineStr">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2298"/>
+  <dimension ref="A1:D2333"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="50.7777777777778" customWidth="1" style="3" min="2" max="2"/>
@@ -45601,6 +45601,706 @@
         </is>
       </c>
     </row>
+    <row r="2299">
+      <c r="A2299" t="n">
+        <v>90401</v>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>第4关第1点重堡</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,400001,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2299" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="n">
+        <v>90402</v>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>第4关第2点哨卫</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,400002,400002,400002,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2300" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="n">
+        <v>90403</v>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>第4关第3点重堡</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,400003,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2301" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="n">
+        <v>90404</v>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>第4关第4点蜂群</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>{null,null,400004,400004,400004,400004,400004,400004,400004,400004,400004,400004,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2302" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="n">
+        <v>90405</v>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>第4关第5点重堡</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,400005,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2303" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="n">
+        <v>90406</v>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>第4关第6点哨卫</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,400006,400006,400006,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2304" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="n">
+        <v>90407</v>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>第4关第7点重堡</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,400007,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2305" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="n">
+        <v>90408</v>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>第4关第8点重堡</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,400008,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2306" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="n">
+        <v>90501</v>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>第5关第1点哨卫</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,500001,500001,500001,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2307" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="n">
+        <v>90502</v>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>第5关第2点哨卫</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,500002,500002,500002,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2308" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="n">
+        <v>90503</v>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>第5关第3点蜂群</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>{null,null,500003,500003,500003,500003,500003,500003,500003,500003,500003,500003,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2309" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="n">
+        <v>90504</v>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>第5关第4点蜂群</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>{null,null,500004,500004,500004,500004,500004,500004,500004,500004,500004,500004,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2310" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="n">
+        <v>90505</v>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>第5关第5点重堡</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,500005,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2311" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="n">
+        <v>90506</v>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>第5关第6点重堡</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,500006,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2312" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="n">
+        <v>90507</v>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>第5关第7点哨卫</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,500007,500007,500007,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2313" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="n">
+        <v>90508</v>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>第5关第8点蜂群</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>{null,null,500008,500008,500008,500008,500008,500008,500008,500008,500008,500008,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2314" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="n">
+        <v>90509</v>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>第5关第9点重堡</t>
+        </is>
+      </c>
+      <c r="C2315" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,500009,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2315" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="n">
+        <v>90601</v>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>第6关第1点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2316" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,600001,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2316" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="n">
+        <v>90602</v>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>第6关第2点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2317" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,600002,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2317" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="n">
+        <v>90603</v>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>第6关第3点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2318" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,600003,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2318" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="n">
+        <v>90604</v>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>第6关第4点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2319" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,600004,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2319" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="n">
+        <v>90605</v>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>第6关第5点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2320" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,600005,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2320" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="n">
+        <v>90606</v>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>第6关第6点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,600006,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2321" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="n">
+        <v>90607</v>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>第6关第7点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,600007,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2322" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="n">
+        <v>90608</v>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>第6关第8点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,600008,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2323" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="n">
+        <v>90609</v>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>第6关第9点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2324" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,600009,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2324" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="n">
+        <v>90701</v>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>第7关第1点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2325" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,700001,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2325" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="n">
+        <v>90702</v>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>第7关第2点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2326" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,700002,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2326" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="n">
+        <v>90703</v>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>第7关第3点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2327" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,700003,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2327" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="n">
+        <v>90704</v>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>第7关第4点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2328" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,700004,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2328" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="n">
+        <v>90705</v>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>第7关第5点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2329" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,700005,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2329" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="n">
+        <v>90706</v>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>第7关第6点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2330" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,700006,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2330" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="n">
+        <v>90707</v>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>第7关第7点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2331" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,700007,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2331" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="n">
+        <v>90708</v>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>第7关第8点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2332" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,700008,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2332" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="n">
+        <v>90709</v>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>第7关第9点光束靶舰</t>
+        </is>
+      </c>
+      <c r="C2333" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,700009,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2333" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="17700" windowHeight="13908" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="monGroup" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monGroup" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -45602,700 +45602,700 @@
       </c>
     </row>
     <row r="2299">
-      <c r="A2299" t="n">
+      <c r="A2299" s="2" t="n">
         <v>90401</v>
       </c>
-      <c r="B2299" t="inlineStr">
-        <is>
-          <t>第4关第1点重堡</t>
-        </is>
-      </c>
-      <c r="C2299" t="inlineStr">
+      <c r="B2299" s="2" t="inlineStr">
+        <is>
+          <t>磁轨壁垒</t>
+        </is>
+      </c>
+      <c r="C2299" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,400001,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2299" t="inlineStr">
+      <c r="D2299" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2300">
-      <c r="A2300" t="n">
+      <c r="A2300" s="2" t="n">
         <v>90402</v>
       </c>
-      <c r="B2300" t="inlineStr">
-        <is>
-          <t>第4关第2点哨卫</t>
-        </is>
-      </c>
-      <c r="C2300" t="inlineStr">
+      <c r="B2300" s="2" t="inlineStr">
+        <is>
+          <t>能量哨卫</t>
+        </is>
+      </c>
+      <c r="C2300" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,400002,400002,400002,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2300" t="inlineStr">
+      <c r="D2300" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2301">
-      <c r="A2301" t="n">
+      <c r="A2301" s="2" t="n">
         <v>90403</v>
       </c>
-      <c r="B2301" t="inlineStr">
-        <is>
-          <t>第4关第3点重堡</t>
-        </is>
-      </c>
-      <c r="C2301" t="inlineStr">
+      <c r="B2301" s="2" t="inlineStr">
+        <is>
+          <t>轨道重堡</t>
+        </is>
+      </c>
+      <c r="C2301" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,400003,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2301" t="inlineStr">
+      <c r="D2301" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2302">
-      <c r="A2302" t="n">
+      <c r="A2302" s="2" t="n">
         <v>90404</v>
       </c>
-      <c r="B2302" t="inlineStr">
-        <is>
-          <t>第4关第4点蜂群</t>
-        </is>
-      </c>
-      <c r="C2302" t="inlineStr">
+      <c r="B2302" s="2" t="inlineStr">
+        <is>
+          <t>蜂群巡防群</t>
+        </is>
+      </c>
+      <c r="C2302" s="2" t="inlineStr">
         <is>
           <t>{null,null,400004,400004,400004,400004,400004,400004,400004,400004,400004,400004,null,null,null}</t>
         </is>
       </c>
-      <c r="D2302" t="inlineStr">
+      <c r="D2302" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2303">
-      <c r="A2303" t="n">
+      <c r="A2303" s="2" t="n">
         <v>90405</v>
       </c>
-      <c r="B2303" t="inlineStr">
-        <is>
-          <t>第4关第5点重堡</t>
-        </is>
-      </c>
-      <c r="C2303" t="inlineStr">
+      <c r="B2303" s="2" t="inlineStr">
+        <is>
+          <t>合金堡垒</t>
+        </is>
+      </c>
+      <c r="C2303" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,400005,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2303" t="inlineStr">
+      <c r="D2303" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2304">
-      <c r="A2304" t="n">
+      <c r="A2304" s="2" t="n">
         <v>90406</v>
       </c>
-      <c r="B2304" t="inlineStr">
-        <is>
-          <t>第4关第6点哨卫</t>
-        </is>
-      </c>
-      <c r="C2304" t="inlineStr">
+      <c r="B2304" s="2" t="inlineStr">
+        <is>
+          <t>脉冲哨卫</t>
+        </is>
+      </c>
+      <c r="C2304" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,400006,400006,400006,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2304" t="inlineStr">
+      <c r="D2304" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2305">
-      <c r="A2305" t="n">
+      <c r="A2305" s="2" t="n">
         <v>90407</v>
       </c>
-      <c r="B2305" t="inlineStr">
-        <is>
-          <t>第4关第7点重堡</t>
-        </is>
-      </c>
-      <c r="C2305" t="inlineStr">
+      <c r="B2305" s="2" t="inlineStr">
+        <is>
+          <t>重炮壁垒</t>
+        </is>
+      </c>
+      <c r="C2305" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,400007,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2305" t="inlineStr">
+      <c r="D2305" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2306">
-      <c r="A2306" t="n">
+      <c r="A2306" s="2" t="n">
         <v>90408</v>
       </c>
-      <c r="B2306" t="inlineStr">
-        <is>
-          <t>第4关第8点重堡</t>
-        </is>
-      </c>
-      <c r="C2306" t="inlineStr">
+      <c r="B2306" s="2" t="inlineStr">
+        <is>
+          <t>关隘核心</t>
+        </is>
+      </c>
+      <c r="C2306" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,400008,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2306" t="inlineStr">
+      <c r="D2306" s="2" t="inlineStr">
         <is>
           <t>elite</t>
         </is>
       </c>
     </row>
     <row r="2307">
-      <c r="A2307" t="n">
+      <c r="A2307" s="2" t="n">
         <v>90501</v>
       </c>
-      <c r="B2307" t="inlineStr">
-        <is>
-          <t>第5关第1点哨卫</t>
-        </is>
-      </c>
-      <c r="C2307" t="inlineStr">
+      <c r="B2307" s="2" t="inlineStr">
+        <is>
+          <t>哨卫巡逻队</t>
+        </is>
+      </c>
+      <c r="C2307" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,500001,500001,500001,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2307" t="inlineStr">
+      <c r="D2307" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2308">
-      <c r="A2308" t="n">
+      <c r="A2308" s="2" t="n">
         <v>90502</v>
       </c>
-      <c r="B2308" t="inlineStr">
-        <is>
-          <t>第5关第2点哨卫</t>
-        </is>
-      </c>
-      <c r="C2308" t="inlineStr">
+      <c r="B2308" s="2" t="inlineStr">
+        <is>
+          <t>哨卫阻截队</t>
+        </is>
+      </c>
+      <c r="C2308" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,500002,500002,500002,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2308" t="inlineStr">
+      <c r="D2308" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2309">
-      <c r="A2309" t="n">
+      <c r="A2309" s="2" t="n">
         <v>90503</v>
       </c>
-      <c r="B2309" t="inlineStr">
-        <is>
-          <t>第5关第3点蜂群</t>
-        </is>
-      </c>
-      <c r="C2309" t="inlineStr">
+      <c r="B2309" s="2" t="inlineStr">
+        <is>
+          <t>蜂群散阵</t>
+        </is>
+      </c>
+      <c r="C2309" s="2" t="inlineStr">
         <is>
           <t>{null,null,500003,500003,500003,500003,500003,500003,500003,500003,500003,500003,null,null,null}</t>
         </is>
       </c>
-      <c r="D2309" t="inlineStr">
+      <c r="D2309" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2310">
-      <c r="A2310" t="n">
+      <c r="A2310" s="2" t="n">
         <v>90504</v>
       </c>
-      <c r="B2310" t="inlineStr">
-        <is>
-          <t>第5关第4点蜂群</t>
-        </is>
-      </c>
-      <c r="C2310" t="inlineStr">
+      <c r="B2310" s="2" t="inlineStr">
+        <is>
+          <t>蜂群密阵</t>
+        </is>
+      </c>
+      <c r="C2310" s="2" t="inlineStr">
         <is>
           <t>{null,null,500004,500004,500004,500004,500004,500004,500004,500004,500004,500004,null,null,null}</t>
         </is>
       </c>
-      <c r="D2310" t="inlineStr">
+      <c r="D2310" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2311">
-      <c r="A2311" t="n">
+      <c r="A2311" s="2" t="n">
         <v>90505</v>
       </c>
-      <c r="B2311" t="inlineStr">
-        <is>
-          <t>第5关第5点重堡</t>
-        </is>
-      </c>
-      <c r="C2311" t="inlineStr">
+      <c r="B2311" s="2" t="inlineStr">
+        <is>
+          <t>重甲堡垒</t>
+        </is>
+      </c>
+      <c r="C2311" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,500005,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2311" t="inlineStr">
+      <c r="D2311" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2312">
-      <c r="A2312" t="n">
+      <c r="A2312" s="2" t="n">
         <v>90506</v>
       </c>
-      <c r="B2312" t="inlineStr">
-        <is>
-          <t>第5关第6点重堡</t>
-        </is>
-      </c>
-      <c r="C2312" t="inlineStr">
+      <c r="B2312" s="2" t="inlineStr">
+        <is>
+          <t>重炮堡垒</t>
+        </is>
+      </c>
+      <c r="C2312" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,500006,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2312" t="inlineStr">
+      <c r="D2312" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2313">
-      <c r="A2313" t="n">
+      <c r="A2313" s="2" t="n">
         <v>90507</v>
       </c>
-      <c r="B2313" t="inlineStr">
-        <is>
-          <t>第5关第7点哨卫</t>
-        </is>
-      </c>
-      <c r="C2313" t="inlineStr">
+      <c r="B2313" s="2" t="inlineStr">
+        <is>
+          <t>能量哨卫群</t>
+        </is>
+      </c>
+      <c r="C2313" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,500007,500007,500007,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2313" t="inlineStr">
+      <c r="D2313" s="2" t="inlineStr">
         <is>
           <t>elite</t>
         </is>
       </c>
     </row>
     <row r="2314">
-      <c r="A2314" t="n">
+      <c r="A2314" s="2" t="n">
         <v>90508</v>
       </c>
-      <c r="B2314" t="inlineStr">
-        <is>
-          <t>第5关第8点蜂群</t>
-        </is>
-      </c>
-      <c r="C2314" t="inlineStr">
+      <c r="B2314" s="2" t="inlineStr">
+        <is>
+          <t>蜂群终阵</t>
+        </is>
+      </c>
+      <c r="C2314" s="2" t="inlineStr">
         <is>
           <t>{null,null,500008,500008,500008,500008,500008,500008,500008,500008,500008,500008,null,null,null}</t>
         </is>
       </c>
-      <c r="D2314" t="inlineStr">
+      <c r="D2314" s="2" t="inlineStr">
         <is>
           <t>elite</t>
         </is>
       </c>
     </row>
     <row r="2315">
-      <c r="A2315" t="n">
+      <c r="A2315" s="2" t="n">
         <v>90509</v>
       </c>
-      <c r="B2315" t="inlineStr">
-        <is>
-          <t>第5关第9点重堡</t>
-        </is>
-      </c>
-      <c r="C2315" t="inlineStr">
+      <c r="B2315" s="2" t="inlineStr">
+        <is>
+          <t>深空重堡</t>
+        </is>
+      </c>
+      <c r="C2315" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,500009,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2315" t="inlineStr">
+      <c r="D2315" s="2" t="inlineStr">
         <is>
           <t>elite</t>
         </is>
       </c>
     </row>
     <row r="2316">
-      <c r="A2316" t="n">
+      <c r="A2316" s="2" t="n">
         <v>90601</v>
       </c>
-      <c r="B2316" t="inlineStr">
-        <is>
-          <t>第6关第1点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2316" t="inlineStr">
+      <c r="B2316" s="2" t="inlineStr">
+        <is>
+          <t>锁定侦察艇</t>
+        </is>
+      </c>
+      <c r="C2316" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,600001,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2316" t="inlineStr">
+      <c r="D2316" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2317">
-      <c r="A2317" t="n">
+      <c r="A2317" s="2" t="n">
         <v>90602</v>
       </c>
-      <c r="B2317" t="inlineStr">
-        <is>
-          <t>第6关第2点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2317" t="inlineStr">
+      <c r="B2317" s="2" t="inlineStr">
+        <is>
+          <t>重脉冲哨卫</t>
+        </is>
+      </c>
+      <c r="C2317" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,600002,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2317" t="inlineStr">
+      <c r="D2317" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2318">
-      <c r="A2318" t="n">
+      <c r="A2318" s="2" t="n">
         <v>90603</v>
       </c>
-      <c r="B2318" t="inlineStr">
-        <is>
-          <t>第6关第3点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2318" t="inlineStr">
-        <is>
-          <t>{null,null,null,null,null,null,null,600003,null,null,null,null,null,null,null}</t>
-        </is>
-      </c>
-      <c r="D2318" t="inlineStr">
+      <c r="B2318" s="2" t="inlineStr">
+        <is>
+          <t>双机警戒线</t>
+        </is>
+      </c>
+      <c r="C2318" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,960003,null,600003,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2318" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2319">
-      <c r="A2319" t="n">
+      <c r="A2319" s="2" t="n">
         <v>90604</v>
       </c>
-      <c r="B2319" t="inlineStr">
-        <is>
-          <t>第6关第4点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2319" t="inlineStr">
+      <c r="B2319" s="2" t="inlineStr">
+        <is>
+          <t>回充护卫舰</t>
+        </is>
+      </c>
+      <c r="C2319" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,600004,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2319" t="inlineStr">
+      <c r="D2319" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2320">
-      <c r="A2320" t="n">
+      <c r="A2320" s="2" t="n">
         <v>90605</v>
       </c>
-      <c r="B2320" t="inlineStr">
-        <is>
-          <t>第6关第5点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2320" t="inlineStr">
+      <c r="B2320" s="2" t="inlineStr">
+        <is>
+          <t>重击炮艇</t>
+        </is>
+      </c>
+      <c r="C2320" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,600005,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2320" t="inlineStr">
+      <c r="D2320" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2321">
-      <c r="A2321" t="n">
+      <c r="A2321" s="2" t="n">
         <v>90606</v>
       </c>
-      <c r="B2321" t="inlineStr">
-        <is>
-          <t>第6关第6点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2321" t="inlineStr">
-        <is>
-          <t>{null,null,null,null,null,null,null,600006,null,null,null,null,null,null,null}</t>
-        </is>
-      </c>
-      <c r="D2321" t="inlineStr">
+      <c r="B2321" s="2" t="inlineStr">
+        <is>
+          <t>双翼巡防阵</t>
+        </is>
+      </c>
+      <c r="C2321" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,600006,null,960006,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2321" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2322">
-      <c r="A2322" t="n">
+      <c r="A2322" s="2" t="n">
         <v>90607</v>
       </c>
-      <c r="B2322" t="inlineStr">
-        <is>
-          <t>第6关第7点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2322" t="inlineStr">
+      <c r="B2322" s="2" t="inlineStr">
+        <is>
+          <t>再生护卫舰</t>
+        </is>
+      </c>
+      <c r="C2322" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,600007,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2322" t="inlineStr">
+      <c r="D2322" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2323">
-      <c r="A2323" t="n">
+      <c r="A2323" s="2" t="n">
         <v>90608</v>
       </c>
-      <c r="B2323" t="inlineStr">
-        <is>
-          <t>第6关第8点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2323" t="inlineStr">
+      <c r="B2323" s="2" t="inlineStr">
+        <is>
+          <t>远程炮台</t>
+        </is>
+      </c>
+      <c r="C2323" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,600008,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2323" t="inlineStr">
+      <c r="D2323" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2324">
-      <c r="A2324" t="n">
+      <c r="A2324" s="2" t="n">
         <v>90609</v>
       </c>
-      <c r="B2324" t="inlineStr">
-        <is>
-          <t>第6关第9点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2324" t="inlineStr">
+      <c r="B2324" s="2" t="inlineStr">
+        <is>
+          <t>束流壁垒</t>
+        </is>
+      </c>
+      <c r="C2324" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,600009,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2324" t="inlineStr">
+      <c r="D2324" s="2" t="inlineStr">
         <is>
           <t>boss</t>
         </is>
       </c>
     </row>
     <row r="2325">
-      <c r="A2325" t="n">
+      <c r="A2325" s="2" t="n">
         <v>90701</v>
       </c>
-      <c r="B2325" t="inlineStr">
-        <is>
-          <t>第7关第1点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2325" t="inlineStr">
+      <c r="B2325" s="2" t="inlineStr">
+        <is>
+          <t>深空屏障舰</t>
+        </is>
+      </c>
+      <c r="C2325" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,700001,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2325" t="inlineStr">
+      <c r="D2325" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2326">
-      <c r="A2326" t="n">
+      <c r="A2326" s="2" t="n">
         <v>90702</v>
       </c>
-      <c r="B2326" t="inlineStr">
-        <is>
-          <t>第7关第2点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2326" t="inlineStr">
+      <c r="B2326" s="2" t="inlineStr">
+        <is>
+          <t>重击哨卫</t>
+        </is>
+      </c>
+      <c r="C2326" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,700002,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2326" t="inlineStr">
+      <c r="D2326" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2327">
-      <c r="A2327" t="n">
+      <c r="A2327" s="2" t="n">
         <v>90703</v>
       </c>
-      <c r="B2327" t="inlineStr">
-        <is>
-          <t>第7关第3点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2327" t="inlineStr">
+      <c r="B2327" s="2" t="inlineStr">
+        <is>
+          <t>回充堡垒</t>
+        </is>
+      </c>
+      <c r="C2327" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,700003,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2327" t="inlineStr">
+      <c r="D2327" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2328">
-      <c r="A2328" t="n">
+      <c r="A2328" s="2" t="n">
         <v>90704</v>
       </c>
-      <c r="B2328" t="inlineStr">
-        <is>
-          <t>第7关第4点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2328" t="inlineStr">
-        <is>
-          <t>{null,null,null,null,null,null,null,700004,null,null,null,null,null,null,null}</t>
-        </is>
-      </c>
-      <c r="D2328" t="inlineStr">
+      <c r="B2328" s="2" t="inlineStr">
+        <is>
+          <t>双舰截击阵</t>
+        </is>
+      </c>
+      <c r="C2328" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,970004,null,700004,null,null,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2328" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2329">
-      <c r="A2329" t="n">
+      <c r="A2329" s="2" t="n">
         <v>90705</v>
       </c>
-      <c r="B2329" t="inlineStr">
-        <is>
-          <t>第7关第5点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2329" t="inlineStr">
+      <c r="B2329" s="2" t="inlineStr">
+        <is>
+          <t>长距炮艇</t>
+        </is>
+      </c>
+      <c r="C2329" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,700005,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2329" t="inlineStr">
+      <c r="D2329" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2330">
-      <c r="A2330" t="n">
+      <c r="A2330" s="2" t="n">
         <v>90706</v>
       </c>
-      <c r="B2330" t="inlineStr">
-        <is>
-          <t>第7关第6点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2330" t="inlineStr">
+      <c r="B2330" s="2" t="inlineStr">
+        <is>
+          <t>持续压制舰</t>
+        </is>
+      </c>
+      <c r="C2330" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,700006,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2330" t="inlineStr">
+      <c r="D2330" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2331">
-      <c r="A2331" t="n">
+      <c r="A2331" s="2" t="n">
         <v>90707</v>
       </c>
-      <c r="B2331" t="inlineStr">
-        <is>
-          <t>第7关第7点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2331" t="inlineStr">
-        <is>
-          <t>{null,null,null,null,null,null,null,700007,null,null,null,null,null,null,null}</t>
-        </is>
-      </c>
-      <c r="D2331" t="inlineStr">
+      <c r="B2331" s="2" t="inlineStr">
+        <is>
+          <t>双翼护航阵</t>
+        </is>
+      </c>
+      <c r="C2331" s="2" t="inlineStr">
+        <is>
+          <t>{null,null,null,null,null,null,null,700007,null,970007,null,null,null,null,null}</t>
+        </is>
+      </c>
+      <c r="D2331" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2332">
-      <c r="A2332" t="n">
+      <c r="A2332" s="2" t="n">
         <v>90708</v>
       </c>
-      <c r="B2332" t="inlineStr">
-        <is>
-          <t>第7关第8点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2332" t="inlineStr">
+      <c r="B2332" s="2" t="inlineStr">
+        <is>
+          <t>高压突击舰</t>
+        </is>
+      </c>
+      <c r="C2332" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,700008,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2332" t="inlineStr">
+      <c r="D2332" s="2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
     <row r="2333">
-      <c r="A2333" t="n">
+      <c r="A2333" s="2" t="n">
         <v>90709</v>
       </c>
-      <c r="B2333" t="inlineStr">
-        <is>
-          <t>第7关第9点光束靶舰</t>
-        </is>
-      </c>
-      <c r="C2333" t="inlineStr">
+      <c r="B2333" s="2" t="inlineStr">
+        <is>
+          <t>异空间门卫</t>
+        </is>
+      </c>
+      <c r="C2333" s="2" t="inlineStr">
         <is>
           <t>{null,null,null,null,null,null,null,700009,null,null,null,null,null,null,null}</t>
         </is>
       </c>
-      <c r="D2333" t="inlineStr">
+      <c r="D2333" s="2" t="inlineStr">
         <is>
           <t>boss</t>
         </is>

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="17700" windowHeight="13908" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monGroup" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="monGroup" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -45312,7 +45312,7 @@
       </c>
       <c r="C2284" s="2" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,271008,271009,271009,271010,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,271008,271009,271009,271005,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2284" s="2" t="inlineStr">
@@ -45532,7 +45532,7 @@
       </c>
       <c r="C2295" s="2" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,271008,271026,271027,271008,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,271017,271026,271027,271017,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2295" s="2" t="inlineStr">
@@ -45672,7 +45672,7 @@
       </c>
       <c r="C2302" s="2" t="inlineStr">
         <is>
-          <t>{null,null,400004,400004,400004,400004,400004,400004,400004,400004,400004,400004,null,null,null}</t>
+          <t>{null,null,null,null,null,400004,400004,400004,null,null,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2302" s="2" t="inlineStr">

--- a/space-battleship/config_excel/monGroup.xlsx
+++ b/space-battleship/config_excel/monGroup.xlsx
@@ -45672,7 +45672,7 @@
       </c>
       <c r="C2302" s="2" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,400004,400004,400004,null,null,null,null,null,null,null}</t>
+          <t>{null,null,null,400004,null,400004,null,400004,null,400004,null,400004,null,null,null}</t>
         </is>
       </c>
       <c r="D2302" s="2" t="inlineStr">
@@ -45712,7 +45712,7 @@
       </c>
       <c r="C2304" s="2" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,400006,400006,400006,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,400006,null,null,null,400006,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2304" s="2" t="inlineStr">
@@ -45792,7 +45792,7 @@
       </c>
       <c r="C2308" s="2" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,500002,500002,500002,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,500002,null,null,null,500002,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2308" s="2" t="inlineStr">
@@ -45832,7 +45832,7 @@
       </c>
       <c r="C2310" s="2" t="inlineStr">
         <is>
-          <t>{null,null,500004,500004,500004,500004,500004,500004,500004,500004,500004,500004,null,null,null}</t>
+          <t>{null,500004,null,500004,null,500004,500004,null,500004,500004,null,500004,null,500004,null}</t>
         </is>
       </c>
       <c r="D2310" s="2" t="inlineStr">
@@ -45872,7 +45872,7 @@
       </c>
       <c r="C2312" s="2" t="inlineStr">
         <is>
-          <t>{null,null,null,null,null,null,null,500006,null,null,null,null,null,null,null}</t>
+          <t>{null,null,null,null,null,500006,null,null,null,500006,null,null,null,null,null}</t>
         </is>
       </c>
       <c r="D2312" s="2" t="inlineStr">
